--- a/data/简答题评分.xlsx
+++ b/data/简答题评分.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2153" uniqueCount="972">
   <si>
     <t>疾病</t>
   </si>
@@ -1716,6 +1716,1233 @@
   </si>
   <si>
     <t>骨保护剂</t>
+  </si>
+  <si>
+    <t>“脑中风的警报”</t>
+  </si>
+  <si>
+    <t>偏瘫</t>
+  </si>
+  <si>
+    <t>半身不遂</t>
+  </si>
+  <si>
+    <t>肢体无力</t>
+  </si>
+  <si>
+    <t>失语</t>
+  </si>
+  <si>
+    <t>脑梗死</t>
+  </si>
+  <si>
+    <t>缺血性脑卒中</t>
+  </si>
+  <si>
+    <t>脑梗塞</t>
+  </si>
+  <si>
+    <t>溶栓</t>
+  </si>
+  <si>
+    <t>rt-PA</t>
+  </si>
+  <si>
+    <t>阿司匹林</t>
+  </si>
+  <si>
+    <t>抗血小板</t>
+  </si>
+  <si>
+    <t>他汀</t>
+  </si>
+  <si>
+    <t>降脂药</t>
+  </si>
+  <si>
+    <t>NIHSS评分</t>
+  </si>
+  <si>
+    <t>神经功能缺损评分</t>
+  </si>
+  <si>
+    <t>脑疝</t>
+  </si>
+  <si>
+    <t>颅内压增高</t>
+  </si>
+  <si>
+    <t>颈动脉斑块</t>
+  </si>
+  <si>
+    <t>动脉硬化</t>
+  </si>
+  <si>
+    <t>“半身风云”</t>
+  </si>
+  <si>
+    <t>“惊厥之舞”</t>
+  </si>
+  <si>
+    <t>抽搐</t>
+  </si>
+  <si>
+    <t>惊厥</t>
+  </si>
+  <si>
+    <t>痉挛</t>
+  </si>
+  <si>
+    <t>昏迷</t>
+  </si>
+  <si>
+    <t>口吐白沫</t>
+  </si>
+  <si>
+    <t>流涎</t>
+  </si>
+  <si>
+    <t>脑电图</t>
+  </si>
+  <si>
+    <t>EEG</t>
+  </si>
+  <si>
+    <t>棘慢波</t>
+  </si>
+  <si>
+    <t>抗癫痫药物</t>
+  </si>
+  <si>
+    <t>AED</t>
+  </si>
+  <si>
+    <t>丙戊酸钠</t>
+  </si>
+  <si>
+    <t>VPA</t>
+  </si>
+  <si>
+    <t>副作用</t>
+  </si>
+  <si>
+    <t>血药浓度</t>
+  </si>
+  <si>
+    <t>TDM</t>
+  </si>
+  <si>
+    <t>长期治疗</t>
+  </si>
+  <si>
+    <t>维持治疗</t>
+  </si>
+  <si>
+    <t>避免诱因</t>
+  </si>
+  <si>
+    <t>驾驶禁忌</t>
+  </si>
+  <si>
+    <t>安全限制</t>
+  </si>
+  <si>
+    <t>停药</t>
+  </si>
+  <si>
+    <t>撤药</t>
+  </si>
+  <si>
+    <t>“隐形的枷锁”</t>
+  </si>
+  <si>
+    <t>情绪低落</t>
+  </si>
+  <si>
+    <t>抑郁</t>
+  </si>
+  <si>
+    <t>沮丧</t>
+  </si>
+  <si>
+    <t>兴趣减退</t>
+  </si>
+  <si>
+    <t>快感缺失</t>
+  </si>
+  <si>
+    <t>自杀念头</t>
+  </si>
+  <si>
+    <t>自杀观念</t>
+  </si>
+  <si>
+    <t>自杀意向</t>
+  </si>
+  <si>
+    <t>失眠</t>
+  </si>
+  <si>
+    <t>入睡困难</t>
+  </si>
+  <si>
+    <t>早醒</t>
+  </si>
+  <si>
+    <t>SSRI</t>
+  </si>
+  <si>
+    <t>选择性5-羟色胺再摄取抑制剂</t>
+  </si>
+  <si>
+    <t>舍曲林</t>
+  </si>
+  <si>
+    <t>sertraline</t>
+  </si>
+  <si>
+    <t>心理治疗</t>
+  </si>
+  <si>
+    <t>CBT</t>
+  </si>
+  <si>
+    <t>认知行为疗法</t>
+  </si>
+  <si>
+    <t>巩固期</t>
+  </si>
+  <si>
+    <t>PHQ-9</t>
+  </si>
+  <si>
+    <t>患者健康问卷</t>
+  </si>
+  <si>
+    <t>家庭支持</t>
+  </si>
+  <si>
+    <t>家属陪伴</t>
+  </si>
+  <si>
+    <t>“心弦紧绷”</t>
+  </si>
+  <si>
+    <t>压榨感</t>
+  </si>
+  <si>
+    <t>压迫感</t>
+  </si>
+  <si>
+    <t>紧缩感</t>
+  </si>
+  <si>
+    <t>向左肩放射</t>
+  </si>
+  <si>
+    <t>放射痛</t>
+  </si>
+  <si>
+    <t>硝酸甘油</t>
+  </si>
+  <si>
+    <t>消心痛</t>
+  </si>
+  <si>
+    <t>冠脉造影</t>
+  </si>
+  <si>
+    <t>CAG</t>
+  </si>
+  <si>
+    <t>氯吡格雷</t>
+  </si>
+  <si>
+    <t>波立维</t>
+  </si>
+  <si>
+    <t>双抗</t>
+  </si>
+  <si>
+    <t>“心跳乱了”</t>
+  </si>
+  <si>
+    <t>心悸</t>
+  </si>
+  <si>
+    <t>心慌</t>
+  </si>
+  <si>
+    <t>心跳加速</t>
+  </si>
+  <si>
+    <t>憋气</t>
+  </si>
+  <si>
+    <t>气短</t>
+  </si>
+  <si>
+    <t>心律不齐</t>
+  </si>
+  <si>
+    <t>房颤</t>
+  </si>
+  <si>
+    <t>心房颤动</t>
+  </si>
+  <si>
+    <t>CHA2DS2-VASc</t>
+  </si>
+  <si>
+    <t>卒中风险评估</t>
+  </si>
+  <si>
+    <t>抗凝</t>
+  </si>
+  <si>
+    <t>抗凝治疗</t>
+  </si>
+  <si>
+    <t>华法林</t>
+  </si>
+  <si>
+    <t>warfarin</t>
+  </si>
+  <si>
+    <t>INR</t>
+  </si>
+  <si>
+    <t>国际标准化比值</t>
+  </si>
+  <si>
+    <t>NOAC</t>
+  </si>
+  <si>
+    <t>新型口服抗凝药</t>
+  </si>
+  <si>
+    <t>卒中预防</t>
+  </si>
+  <si>
+    <t>栓塞预防</t>
+  </si>
+  <si>
+    <t>出血风险</t>
+  </si>
+  <si>
+    <t>HAS-BLED</t>
+  </si>
+  <si>
+    <t>β受体阻滞剂</t>
+  </si>
+  <si>
+    <t>倍他乐克</t>
+  </si>
+  <si>
+    <t>定期监测</t>
+  </si>
+  <si>
+    <t>“泵的挣扎”</t>
+  </si>
+  <si>
+    <t>端坐呼吸</t>
+  </si>
+  <si>
+    <t>不能平卧</t>
+  </si>
+  <si>
+    <t>粉红色泡沫痰</t>
+  </si>
+  <si>
+    <t>肺水肿</t>
+  </si>
+  <si>
+    <t>水泡音</t>
+  </si>
+  <si>
+    <t>呋塞米</t>
+  </si>
+  <si>
+    <t>速尿</t>
+  </si>
+  <si>
+    <t>血管紧张素转换酶抑制剂</t>
+  </si>
+  <si>
+    <t>普利类</t>
+  </si>
+  <si>
+    <t>射血分数</t>
+  </si>
+  <si>
+    <t>BNP</t>
+  </si>
+  <si>
+    <t>脑钠肽</t>
+  </si>
+  <si>
+    <t>NT-proBNP</t>
+  </si>
+  <si>
+    <t>限盐</t>
+  </si>
+  <si>
+    <t>低盐饮食</t>
+  </si>
+  <si>
+    <t>体重监测</t>
+  </si>
+  <si>
+    <t>每日称重</t>
+  </si>
+  <si>
+    <t>缺血性心肌病</t>
+  </si>
+  <si>
+    <t>冠心病心衰</t>
+  </si>
+  <si>
+    <t>“喘息的风箱”</t>
+  </si>
+  <si>
+    <t>喘息</t>
+  </si>
+  <si>
+    <t>哮鸣音</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> wheezing</t>
+  </si>
+  <si>
+    <t>β2受体激动剂</t>
+  </si>
+  <si>
+    <t>沙丁胺醇</t>
+  </si>
+  <si>
+    <t>特布他林</t>
+  </si>
+  <si>
+    <t>吸入糖皮质激素</t>
+  </si>
+  <si>
+    <t>ICS</t>
+  </si>
+  <si>
+    <t>布地奈德</t>
+  </si>
+  <si>
+    <t>氟替卡松</t>
+  </si>
+  <si>
+    <t>肺功能</t>
+  </si>
+  <si>
+    <t>FEV1</t>
+  </si>
+  <si>
+    <t>峰流速</t>
+  </si>
+  <si>
+    <t>过敏原</t>
+  </si>
+  <si>
+    <t>变应原</t>
+  </si>
+  <si>
+    <t>气道炎症</t>
+  </si>
+  <si>
+    <t>慢性炎症</t>
+  </si>
+  <si>
+    <t>控制治疗</t>
+  </si>
+  <si>
+    <t>长期管理</t>
+  </si>
+  <si>
+    <t>峰流速仪</t>
+  </si>
+  <si>
+    <t>PEF监测</t>
+  </si>
+  <si>
+    <t>预防发作</t>
+  </si>
+  <si>
+    <t>哮喘行动计划</t>
+  </si>
+  <si>
+    <t>自我管理</t>
+  </si>
+  <si>
+    <t>“被困的气泡”</t>
+  </si>
+  <si>
+    <t>针刺样疼痛</t>
+  </si>
+  <si>
+    <t>锐痛</t>
+  </si>
+  <si>
+    <t>喘不上气</t>
+  </si>
+  <si>
+    <t>呼吸音消失</t>
+  </si>
+  <si>
+    <t>呼吸音减低</t>
+  </si>
+  <si>
+    <t>呼吸音减弱</t>
+  </si>
+  <si>
+    <t>气胸</t>
+  </si>
+  <si>
+    <t>pneumothorax</t>
+  </si>
+  <si>
+    <t>胸腔闭式引流</t>
+  </si>
+  <si>
+    <t>水封瓶引流</t>
+  </si>
+  <si>
+    <t>肺压缩</t>
+  </si>
+  <si>
+    <t>肺萎陷</t>
+  </si>
+  <si>
+    <t>肺大疱</t>
+  </si>
+  <si>
+    <t>肺大泡</t>
+  </si>
+  <si>
+    <t>拔管</t>
+  </si>
+  <si>
+    <t>引流管拔除</t>
+  </si>
+  <si>
+    <t>避免剧烈运动</t>
+  </si>
+  <si>
+    <t>活动限制</t>
+  </si>
+  <si>
+    <t>潜水禁忌</t>
+  </si>
+  <si>
+    <t>禁潜水</t>
+  </si>
+  <si>
+    <t>乘飞机</t>
+  </si>
+  <si>
+    <t>航空旅行</t>
+  </si>
+  <si>
+    <t>“沉默的阴影”</t>
+  </si>
+  <si>
+    <t>干咳</t>
+  </si>
+  <si>
+    <t>刺激性咳嗽</t>
+  </si>
+  <si>
+    <t>咯血</t>
+  </si>
+  <si>
+    <t>痰中带血</t>
+  </si>
+  <si>
+    <t>血丝痰</t>
+  </si>
+  <si>
+    <t>吸烟</t>
+  </si>
+  <si>
+    <t>吸烟史</t>
+  </si>
+  <si>
+    <t>肺鳞癌</t>
+  </si>
+  <si>
+    <t>鳞状细胞癌</t>
+  </si>
+  <si>
+    <t>支气管镜</t>
+  </si>
+  <si>
+    <t>纤支镜</t>
+  </si>
+  <si>
+    <t>活检</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>计算机断层扫描</t>
+  </si>
+  <si>
+    <t>TNM分期</t>
+  </si>
+  <si>
+    <t>分期</t>
+  </si>
+  <si>
+    <t>放疗</t>
+  </si>
+  <si>
+    <t>放射治疗</t>
+  </si>
+  <si>
+    <t>戒烟</t>
+  </si>
+  <si>
+    <t>停止吸烟</t>
+  </si>
+  <si>
+    <t>“胃里的火山”</t>
+  </si>
+  <si>
+    <t>十二指肠溃疡</t>
+  </si>
+  <si>
+    <t>球部溃疡</t>
+  </si>
+  <si>
+    <t>DU</t>
+  </si>
+  <si>
+    <t>饥饿时痛</t>
+  </si>
+  <si>
+    <t>空腹疼痛</t>
+  </si>
+  <si>
+    <t>阿莫西林+克拉霉素+PPI</t>
+  </si>
+  <si>
+    <t>兰索拉唑</t>
+  </si>
+  <si>
+    <t>泮托拉唑</t>
+  </si>
+  <si>
+    <t>胃镜检查</t>
+  </si>
+  <si>
+    <t>夜间痛醒</t>
+  </si>
+  <si>
+    <t>黏膜保护剂</t>
+  </si>
+  <si>
+    <t>胃黏膜保护药</t>
+  </si>
+  <si>
+    <t>A1期</t>
+  </si>
+  <si>
+    <t>活动期</t>
+  </si>
+  <si>
+    <t>溃疡分期</t>
+  </si>
+  <si>
+    <t>“肝胆风云”</t>
+  </si>
+  <si>
+    <t>胆绞痛</t>
+  </si>
+  <si>
+    <t>右肩放射痛</t>
+  </si>
+  <si>
+    <t>墨菲征</t>
+  </si>
+  <si>
+    <t>Murphy征</t>
+  </si>
+  <si>
+    <t>胆囊触痛</t>
+  </si>
+  <si>
+    <t>胆囊炎</t>
+  </si>
+  <si>
+    <t>胆囊炎症</t>
+  </si>
+  <si>
+    <t>B超</t>
+  </si>
+  <si>
+    <t>超声</t>
+  </si>
+  <si>
+    <t>腹部B超</t>
+  </si>
+  <si>
+    <t>控制脂肪</t>
+  </si>
+  <si>
+    <t>术后并发症</t>
+  </si>
+  <si>
+    <t>残余结石</t>
+  </si>
+  <si>
+    <t>胆漏</t>
+  </si>
+  <si>
+    <t>“肠路惊魂”</t>
+  </si>
+  <si>
+    <t>血便</t>
+  </si>
+  <si>
+    <t>大便带血</t>
+  </si>
+  <si>
+    <t>排便习惯改变</t>
+  </si>
+  <si>
+    <t>腹泻便秘交替</t>
+  </si>
+  <si>
+    <t>结直肠癌</t>
+  </si>
+  <si>
+    <t>大肠癌</t>
+  </si>
+  <si>
+    <t>CRC</t>
+  </si>
+  <si>
+    <t>腺癌</t>
+  </si>
+  <si>
+    <t>adenocarcinoma</t>
+  </si>
+  <si>
+    <t>结肠镜</t>
+  </si>
+  <si>
+    <t>肠镜</t>
+  </si>
+  <si>
+    <t>纤维结肠镜</t>
+  </si>
+  <si>
+    <t>Ⅲ期</t>
+  </si>
+  <si>
+    <t>辅助化疗</t>
+  </si>
+  <si>
+    <t>术后化疗</t>
+  </si>
+  <si>
+    <t>氟尿嘧啶</t>
+  </si>
+  <si>
+    <t>奥沙利铂</t>
+  </si>
+  <si>
+    <t>卡培他滨</t>
+  </si>
+  <si>
+    <t>“石破天惊”</t>
+  </si>
+  <si>
+    <t>肾绞痛</t>
+  </si>
+  <si>
+    <t>腰腹痛</t>
+  </si>
+  <si>
+    <t>绞痛</t>
+  </si>
+  <si>
+    <t>输尿管结石</t>
+  </si>
+  <si>
+    <t>尿路结石</t>
+  </si>
+  <si>
+    <t>肾结石</t>
+  </si>
+  <si>
+    <t>体外冲击波碎石</t>
+  </si>
+  <si>
+    <t>ESWL</t>
+  </si>
+  <si>
+    <t>输尿管镜</t>
+  </si>
+  <si>
+    <t>URS</t>
+  </si>
+  <si>
+    <t>草酸钙</t>
+  </si>
+  <si>
+    <t>结石成分</t>
+  </si>
+  <si>
+    <t>低草酸饮食</t>
+  </si>
+  <si>
+    <t>双J管</t>
+  </si>
+  <si>
+    <t>支架管</t>
+  </si>
+  <si>
+    <t>肾积水</t>
+  </si>
+  <si>
+    <t>肾盂积水</t>
+  </si>
+  <si>
+    <t>解痉止痛</t>
+  </si>
+  <si>
+    <t>山莨菪碱</t>
+  </si>
+  <si>
+    <t>非甾体抗炎药</t>
+  </si>
+  <si>
+    <t>“隐秘的河流”</t>
+  </si>
+  <si>
+    <t>蛋白尿定量</t>
+  </si>
+  <si>
+    <t>慢性肾小球肾炎</t>
+  </si>
+  <si>
+    <t>慢性肾炎</t>
+  </si>
+  <si>
+    <t>CKD</t>
+  </si>
+  <si>
+    <t>eGFR</t>
+  </si>
+  <si>
+    <t>肾小球滤过率</t>
+  </si>
+  <si>
+    <t>肾性贫血</t>
+  </si>
+  <si>
+    <t>EPO</t>
+  </si>
+  <si>
+    <t>透析</t>
+  </si>
+  <si>
+    <t>“火海警报”</t>
+  </si>
+  <si>
+    <t>尿频尿急尿痛</t>
+  </si>
+  <si>
+    <t>膀胱刺激征</t>
+  </si>
+  <si>
+    <t>肾区叩痛</t>
+  </si>
+  <si>
+    <t>肾区压痛</t>
+  </si>
+  <si>
+    <t>尿培养</t>
+  </si>
+  <si>
+    <t>中段尿培养</t>
+  </si>
+  <si>
+    <t>大肠埃希菌</t>
+  </si>
+  <si>
+    <t>大肠杆菌</t>
+  </si>
+  <si>
+    <t>抗菌药物</t>
+  </si>
+  <si>
+    <t>疗程</t>
+  </si>
+  <si>
+    <t>治疗时间</t>
+  </si>
+  <si>
+    <t>引流梗阻</t>
+  </si>
+  <si>
+    <t>勤排尿</t>
+  </si>
+  <si>
+    <t>“折翼天使”</t>
+  </si>
+  <si>
+    <t>肱骨髁上骨折</t>
+  </si>
+  <si>
+    <t>髁上骨折</t>
+  </si>
+  <si>
+    <t>桡动脉搏动减弱</t>
+  </si>
+  <si>
+    <t>血管损伤</t>
+  </si>
+  <si>
+    <t>骨筋膜室综合征</t>
+  </si>
+  <si>
+    <t>筋膜间室综合征</t>
+  </si>
+  <si>
+    <t>缺血性肌挛缩</t>
+  </si>
+  <si>
+    <t>Volkmann挛缩</t>
+  </si>
+  <si>
+    <t>切开减压</t>
+  </si>
+  <si>
+    <t>筋膜切开</t>
+  </si>
+  <si>
+    <t>肘内翻</t>
+  </si>
+  <si>
+    <t>肘内翻畸形</t>
+  </si>
+  <si>
+    <t>神经损伤</t>
+  </si>
+  <si>
+    <t>桡神经损伤</t>
+  </si>
+  <si>
+    <t>儿童骨折</t>
+  </si>
+  <si>
+    <t>骨骺损伤</t>
+  </si>
+  <si>
+    <t>石膏固定</t>
+  </si>
+  <si>
+    <t>外固定</t>
+  </si>
+  <si>
+    <t>“行走的齿轮”</t>
+  </si>
+  <si>
+    <t>骨关节炎</t>
+  </si>
+  <si>
+    <t>骨关节病</t>
+  </si>
+  <si>
+    <t>OA</t>
+  </si>
+  <si>
+    <t>膝关节内翻</t>
+  </si>
+  <si>
+    <t>膝内翻</t>
+  </si>
+  <si>
+    <t>罗圈腿</t>
+  </si>
+  <si>
+    <t>关节间隙变窄</t>
+  </si>
+  <si>
+    <t>软骨退变</t>
+  </si>
+  <si>
+    <t>骨赘</t>
+  </si>
+  <si>
+    <t>骨质增生</t>
+  </si>
+  <si>
+    <t>人工膝关节置换</t>
+  </si>
+  <si>
+    <t>TKA</t>
+  </si>
+  <si>
+    <t>人工关节</t>
+  </si>
+  <si>
+    <t>深静脉血栓</t>
+  </si>
+  <si>
+    <t>DVT</t>
+  </si>
+  <si>
+    <t>氨基葡萄糖</t>
+  </si>
+  <si>
+    <t>软骨素</t>
+  </si>
+  <si>
+    <t>玻璃酸钠</t>
+  </si>
+  <si>
+    <t>透明质酸</t>
+  </si>
+  <si>
+    <t>假体寿命</t>
+  </si>
+  <si>
+    <t>人工关节寿命</t>
+  </si>
+  <si>
+    <t>“断桥残雪”</t>
+  </si>
+  <si>
+    <t>腰椎间盘突出症</t>
+  </si>
+  <si>
+    <t>腰椎间盘突出</t>
+  </si>
+  <si>
+    <t>LDH</t>
+  </si>
+  <si>
+    <t>坐骨神经痛</t>
+  </si>
+  <si>
+    <t>下肢放射痛</t>
+  </si>
+  <si>
+    <t>直腿抬高试验</t>
+  </si>
+  <si>
+    <t>Lasegue征</t>
+  </si>
+  <si>
+    <t>神经根压迫</t>
+  </si>
+  <si>
+    <t>神经根症状</t>
+  </si>
+  <si>
+    <t>马尾综合征</t>
+  </si>
+  <si>
+    <t>马尾神经损伤</t>
+  </si>
+  <si>
+    <t>大小便障碍</t>
+  </si>
+  <si>
+    <t>尿潴留</t>
+  </si>
+  <si>
+    <t>便秘</t>
+  </si>
+  <si>
+    <t>髓核摘除术</t>
+  </si>
+  <si>
+    <t>椎间盘切除术</t>
+  </si>
+  <si>
+    <t>腰背肌锻炼</t>
+  </si>
+  <si>
+    <t>核心肌群锻炼</t>
+  </si>
+  <si>
+    <t>卧床休息</t>
+  </si>
+  <si>
+    <t>保守治疗</t>
+  </si>
+  <si>
+    <t>避免久坐</t>
+  </si>
+  <si>
+    <t>正确姿势</t>
+  </si>
+  <si>
+    <t>“糖衣炮弹”</t>
+  </si>
+  <si>
+    <t>多饮多尿</t>
+  </si>
+  <si>
+    <t>口渴多饮</t>
+  </si>
+  <si>
+    <t>体重下降</t>
+  </si>
+  <si>
+    <t>消瘦</t>
+  </si>
+  <si>
+    <t>空腹血糖</t>
+  </si>
+  <si>
+    <t>血糖升高</t>
+  </si>
+  <si>
+    <t>二甲双胍</t>
+  </si>
+  <si>
+    <t>双胍类</t>
+  </si>
+  <si>
+    <t>胃肠道反应</t>
+  </si>
+  <si>
+    <t>降压目标</t>
+  </si>
+  <si>
+    <t>慢性并发症</t>
+  </si>
+  <si>
+    <t>糖尿病并发症</t>
+  </si>
+  <si>
+    <t>“隐形狂飙”</t>
+  </si>
+  <si>
+    <t>心慌手抖</t>
+  </si>
+  <si>
+    <t>震颤</t>
+  </si>
+  <si>
+    <t>怕热多汗</t>
+  </si>
+  <si>
+    <t>多汗</t>
+  </si>
+  <si>
+    <t>甲状腺肿大</t>
+  </si>
+  <si>
+    <t>甲状腺肿</t>
+  </si>
+  <si>
+    <t>FT3/FT4升高</t>
+  </si>
+  <si>
+    <t>甲功异常</t>
+  </si>
+  <si>
+    <t>TSH降低</t>
+  </si>
+  <si>
+    <t>促甲状腺激素</t>
+  </si>
+  <si>
+    <t>Graves病</t>
+  </si>
+  <si>
+    <t>毒性弥漫性甲状腺肿</t>
+  </si>
+  <si>
+    <t>甲巯咪唑</t>
+  </si>
+  <si>
+    <t>他巴唑</t>
+  </si>
+  <si>
+    <t>粒细胞缺乏</t>
+  </si>
+  <si>
+    <t>白细胞减少</t>
+  </si>
+  <si>
+    <t>丙硫氧嘧啶</t>
+  </si>
+  <si>
+    <t>PTU</t>
+  </si>
+  <si>
+    <t>甲亢危象</t>
+  </si>
+  <si>
+    <t>甲状腺危象</t>
+  </si>
+  <si>
+    <t>“荷尔蒙迷航”</t>
+  </si>
+  <si>
+    <t>月经稀发</t>
+  </si>
+  <si>
+    <t>月经不调</t>
+  </si>
+  <si>
+    <t>多毛</t>
+  </si>
+  <si>
+    <t>毛发增多</t>
+  </si>
+  <si>
+    <t>BMI升高</t>
+  </si>
+  <si>
+    <t>高雄激素</t>
+  </si>
+  <si>
+    <t>睾酮升高</t>
+  </si>
+  <si>
+    <t>LH/FSH比值升高</t>
+  </si>
+  <si>
+    <t>黄体生成素/卵泡刺激素</t>
+  </si>
+  <si>
+    <t>卵巢多囊样改变</t>
+  </si>
+  <si>
+    <t>项链征</t>
+  </si>
+  <si>
+    <t>PCOS超声</t>
+  </si>
+  <si>
+    <t>克罗米芬</t>
+  </si>
+  <si>
+    <t>氯米芬</t>
+  </si>
+  <si>
+    <t>促排卵</t>
+  </si>
+  <si>
+    <t>诱导排卵</t>
+  </si>
+  <si>
+    <t>卵巢过度刺激综合征</t>
+  </si>
+  <si>
+    <t>OHSS</t>
   </si>
 </sst>
 </file>
@@ -2680,7 +3907,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H238"/>
+  <dimension ref="A1:H478"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -7191,6 +8418,4314 @@
         <v>39</v>
       </c>
     </row>
+    <row r="239" spans="1:7">
+      <c r="A239" t="s">
+        <v>563</v>
+      </c>
+      <c r="B239" t="s">
+        <v>564</v>
+      </c>
+      <c r="C239">
+        <v>2</v>
+      </c>
+      <c r="D239" t="s">
+        <v>565</v>
+      </c>
+      <c r="E239" t="s">
+        <v>566</v>
+      </c>
+      <c r="G239" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" t="s">
+        <v>563</v>
+      </c>
+      <c r="B240" t="s">
+        <v>567</v>
+      </c>
+      <c r="C240">
+        <v>2</v>
+      </c>
+      <c r="D240" t="s">
+        <v>34</v>
+      </c>
+      <c r="F240" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" t="s">
+        <v>563</v>
+      </c>
+      <c r="B241" t="s">
+        <v>568</v>
+      </c>
+      <c r="C241">
+        <v>3</v>
+      </c>
+      <c r="D241" t="s">
+        <v>569</v>
+      </c>
+      <c r="E241" t="s">
+        <v>570</v>
+      </c>
+      <c r="G241" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" t="s">
+        <v>563</v>
+      </c>
+      <c r="B242" t="s">
+        <v>571</v>
+      </c>
+      <c r="C242">
+        <v>3</v>
+      </c>
+      <c r="D242" t="s">
+        <v>572</v>
+      </c>
+      <c r="F242" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243" t="s">
+        <v>563</v>
+      </c>
+      <c r="B243" t="s">
+        <v>573</v>
+      </c>
+      <c r="C243">
+        <v>2</v>
+      </c>
+      <c r="D243" t="s">
+        <v>574</v>
+      </c>
+      <c r="F243" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244" t="s">
+        <v>563</v>
+      </c>
+      <c r="B244" t="s">
+        <v>575</v>
+      </c>
+      <c r="C244">
+        <v>2</v>
+      </c>
+      <c r="D244" t="s">
+        <v>576</v>
+      </c>
+      <c r="F244" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245" t="s">
+        <v>563</v>
+      </c>
+      <c r="B245" t="s">
+        <v>44</v>
+      </c>
+      <c r="C245">
+        <v>2</v>
+      </c>
+      <c r="D245" t="s">
+        <v>372</v>
+      </c>
+      <c r="F245" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246" t="s">
+        <v>563</v>
+      </c>
+      <c r="B246" t="s">
+        <v>234</v>
+      </c>
+      <c r="C246">
+        <v>2</v>
+      </c>
+      <c r="D246" t="s">
+        <v>208</v>
+      </c>
+      <c r="F246" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247" t="s">
+        <v>563</v>
+      </c>
+      <c r="B247" t="s">
+        <v>9</v>
+      </c>
+      <c r="C247">
+        <v>2</v>
+      </c>
+      <c r="D247" t="s">
+        <v>479</v>
+      </c>
+      <c r="F247" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248" t="s">
+        <v>563</v>
+      </c>
+      <c r="B248" t="s">
+        <v>577</v>
+      </c>
+      <c r="C248">
+        <v>3</v>
+      </c>
+      <c r="D248" t="s">
+        <v>578</v>
+      </c>
+      <c r="F248" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249" t="s">
+        <v>563</v>
+      </c>
+      <c r="B249" t="s">
+        <v>579</v>
+      </c>
+      <c r="C249">
+        <v>3</v>
+      </c>
+      <c r="D249" t="s">
+        <v>580</v>
+      </c>
+      <c r="F249" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250" t="s">
+        <v>563</v>
+      </c>
+      <c r="B250" t="s">
+        <v>581</v>
+      </c>
+      <c r="C250">
+        <v>2</v>
+      </c>
+      <c r="D250" t="s">
+        <v>582</v>
+      </c>
+      <c r="F250" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251" t="s">
+        <v>583</v>
+      </c>
+      <c r="B251" t="s">
+        <v>564</v>
+      </c>
+      <c r="C251">
+        <v>2</v>
+      </c>
+      <c r="D251" t="s">
+        <v>565</v>
+      </c>
+      <c r="E251" t="s">
+        <v>566</v>
+      </c>
+      <c r="G251" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252" t="s">
+        <v>583</v>
+      </c>
+      <c r="B252" t="s">
+        <v>567</v>
+      </c>
+      <c r="C252">
+        <v>2</v>
+      </c>
+      <c r="D252" t="s">
+        <v>34</v>
+      </c>
+      <c r="F252" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253" t="s">
+        <v>583</v>
+      </c>
+      <c r="B253" t="s">
+        <v>568</v>
+      </c>
+      <c r="C253">
+        <v>3</v>
+      </c>
+      <c r="D253" t="s">
+        <v>569</v>
+      </c>
+      <c r="E253" t="s">
+        <v>570</v>
+      </c>
+      <c r="G253" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254" t="s">
+        <v>583</v>
+      </c>
+      <c r="B254" t="s">
+        <v>571</v>
+      </c>
+      <c r="C254">
+        <v>3</v>
+      </c>
+      <c r="D254" t="s">
+        <v>572</v>
+      </c>
+      <c r="F254" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255" t="s">
+        <v>583</v>
+      </c>
+      <c r="B255" t="s">
+        <v>573</v>
+      </c>
+      <c r="C255">
+        <v>2</v>
+      </c>
+      <c r="D255" t="s">
+        <v>574</v>
+      </c>
+      <c r="F255" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256" t="s">
+        <v>583</v>
+      </c>
+      <c r="B256" t="s">
+        <v>575</v>
+      </c>
+      <c r="C256">
+        <v>2</v>
+      </c>
+      <c r="D256" t="s">
+        <v>576</v>
+      </c>
+      <c r="F256" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" t="s">
+        <v>583</v>
+      </c>
+      <c r="B257" t="s">
+        <v>44</v>
+      </c>
+      <c r="C257">
+        <v>2</v>
+      </c>
+      <c r="D257" t="s">
+        <v>372</v>
+      </c>
+      <c r="F257" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" t="s">
+        <v>583</v>
+      </c>
+      <c r="B258" t="s">
+        <v>234</v>
+      </c>
+      <c r="C258">
+        <v>2</v>
+      </c>
+      <c r="D258" t="s">
+        <v>208</v>
+      </c>
+      <c r="F258" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" t="s">
+        <v>583</v>
+      </c>
+      <c r="B259" t="s">
+        <v>9</v>
+      </c>
+      <c r="C259">
+        <v>2</v>
+      </c>
+      <c r="D259" t="s">
+        <v>479</v>
+      </c>
+      <c r="F259" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" t="s">
+        <v>583</v>
+      </c>
+      <c r="B260" t="s">
+        <v>577</v>
+      </c>
+      <c r="C260">
+        <v>3</v>
+      </c>
+      <c r="D260" t="s">
+        <v>578</v>
+      </c>
+      <c r="F260" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" t="s">
+        <v>583</v>
+      </c>
+      <c r="B261" t="s">
+        <v>579</v>
+      </c>
+      <c r="C261">
+        <v>3</v>
+      </c>
+      <c r="D261" t="s">
+        <v>580</v>
+      </c>
+      <c r="F261" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" t="s">
+        <v>583</v>
+      </c>
+      <c r="B262" t="s">
+        <v>581</v>
+      </c>
+      <c r="C262">
+        <v>2</v>
+      </c>
+      <c r="D262" t="s">
+        <v>582</v>
+      </c>
+      <c r="F262" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263" t="s">
+        <v>584</v>
+      </c>
+      <c r="B263" t="s">
+        <v>585</v>
+      </c>
+      <c r="C263">
+        <v>2</v>
+      </c>
+      <c r="D263" t="s">
+        <v>586</v>
+      </c>
+      <c r="E263" t="s">
+        <v>587</v>
+      </c>
+      <c r="G263" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" t="s">
+        <v>584</v>
+      </c>
+      <c r="B264" t="s">
+        <v>244</v>
+      </c>
+      <c r="C264">
+        <v>2</v>
+      </c>
+      <c r="D264" t="s">
+        <v>588</v>
+      </c>
+      <c r="E264" t="s">
+        <v>245</v>
+      </c>
+      <c r="G264" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" t="s">
+        <v>584</v>
+      </c>
+      <c r="B265" t="s">
+        <v>589</v>
+      </c>
+      <c r="C265">
+        <v>2</v>
+      </c>
+      <c r="D265" t="s">
+        <v>590</v>
+      </c>
+      <c r="F265" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" t="s">
+        <v>584</v>
+      </c>
+      <c r="B266" t="s">
+        <v>591</v>
+      </c>
+      <c r="C266">
+        <v>3</v>
+      </c>
+      <c r="D266" t="s">
+        <v>592</v>
+      </c>
+      <c r="E266" t="s">
+        <v>593</v>
+      </c>
+      <c r="G266" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" t="s">
+        <v>584</v>
+      </c>
+      <c r="B267" t="s">
+        <v>594</v>
+      </c>
+      <c r="C267">
+        <v>3</v>
+      </c>
+      <c r="D267" t="s">
+        <v>595</v>
+      </c>
+      <c r="F267" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" t="s">
+        <v>584</v>
+      </c>
+      <c r="B268" t="s">
+        <v>596</v>
+      </c>
+      <c r="C268">
+        <v>3</v>
+      </c>
+      <c r="D268" t="s">
+        <v>597</v>
+      </c>
+      <c r="F268" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" t="s">
+        <v>584</v>
+      </c>
+      <c r="B269" t="s">
+        <v>598</v>
+      </c>
+      <c r="C269">
+        <v>2</v>
+      </c>
+      <c r="D269" t="s">
+        <v>352</v>
+      </c>
+      <c r="F269" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" t="s">
+        <v>584</v>
+      </c>
+      <c r="B270" t="s">
+        <v>599</v>
+      </c>
+      <c r="C270">
+        <v>3</v>
+      </c>
+      <c r="D270" t="s">
+        <v>600</v>
+      </c>
+      <c r="F270" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" t="s">
+        <v>584</v>
+      </c>
+      <c r="B271" t="s">
+        <v>601</v>
+      </c>
+      <c r="C271">
+        <v>2</v>
+      </c>
+      <c r="D271" t="s">
+        <v>602</v>
+      </c>
+      <c r="F271" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" t="s">
+        <v>584</v>
+      </c>
+      <c r="B272" t="s">
+        <v>603</v>
+      </c>
+      <c r="C272">
+        <v>2</v>
+      </c>
+      <c r="D272" t="s">
+        <v>79</v>
+      </c>
+      <c r="F272" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" t="s">
+        <v>584</v>
+      </c>
+      <c r="B273" t="s">
+        <v>604</v>
+      </c>
+      <c r="C273">
+        <v>2</v>
+      </c>
+      <c r="D273" t="s">
+        <v>605</v>
+      </c>
+      <c r="F273" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" t="s">
+        <v>584</v>
+      </c>
+      <c r="B274" t="s">
+        <v>606</v>
+      </c>
+      <c r="C274">
+        <v>2</v>
+      </c>
+      <c r="D274" t="s">
+        <v>607</v>
+      </c>
+      <c r="F274" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" t="s">
+        <v>608</v>
+      </c>
+      <c r="B275" t="s">
+        <v>609</v>
+      </c>
+      <c r="C275">
+        <v>2</v>
+      </c>
+      <c r="D275" t="s">
+        <v>610</v>
+      </c>
+      <c r="E275" t="s">
+        <v>611</v>
+      </c>
+      <c r="G275" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" t="s">
+        <v>608</v>
+      </c>
+      <c r="B276" t="s">
+        <v>612</v>
+      </c>
+      <c r="C276">
+        <v>2</v>
+      </c>
+      <c r="D276" t="s">
+        <v>613</v>
+      </c>
+      <c r="F276" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" t="s">
+        <v>608</v>
+      </c>
+      <c r="B277" t="s">
+        <v>614</v>
+      </c>
+      <c r="C277">
+        <v>3</v>
+      </c>
+      <c r="D277" t="s">
+        <v>615</v>
+      </c>
+      <c r="E277" t="s">
+        <v>616</v>
+      </c>
+      <c r="G277" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" t="s">
+        <v>608</v>
+      </c>
+      <c r="B278" t="s">
+        <v>617</v>
+      </c>
+      <c r="C278">
+        <v>2</v>
+      </c>
+      <c r="D278" t="s">
+        <v>618</v>
+      </c>
+      <c r="E278" t="s">
+        <v>619</v>
+      </c>
+      <c r="G278" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" t="s">
+        <v>608</v>
+      </c>
+      <c r="B279" t="s">
+        <v>620</v>
+      </c>
+      <c r="C279">
+        <v>3</v>
+      </c>
+      <c r="D279" t="s">
+        <v>621</v>
+      </c>
+      <c r="E279" t="s">
+        <v>622</v>
+      </c>
+      <c r="G279" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" t="s">
+        <v>608</v>
+      </c>
+      <c r="B280" t="s">
+        <v>622</v>
+      </c>
+      <c r="C280">
+        <v>3</v>
+      </c>
+      <c r="D280" t="s">
+        <v>623</v>
+      </c>
+      <c r="F280" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" t="s">
+        <v>608</v>
+      </c>
+      <c r="B281" t="s">
+        <v>598</v>
+      </c>
+      <c r="C281">
+        <v>2</v>
+      </c>
+      <c r="D281" t="s">
+        <v>352</v>
+      </c>
+      <c r="F281" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" t="s">
+        <v>608</v>
+      </c>
+      <c r="B282" t="s">
+        <v>624</v>
+      </c>
+      <c r="C282">
+        <v>2</v>
+      </c>
+      <c r="D282" t="s">
+        <v>625</v>
+      </c>
+      <c r="E282" t="s">
+        <v>626</v>
+      </c>
+      <c r="G282" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" t="s">
+        <v>608</v>
+      </c>
+      <c r="B283" t="s">
+        <v>602</v>
+      </c>
+      <c r="C283">
+        <v>2</v>
+      </c>
+      <c r="D283" t="s">
+        <v>627</v>
+      </c>
+      <c r="E283" t="s">
+        <v>48</v>
+      </c>
+      <c r="G283" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" t="s">
+        <v>608</v>
+      </c>
+      <c r="B284" t="s">
+        <v>110</v>
+      </c>
+      <c r="C284">
+        <v>2</v>
+      </c>
+      <c r="D284" t="s">
+        <v>111</v>
+      </c>
+      <c r="F284" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" t="s">
+        <v>608</v>
+      </c>
+      <c r="B285" t="s">
+        <v>628</v>
+      </c>
+      <c r="C285">
+        <v>3</v>
+      </c>
+      <c r="D285" t="s">
+        <v>629</v>
+      </c>
+      <c r="F285" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" t="s">
+        <v>608</v>
+      </c>
+      <c r="B286" t="s">
+        <v>630</v>
+      </c>
+      <c r="C286">
+        <v>2</v>
+      </c>
+      <c r="D286" t="s">
+        <v>631</v>
+      </c>
+      <c r="F286" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" t="s">
+        <v>632</v>
+      </c>
+      <c r="B287" t="s">
+        <v>306</v>
+      </c>
+      <c r="C287">
+        <v>2</v>
+      </c>
+      <c r="D287" t="s">
+        <v>242</v>
+      </c>
+      <c r="E287" t="s">
+        <v>243</v>
+      </c>
+      <c r="G287" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" t="s">
+        <v>632</v>
+      </c>
+      <c r="B288" t="s">
+        <v>633</v>
+      </c>
+      <c r="C288">
+        <v>2</v>
+      </c>
+      <c r="D288" t="s">
+        <v>634</v>
+      </c>
+      <c r="E288" t="s">
+        <v>635</v>
+      </c>
+      <c r="G288" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
+      <c r="A289" t="s">
+        <v>632</v>
+      </c>
+      <c r="B289" t="s">
+        <v>636</v>
+      </c>
+      <c r="C289">
+        <v>2</v>
+      </c>
+      <c r="D289" t="s">
+        <v>637</v>
+      </c>
+      <c r="F289" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290" t="s">
+        <v>632</v>
+      </c>
+      <c r="B290" t="s">
+        <v>638</v>
+      </c>
+      <c r="C290">
+        <v>2</v>
+      </c>
+      <c r="D290" t="s">
+        <v>639</v>
+      </c>
+      <c r="F290" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" t="s">
+        <v>632</v>
+      </c>
+      <c r="B291" t="s">
+        <v>640</v>
+      </c>
+      <c r="C291">
+        <v>3</v>
+      </c>
+      <c r="D291" t="s">
+        <v>641</v>
+      </c>
+      <c r="F291" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" t="s">
+        <v>632</v>
+      </c>
+      <c r="B292" t="s">
+        <v>260</v>
+      </c>
+      <c r="C292">
+        <v>3</v>
+      </c>
+      <c r="D292" t="s">
+        <v>261</v>
+      </c>
+      <c r="E292" t="s">
+        <v>262</v>
+      </c>
+      <c r="G292" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293" t="s">
+        <v>632</v>
+      </c>
+      <c r="B293" t="s">
+        <v>573</v>
+      </c>
+      <c r="C293">
+        <v>2</v>
+      </c>
+      <c r="D293" t="s">
+        <v>574</v>
+      </c>
+      <c r="F293" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" t="s">
+        <v>632</v>
+      </c>
+      <c r="B294" t="s">
+        <v>575</v>
+      </c>
+      <c r="C294">
+        <v>2</v>
+      </c>
+      <c r="D294" t="s">
+        <v>576</v>
+      </c>
+      <c r="F294" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" t="s">
+        <v>632</v>
+      </c>
+      <c r="B295" t="s">
+        <v>642</v>
+      </c>
+      <c r="C295">
+        <v>2</v>
+      </c>
+      <c r="D295" t="s">
+        <v>643</v>
+      </c>
+      <c r="F295" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" t="s">
+        <v>632</v>
+      </c>
+      <c r="B296" t="s">
+        <v>644</v>
+      </c>
+      <c r="C296">
+        <v>3</v>
+      </c>
+      <c r="D296" t="s">
+        <v>264</v>
+      </c>
+      <c r="F296" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" t="s">
+        <v>632</v>
+      </c>
+      <c r="B297" t="s">
+        <v>44</v>
+      </c>
+      <c r="C297">
+        <v>2</v>
+      </c>
+      <c r="D297" t="s">
+        <v>372</v>
+      </c>
+      <c r="F297" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" t="s">
+        <v>632</v>
+      </c>
+      <c r="B298" t="s">
+        <v>47</v>
+      </c>
+      <c r="C298">
+        <v>2</v>
+      </c>
+      <c r="D298" t="s">
+        <v>429</v>
+      </c>
+      <c r="F298" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" t="s">
+        <v>645</v>
+      </c>
+      <c r="B299" t="s">
+        <v>646</v>
+      </c>
+      <c r="C299">
+        <v>2</v>
+      </c>
+      <c r="D299" t="s">
+        <v>647</v>
+      </c>
+      <c r="E299" t="s">
+        <v>648</v>
+      </c>
+      <c r="G299" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" t="s">
+        <v>645</v>
+      </c>
+      <c r="B300" t="s">
+        <v>243</v>
+      </c>
+      <c r="C300">
+        <v>2</v>
+      </c>
+      <c r="D300" t="s">
+        <v>649</v>
+      </c>
+      <c r="E300" t="s">
+        <v>650</v>
+      </c>
+      <c r="G300" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" t="s">
+        <v>645</v>
+      </c>
+      <c r="B301" t="s">
+        <v>651</v>
+      </c>
+      <c r="C301">
+        <v>3</v>
+      </c>
+      <c r="D301" t="s">
+        <v>652</v>
+      </c>
+      <c r="E301" t="s">
+        <v>653</v>
+      </c>
+      <c r="G301" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302" t="s">
+        <v>645</v>
+      </c>
+      <c r="B302" t="s">
+        <v>654</v>
+      </c>
+      <c r="C302">
+        <v>3</v>
+      </c>
+      <c r="D302" t="s">
+        <v>655</v>
+      </c>
+      <c r="F302" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" t="s">
+        <v>645</v>
+      </c>
+      <c r="B303" t="s">
+        <v>656</v>
+      </c>
+      <c r="C303">
+        <v>3</v>
+      </c>
+      <c r="D303" t="s">
+        <v>657</v>
+      </c>
+      <c r="F303" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304" t="s">
+        <v>645</v>
+      </c>
+      <c r="B304" t="s">
+        <v>658</v>
+      </c>
+      <c r="C304">
+        <v>3</v>
+      </c>
+      <c r="D304" t="s">
+        <v>659</v>
+      </c>
+      <c r="F304" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
+      <c r="A305" t="s">
+        <v>645</v>
+      </c>
+      <c r="B305" t="s">
+        <v>660</v>
+      </c>
+      <c r="C305">
+        <v>3</v>
+      </c>
+      <c r="D305" t="s">
+        <v>661</v>
+      </c>
+      <c r="F305" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7">
+      <c r="A306" t="s">
+        <v>645</v>
+      </c>
+      <c r="B306" t="s">
+        <v>662</v>
+      </c>
+      <c r="C306">
+        <v>3</v>
+      </c>
+      <c r="D306" t="s">
+        <v>663</v>
+      </c>
+      <c r="F306" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307" t="s">
+        <v>645</v>
+      </c>
+      <c r="B307" t="s">
+        <v>664</v>
+      </c>
+      <c r="C307">
+        <v>2</v>
+      </c>
+      <c r="D307" t="s">
+        <v>665</v>
+      </c>
+      <c r="F307" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7">
+      <c r="A308" t="s">
+        <v>645</v>
+      </c>
+      <c r="B308" t="s">
+        <v>666</v>
+      </c>
+      <c r="C308">
+        <v>2</v>
+      </c>
+      <c r="D308" t="s">
+        <v>667</v>
+      </c>
+      <c r="F308" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309" t="s">
+        <v>645</v>
+      </c>
+      <c r="B309" t="s">
+        <v>668</v>
+      </c>
+      <c r="C309">
+        <v>2</v>
+      </c>
+      <c r="D309" t="s">
+        <v>669</v>
+      </c>
+      <c r="F309" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310" t="s">
+        <v>645</v>
+      </c>
+      <c r="B310" t="s">
+        <v>670</v>
+      </c>
+      <c r="C310">
+        <v>2</v>
+      </c>
+      <c r="D310" t="s">
+        <v>120</v>
+      </c>
+      <c r="F310" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
+      <c r="A311" t="s">
+        <v>671</v>
+      </c>
+      <c r="B311" t="s">
+        <v>304</v>
+      </c>
+      <c r="C311">
+        <v>2</v>
+      </c>
+      <c r="D311" t="s">
+        <v>305</v>
+      </c>
+      <c r="E311" t="s">
+        <v>650</v>
+      </c>
+      <c r="G311" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312" t="s">
+        <v>671</v>
+      </c>
+      <c r="B312" t="s">
+        <v>672</v>
+      </c>
+      <c r="C312">
+        <v>2</v>
+      </c>
+      <c r="D312" t="s">
+        <v>673</v>
+      </c>
+      <c r="F312" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7">
+      <c r="A313" t="s">
+        <v>671</v>
+      </c>
+      <c r="B313" t="s">
+        <v>674</v>
+      </c>
+      <c r="C313">
+        <v>3</v>
+      </c>
+      <c r="D313" t="s">
+        <v>675</v>
+      </c>
+      <c r="F313" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314" t="s">
+        <v>671</v>
+      </c>
+      <c r="B314" t="s">
+        <v>57</v>
+      </c>
+      <c r="C314">
+        <v>2</v>
+      </c>
+      <c r="D314" t="s">
+        <v>676</v>
+      </c>
+      <c r="F314" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7">
+      <c r="A315" t="s">
+        <v>671</v>
+      </c>
+      <c r="B315" t="s">
+        <v>677</v>
+      </c>
+      <c r="C315">
+        <v>2</v>
+      </c>
+      <c r="D315" t="s">
+        <v>678</v>
+      </c>
+      <c r="F315" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7">
+      <c r="A316" t="s">
+        <v>671</v>
+      </c>
+      <c r="B316" t="s">
+        <v>296</v>
+      </c>
+      <c r="C316">
+        <v>3</v>
+      </c>
+      <c r="D316" t="s">
+        <v>679</v>
+      </c>
+      <c r="E316" t="s">
+        <v>680</v>
+      </c>
+      <c r="G316" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7">
+      <c r="A317" t="s">
+        <v>671</v>
+      </c>
+      <c r="B317" t="s">
+        <v>668</v>
+      </c>
+      <c r="C317">
+        <v>3</v>
+      </c>
+      <c r="D317" t="s">
+        <v>297</v>
+      </c>
+      <c r="F317" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7">
+      <c r="A318" t="s">
+        <v>671</v>
+      </c>
+      <c r="B318" t="s">
+        <v>282</v>
+      </c>
+      <c r="C318">
+        <v>3</v>
+      </c>
+      <c r="D318" t="s">
+        <v>681</v>
+      </c>
+      <c r="F318" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7">
+      <c r="A319" t="s">
+        <v>671</v>
+      </c>
+      <c r="B319" t="s">
+        <v>682</v>
+      </c>
+      <c r="C319">
+        <v>3</v>
+      </c>
+      <c r="D319" t="s">
+        <v>683</v>
+      </c>
+      <c r="E319" t="s">
+        <v>684</v>
+      </c>
+      <c r="G319" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7">
+      <c r="A320" t="s">
+        <v>671</v>
+      </c>
+      <c r="B320" t="s">
+        <v>685</v>
+      </c>
+      <c r="C320">
+        <v>2</v>
+      </c>
+      <c r="D320" t="s">
+        <v>686</v>
+      </c>
+      <c r="F320" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8">
+      <c r="A321" t="s">
+        <v>671</v>
+      </c>
+      <c r="B321" t="s">
+        <v>687</v>
+      </c>
+      <c r="C321">
+        <v>2</v>
+      </c>
+      <c r="D321" t="s">
+        <v>688</v>
+      </c>
+      <c r="F321" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8">
+      <c r="A322" t="s">
+        <v>671</v>
+      </c>
+      <c r="B322" t="s">
+        <v>689</v>
+      </c>
+      <c r="C322">
+        <v>3</v>
+      </c>
+      <c r="D322" t="s">
+        <v>690</v>
+      </c>
+      <c r="F322" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8">
+      <c r="A323" t="s">
+        <v>691</v>
+      </c>
+      <c r="B323" t="s">
+        <v>692</v>
+      </c>
+      <c r="C323">
+        <v>2</v>
+      </c>
+      <c r="D323" t="s">
+        <v>304</v>
+      </c>
+      <c r="E323" t="s">
+        <v>305</v>
+      </c>
+      <c r="G323" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8">
+      <c r="A324" t="s">
+        <v>691</v>
+      </c>
+      <c r="B324" t="s">
+        <v>693</v>
+      </c>
+      <c r="C324">
+        <v>3</v>
+      </c>
+      <c r="D324" t="s">
+        <v>694</v>
+      </c>
+      <c r="F324" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8">
+      <c r="A325" t="s">
+        <v>691</v>
+      </c>
+      <c r="B325" t="s">
+        <v>672</v>
+      </c>
+      <c r="C325">
+        <v>2</v>
+      </c>
+      <c r="D325" t="s">
+        <v>673</v>
+      </c>
+      <c r="F325" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8">
+      <c r="A326" t="s">
+        <v>691</v>
+      </c>
+      <c r="B326" t="s">
+        <v>695</v>
+      </c>
+      <c r="C326">
+        <v>3</v>
+      </c>
+      <c r="D326" t="s">
+        <v>696</v>
+      </c>
+      <c r="E326" t="s">
+        <v>697</v>
+      </c>
+      <c r="G326" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8">
+      <c r="A327" t="s">
+        <v>691</v>
+      </c>
+      <c r="B327" t="s">
+        <v>698</v>
+      </c>
+      <c r="C327">
+        <v>3</v>
+      </c>
+      <c r="D327" t="s">
+        <v>699</v>
+      </c>
+      <c r="E327" t="s">
+        <v>700</v>
+      </c>
+      <c r="F327" t="s">
+        <v>701</v>
+      </c>
+      <c r="H327" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8">
+      <c r="A328" t="s">
+        <v>691</v>
+      </c>
+      <c r="B328" t="s">
+        <v>702</v>
+      </c>
+      <c r="C328">
+        <v>3</v>
+      </c>
+      <c r="D328" t="s">
+        <v>703</v>
+      </c>
+      <c r="E328" t="s">
+        <v>704</v>
+      </c>
+      <c r="G328" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8">
+      <c r="A329" t="s">
+        <v>691</v>
+      </c>
+      <c r="B329" t="s">
+        <v>705</v>
+      </c>
+      <c r="C329">
+        <v>2</v>
+      </c>
+      <c r="D329" t="s">
+        <v>706</v>
+      </c>
+      <c r="F329" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8">
+      <c r="A330" t="s">
+        <v>691</v>
+      </c>
+      <c r="B330" t="s">
+        <v>707</v>
+      </c>
+      <c r="C330">
+        <v>2</v>
+      </c>
+      <c r="D330" t="s">
+        <v>708</v>
+      </c>
+      <c r="F330" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8">
+      <c r="A331" t="s">
+        <v>691</v>
+      </c>
+      <c r="B331" t="s">
+        <v>709</v>
+      </c>
+      <c r="C331">
+        <v>2</v>
+      </c>
+      <c r="D331" t="s">
+        <v>710</v>
+      </c>
+      <c r="F331" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8">
+      <c r="A332" t="s">
+        <v>691</v>
+      </c>
+      <c r="B332" t="s">
+        <v>711</v>
+      </c>
+      <c r="C332">
+        <v>2</v>
+      </c>
+      <c r="D332" t="s">
+        <v>712</v>
+      </c>
+      <c r="F332" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8">
+      <c r="A333" t="s">
+        <v>691</v>
+      </c>
+      <c r="B333" t="s">
+        <v>603</v>
+      </c>
+      <c r="C333">
+        <v>2</v>
+      </c>
+      <c r="D333" t="s">
+        <v>713</v>
+      </c>
+      <c r="F333" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8">
+      <c r="A334" t="s">
+        <v>691</v>
+      </c>
+      <c r="B334" t="s">
+        <v>714</v>
+      </c>
+      <c r="C334">
+        <v>3</v>
+      </c>
+      <c r="D334" t="s">
+        <v>715</v>
+      </c>
+      <c r="F334" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8">
+      <c r="A335" t="s">
+        <v>716</v>
+      </c>
+      <c r="B335" t="s">
+        <v>306</v>
+      </c>
+      <c r="C335">
+        <v>2</v>
+      </c>
+      <c r="D335" t="s">
+        <v>717</v>
+      </c>
+      <c r="E335" t="s">
+        <v>718</v>
+      </c>
+      <c r="G335" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8">
+      <c r="A336" t="s">
+        <v>716</v>
+      </c>
+      <c r="B336" t="s">
+        <v>304</v>
+      </c>
+      <c r="C336">
+        <v>2</v>
+      </c>
+      <c r="D336" t="s">
+        <v>305</v>
+      </c>
+      <c r="E336" t="s">
+        <v>719</v>
+      </c>
+      <c r="G336" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7">
+      <c r="A337" t="s">
+        <v>716</v>
+      </c>
+      <c r="B337" t="s">
+        <v>720</v>
+      </c>
+      <c r="C337">
+        <v>3</v>
+      </c>
+      <c r="D337" t="s">
+        <v>721</v>
+      </c>
+      <c r="E337" t="s">
+        <v>722</v>
+      </c>
+      <c r="G337" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7">
+      <c r="A338" t="s">
+        <v>716</v>
+      </c>
+      <c r="B338" t="s">
+        <v>723</v>
+      </c>
+      <c r="C338">
+        <v>3</v>
+      </c>
+      <c r="D338" t="s">
+        <v>724</v>
+      </c>
+      <c r="F338" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7">
+      <c r="A339" t="s">
+        <v>716</v>
+      </c>
+      <c r="B339" t="s">
+        <v>725</v>
+      </c>
+      <c r="C339">
+        <v>3</v>
+      </c>
+      <c r="D339" t="s">
+        <v>726</v>
+      </c>
+      <c r="F339" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7">
+      <c r="A340" t="s">
+        <v>716</v>
+      </c>
+      <c r="B340" t="s">
+        <v>727</v>
+      </c>
+      <c r="C340">
+        <v>2</v>
+      </c>
+      <c r="D340" t="s">
+        <v>728</v>
+      </c>
+      <c r="F340" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7">
+      <c r="A341" t="s">
+        <v>716</v>
+      </c>
+      <c r="B341" t="s">
+        <v>729</v>
+      </c>
+      <c r="C341">
+        <v>3</v>
+      </c>
+      <c r="D341" t="s">
+        <v>730</v>
+      </c>
+      <c r="F341" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7">
+      <c r="A342" t="s">
+        <v>716</v>
+      </c>
+      <c r="B342" t="s">
+        <v>731</v>
+      </c>
+      <c r="C342">
+        <v>2</v>
+      </c>
+      <c r="D342" t="s">
+        <v>732</v>
+      </c>
+      <c r="F342" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7">
+      <c r="A343" t="s">
+        <v>716</v>
+      </c>
+      <c r="B343" t="s">
+        <v>110</v>
+      </c>
+      <c r="C343">
+        <v>2</v>
+      </c>
+      <c r="D343" t="s">
+        <v>111</v>
+      </c>
+      <c r="F343" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7">
+      <c r="A344" t="s">
+        <v>716</v>
+      </c>
+      <c r="B344" t="s">
+        <v>733</v>
+      </c>
+      <c r="C344">
+        <v>2</v>
+      </c>
+      <c r="D344" t="s">
+        <v>734</v>
+      </c>
+      <c r="F344" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7">
+      <c r="A345" t="s">
+        <v>716</v>
+      </c>
+      <c r="B345" t="s">
+        <v>735</v>
+      </c>
+      <c r="C345">
+        <v>2</v>
+      </c>
+      <c r="D345" t="s">
+        <v>736</v>
+      </c>
+      <c r="F345" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7">
+      <c r="A346" t="s">
+        <v>716</v>
+      </c>
+      <c r="B346" t="s">
+        <v>737</v>
+      </c>
+      <c r="C346">
+        <v>2</v>
+      </c>
+      <c r="D346" t="s">
+        <v>738</v>
+      </c>
+      <c r="F346" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7">
+      <c r="A347" t="s">
+        <v>739</v>
+      </c>
+      <c r="B347" t="s">
+        <v>55</v>
+      </c>
+      <c r="C347">
+        <v>2</v>
+      </c>
+      <c r="D347" t="s">
+        <v>740</v>
+      </c>
+      <c r="E347" t="s">
+        <v>741</v>
+      </c>
+      <c r="G347" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7">
+      <c r="A348" t="s">
+        <v>739</v>
+      </c>
+      <c r="B348" t="s">
+        <v>742</v>
+      </c>
+      <c r="C348">
+        <v>2</v>
+      </c>
+      <c r="D348" t="s">
+        <v>743</v>
+      </c>
+      <c r="E348" t="s">
+        <v>744</v>
+      </c>
+      <c r="G348" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7">
+      <c r="A349" t="s">
+        <v>739</v>
+      </c>
+      <c r="B349" t="s">
+        <v>745</v>
+      </c>
+      <c r="C349">
+        <v>2</v>
+      </c>
+      <c r="D349" t="s">
+        <v>746</v>
+      </c>
+      <c r="F349" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7">
+      <c r="A350" t="s">
+        <v>739</v>
+      </c>
+      <c r="B350" t="s">
+        <v>747</v>
+      </c>
+      <c r="C350">
+        <v>3</v>
+      </c>
+      <c r="D350" t="s">
+        <v>748</v>
+      </c>
+      <c r="F350" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7">
+      <c r="A351" t="s">
+        <v>739</v>
+      </c>
+      <c r="B351" t="s">
+        <v>749</v>
+      </c>
+      <c r="C351">
+        <v>3</v>
+      </c>
+      <c r="D351" t="s">
+        <v>750</v>
+      </c>
+      <c r="E351" t="s">
+        <v>751</v>
+      </c>
+      <c r="G351" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7">
+      <c r="A352" t="s">
+        <v>739</v>
+      </c>
+      <c r="B352" t="s">
+        <v>752</v>
+      </c>
+      <c r="C352">
+        <v>2</v>
+      </c>
+      <c r="D352" t="s">
+        <v>753</v>
+      </c>
+      <c r="F352" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8">
+      <c r="A353" t="s">
+        <v>739</v>
+      </c>
+      <c r="B353" t="s">
+        <v>754</v>
+      </c>
+      <c r="C353">
+        <v>3</v>
+      </c>
+      <c r="D353" t="s">
+        <v>755</v>
+      </c>
+      <c r="F353" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8">
+      <c r="A354" t="s">
+        <v>739</v>
+      </c>
+      <c r="B354" t="s">
+        <v>337</v>
+      </c>
+      <c r="C354">
+        <v>3</v>
+      </c>
+      <c r="D354" t="s">
+        <v>338</v>
+      </c>
+      <c r="F354" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8">
+      <c r="A355" t="s">
+        <v>739</v>
+      </c>
+      <c r="B355" t="s">
+        <v>756</v>
+      </c>
+      <c r="C355">
+        <v>2</v>
+      </c>
+      <c r="D355" t="s">
+        <v>757</v>
+      </c>
+      <c r="F355" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8">
+      <c r="A356" t="s">
+        <v>739</v>
+      </c>
+      <c r="B356" t="s">
+        <v>559</v>
+      </c>
+      <c r="C356">
+        <v>2</v>
+      </c>
+      <c r="D356" t="s">
+        <v>560</v>
+      </c>
+      <c r="F356" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8">
+      <c r="A357" t="s">
+        <v>739</v>
+      </c>
+      <c r="B357" t="s">
+        <v>120</v>
+      </c>
+      <c r="C357">
+        <v>2</v>
+      </c>
+      <c r="D357" t="s">
+        <v>119</v>
+      </c>
+      <c r="F357" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8">
+      <c r="A358" t="s">
+        <v>739</v>
+      </c>
+      <c r="B358" t="s">
+        <v>758</v>
+      </c>
+      <c r="C358">
+        <v>2</v>
+      </c>
+      <c r="D358" t="s">
+        <v>759</v>
+      </c>
+      <c r="F358" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8">
+      <c r="A359" t="s">
+        <v>760</v>
+      </c>
+      <c r="B359" t="s">
+        <v>761</v>
+      </c>
+      <c r="C359">
+        <v>2</v>
+      </c>
+      <c r="D359" t="s">
+        <v>762</v>
+      </c>
+      <c r="F359" t="s">
+        <v>763</v>
+      </c>
+      <c r="H359" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8">
+      <c r="A360" t="s">
+        <v>760</v>
+      </c>
+      <c r="B360" t="s">
+        <v>85</v>
+      </c>
+      <c r="C360">
+        <v>2</v>
+      </c>
+      <c r="D360" t="s">
+        <v>764</v>
+      </c>
+      <c r="E360" t="s">
+        <v>765</v>
+      </c>
+      <c r="G360" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8">
+      <c r="A361" t="s">
+        <v>760</v>
+      </c>
+      <c r="B361" t="s">
+        <v>95</v>
+      </c>
+      <c r="C361">
+        <v>3</v>
+      </c>
+      <c r="D361" t="s">
+        <v>96</v>
+      </c>
+      <c r="E361" t="s">
+        <v>97</v>
+      </c>
+      <c r="G361" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8">
+      <c r="A362" t="s">
+        <v>760</v>
+      </c>
+      <c r="B362" t="s">
+        <v>114</v>
+      </c>
+      <c r="C362">
+        <v>3</v>
+      </c>
+      <c r="D362" t="s">
+        <v>112</v>
+      </c>
+      <c r="E362" t="s">
+        <v>766</v>
+      </c>
+      <c r="G362" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8">
+      <c r="A363" t="s">
+        <v>760</v>
+      </c>
+      <c r="B363" t="s">
+        <v>104</v>
+      </c>
+      <c r="C363">
+        <v>2</v>
+      </c>
+      <c r="D363" t="s">
+        <v>106</v>
+      </c>
+      <c r="E363" t="s">
+        <v>105</v>
+      </c>
+      <c r="F363" t="s">
+        <v>767</v>
+      </c>
+      <c r="G363" t="s">
+        <v>768</v>
+      </c>
+      <c r="H363" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8">
+      <c r="A364" t="s">
+        <v>760</v>
+      </c>
+      <c r="B364" t="s">
+        <v>98</v>
+      </c>
+      <c r="C364">
+        <v>2</v>
+      </c>
+      <c r="D364" t="s">
+        <v>99</v>
+      </c>
+      <c r="E364" t="s">
+        <v>769</v>
+      </c>
+      <c r="G364" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8">
+      <c r="A365" t="s">
+        <v>760</v>
+      </c>
+      <c r="B365" t="s">
+        <v>86</v>
+      </c>
+      <c r="C365">
+        <v>2</v>
+      </c>
+      <c r="D365" t="s">
+        <v>770</v>
+      </c>
+      <c r="F365" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8">
+      <c r="A366" t="s">
+        <v>760</v>
+      </c>
+      <c r="B366" t="s">
+        <v>372</v>
+      </c>
+      <c r="C366">
+        <v>2</v>
+      </c>
+      <c r="D366" t="s">
+        <v>44</v>
+      </c>
+      <c r="E366" t="s">
+        <v>427</v>
+      </c>
+      <c r="G366" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8">
+      <c r="A367" t="s">
+        <v>760</v>
+      </c>
+      <c r="B367" t="s">
+        <v>771</v>
+      </c>
+      <c r="C367">
+        <v>2</v>
+      </c>
+      <c r="D367" t="s">
+        <v>772</v>
+      </c>
+      <c r="F367" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8">
+      <c r="A368" t="s">
+        <v>760</v>
+      </c>
+      <c r="B368" t="s">
+        <v>773</v>
+      </c>
+      <c r="C368">
+        <v>3</v>
+      </c>
+      <c r="D368" t="s">
+        <v>774</v>
+      </c>
+      <c r="E368" t="s">
+        <v>775</v>
+      </c>
+      <c r="G368" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7">
+      <c r="A369" t="s">
+        <v>776</v>
+      </c>
+      <c r="B369" t="s">
+        <v>355</v>
+      </c>
+      <c r="C369">
+        <v>2</v>
+      </c>
+      <c r="D369" t="s">
+        <v>777</v>
+      </c>
+      <c r="E369" t="s">
+        <v>778</v>
+      </c>
+      <c r="G369" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7">
+      <c r="A370" t="s">
+        <v>776</v>
+      </c>
+      <c r="B370" t="s">
+        <v>779</v>
+      </c>
+      <c r="C370">
+        <v>3</v>
+      </c>
+      <c r="D370" t="s">
+        <v>780</v>
+      </c>
+      <c r="E370" t="s">
+        <v>781</v>
+      </c>
+      <c r="G370" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7">
+      <c r="A371" t="s">
+        <v>776</v>
+      </c>
+      <c r="B371" t="s">
+        <v>358</v>
+      </c>
+      <c r="C371">
+        <v>3</v>
+      </c>
+      <c r="D371" t="s">
+        <v>359</v>
+      </c>
+      <c r="F371" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7">
+      <c r="A372" t="s">
+        <v>776</v>
+      </c>
+      <c r="B372" t="s">
+        <v>782</v>
+      </c>
+      <c r="C372">
+        <v>3</v>
+      </c>
+      <c r="D372" t="s">
+        <v>783</v>
+      </c>
+      <c r="F372" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7">
+      <c r="A373" t="s">
+        <v>776</v>
+      </c>
+      <c r="B373" t="s">
+        <v>784</v>
+      </c>
+      <c r="C373">
+        <v>2</v>
+      </c>
+      <c r="D373" t="s">
+        <v>785</v>
+      </c>
+      <c r="E373" t="s">
+        <v>786</v>
+      </c>
+      <c r="G373" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7">
+      <c r="A374" t="s">
+        <v>776</v>
+      </c>
+      <c r="B374" t="s">
+        <v>365</v>
+      </c>
+      <c r="C374">
+        <v>3</v>
+      </c>
+      <c r="D374" t="s">
+        <v>366</v>
+      </c>
+      <c r="F374" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7">
+      <c r="A375" t="s">
+        <v>776</v>
+      </c>
+      <c r="B375" t="s">
+        <v>360</v>
+      </c>
+      <c r="C375">
+        <v>3</v>
+      </c>
+      <c r="D375" t="s">
+        <v>361</v>
+      </c>
+      <c r="F375" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7">
+      <c r="A376" t="s">
+        <v>776</v>
+      </c>
+      <c r="B376" t="s">
+        <v>367</v>
+      </c>
+      <c r="C376">
+        <v>3</v>
+      </c>
+      <c r="D376" t="s">
+        <v>368</v>
+      </c>
+      <c r="E376" t="s">
+        <v>369</v>
+      </c>
+      <c r="G376" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7">
+      <c r="A377" t="s">
+        <v>776</v>
+      </c>
+      <c r="B377" t="s">
+        <v>370</v>
+      </c>
+      <c r="C377">
+        <v>2</v>
+      </c>
+      <c r="D377" t="s">
+        <v>787</v>
+      </c>
+      <c r="F377" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7">
+      <c r="A378" t="s">
+        <v>776</v>
+      </c>
+      <c r="B378" t="s">
+        <v>788</v>
+      </c>
+      <c r="C378">
+        <v>2</v>
+      </c>
+      <c r="D378" t="s">
+        <v>789</v>
+      </c>
+      <c r="E378" t="s">
+        <v>790</v>
+      </c>
+      <c r="G378" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7">
+      <c r="A379" t="s">
+        <v>791</v>
+      </c>
+      <c r="B379" t="s">
+        <v>88</v>
+      </c>
+      <c r="C379">
+        <v>2</v>
+      </c>
+      <c r="D379" t="s">
+        <v>792</v>
+      </c>
+      <c r="E379" t="s">
+        <v>793</v>
+      </c>
+      <c r="G379" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7">
+      <c r="A380" t="s">
+        <v>791</v>
+      </c>
+      <c r="B380" t="s">
+        <v>794</v>
+      </c>
+      <c r="C380">
+        <v>2</v>
+      </c>
+      <c r="D380" t="s">
+        <v>795</v>
+      </c>
+      <c r="F380" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7">
+      <c r="A381" t="s">
+        <v>791</v>
+      </c>
+      <c r="B381" t="s">
+        <v>796</v>
+      </c>
+      <c r="C381">
+        <v>3</v>
+      </c>
+      <c r="D381" t="s">
+        <v>797</v>
+      </c>
+      <c r="E381" t="s">
+        <v>798</v>
+      </c>
+      <c r="G381" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7">
+      <c r="A382" t="s">
+        <v>791</v>
+      </c>
+      <c r="B382" t="s">
+        <v>799</v>
+      </c>
+      <c r="C382">
+        <v>3</v>
+      </c>
+      <c r="D382" t="s">
+        <v>800</v>
+      </c>
+      <c r="F382" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7">
+      <c r="A383" t="s">
+        <v>791</v>
+      </c>
+      <c r="B383" t="s">
+        <v>543</v>
+      </c>
+      <c r="C383">
+        <v>3</v>
+      </c>
+      <c r="D383" t="s">
+        <v>542</v>
+      </c>
+      <c r="F383" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7">
+      <c r="A384" t="s">
+        <v>791</v>
+      </c>
+      <c r="B384" t="s">
+        <v>801</v>
+      </c>
+      <c r="C384">
+        <v>3</v>
+      </c>
+      <c r="D384" t="s">
+        <v>802</v>
+      </c>
+      <c r="E384" t="s">
+        <v>803</v>
+      </c>
+      <c r="G384" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8">
+      <c r="A385" t="s">
+        <v>791</v>
+      </c>
+      <c r="B385" t="s">
+        <v>754</v>
+      </c>
+      <c r="C385">
+        <v>3</v>
+      </c>
+      <c r="D385" t="s">
+        <v>755</v>
+      </c>
+      <c r="E385" t="s">
+        <v>804</v>
+      </c>
+      <c r="G385" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8">
+      <c r="A386" t="s">
+        <v>791</v>
+      </c>
+      <c r="B386" t="s">
+        <v>805</v>
+      </c>
+      <c r="C386">
+        <v>3</v>
+      </c>
+      <c r="D386" t="s">
+        <v>806</v>
+      </c>
+      <c r="E386" t="s">
+        <v>807</v>
+      </c>
+      <c r="F386" t="s">
+        <v>808</v>
+      </c>
+      <c r="G386" t="s">
+        <v>809</v>
+      </c>
+      <c r="H386" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8">
+      <c r="A387" t="s">
+        <v>791</v>
+      </c>
+      <c r="B387" t="s">
+        <v>339</v>
+      </c>
+      <c r="C387">
+        <v>3</v>
+      </c>
+      <c r="D387" t="s">
+        <v>340</v>
+      </c>
+      <c r="F387" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8">
+      <c r="A388" t="s">
+        <v>791</v>
+      </c>
+      <c r="B388" t="s">
+        <v>120</v>
+      </c>
+      <c r="C388">
+        <v>2</v>
+      </c>
+      <c r="D388" t="s">
+        <v>179</v>
+      </c>
+      <c r="F388" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8">
+      <c r="A389" t="s">
+        <v>810</v>
+      </c>
+      <c r="B389" t="s">
+        <v>811</v>
+      </c>
+      <c r="C389">
+        <v>2</v>
+      </c>
+      <c r="D389" t="s">
+        <v>812</v>
+      </c>
+      <c r="E389" t="s">
+        <v>813</v>
+      </c>
+      <c r="G389" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8">
+      <c r="A390" t="s">
+        <v>810</v>
+      </c>
+      <c r="B390" t="s">
+        <v>814</v>
+      </c>
+      <c r="C390">
+        <v>3</v>
+      </c>
+      <c r="D390" t="s">
+        <v>815</v>
+      </c>
+      <c r="E390" t="s">
+        <v>816</v>
+      </c>
+      <c r="G390" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8">
+      <c r="A391" t="s">
+        <v>810</v>
+      </c>
+      <c r="B391" t="s">
+        <v>154</v>
+      </c>
+      <c r="C391">
+        <v>2</v>
+      </c>
+      <c r="D391" t="s">
+        <v>155</v>
+      </c>
+      <c r="E391" t="s">
+        <v>156</v>
+      </c>
+      <c r="G391" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8">
+      <c r="A392" t="s">
+        <v>810</v>
+      </c>
+      <c r="B392" t="s">
+        <v>817</v>
+      </c>
+      <c r="C392">
+        <v>3</v>
+      </c>
+      <c r="D392" t="s">
+        <v>818</v>
+      </c>
+      <c r="F392" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8">
+      <c r="A393" t="s">
+        <v>810</v>
+      </c>
+      <c r="B393" t="s">
+        <v>819</v>
+      </c>
+      <c r="C393">
+        <v>3</v>
+      </c>
+      <c r="D393" t="s">
+        <v>820</v>
+      </c>
+      <c r="F393" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8">
+      <c r="A394" t="s">
+        <v>810</v>
+      </c>
+      <c r="B394" t="s">
+        <v>821</v>
+      </c>
+      <c r="C394">
+        <v>2</v>
+      </c>
+      <c r="D394" t="s">
+        <v>822</v>
+      </c>
+      <c r="F394" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8">
+      <c r="A395" t="s">
+        <v>810</v>
+      </c>
+      <c r="B395" t="s">
+        <v>48</v>
+      </c>
+      <c r="C395">
+        <v>2</v>
+      </c>
+      <c r="D395" t="s">
+        <v>448</v>
+      </c>
+      <c r="E395" t="s">
+        <v>823</v>
+      </c>
+      <c r="G395" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8">
+      <c r="A396" t="s">
+        <v>810</v>
+      </c>
+      <c r="B396" t="s">
+        <v>824</v>
+      </c>
+      <c r="C396">
+        <v>2</v>
+      </c>
+      <c r="D396" t="s">
+        <v>825</v>
+      </c>
+      <c r="F396" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8">
+      <c r="A397" t="s">
+        <v>810</v>
+      </c>
+      <c r="B397" t="s">
+        <v>826</v>
+      </c>
+      <c r="C397">
+        <v>2</v>
+      </c>
+      <c r="D397" t="s">
+        <v>827</v>
+      </c>
+      <c r="F397" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8">
+      <c r="A398" t="s">
+        <v>810</v>
+      </c>
+      <c r="B398" t="s">
+        <v>828</v>
+      </c>
+      <c r="C398">
+        <v>2</v>
+      </c>
+      <c r="D398" t="s">
+        <v>829</v>
+      </c>
+      <c r="E398" t="s">
+        <v>830</v>
+      </c>
+      <c r="G398" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8">
+      <c r="A399" t="s">
+        <v>831</v>
+      </c>
+      <c r="B399" t="s">
+        <v>453</v>
+      </c>
+      <c r="C399">
+        <v>2</v>
+      </c>
+      <c r="D399" t="s">
+        <v>454</v>
+      </c>
+      <c r="E399" t="s">
+        <v>455</v>
+      </c>
+      <c r="G399" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8">
+      <c r="A400" t="s">
+        <v>831</v>
+      </c>
+      <c r="B400" t="s">
+        <v>157</v>
+      </c>
+      <c r="C400">
+        <v>3</v>
+      </c>
+      <c r="D400" t="s">
+        <v>158</v>
+      </c>
+      <c r="E400" t="s">
+        <v>832</v>
+      </c>
+      <c r="G400" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7">
+      <c r="A401" t="s">
+        <v>831</v>
+      </c>
+      <c r="B401" t="s">
+        <v>154</v>
+      </c>
+      <c r="C401">
+        <v>2</v>
+      </c>
+      <c r="D401" t="s">
+        <v>155</v>
+      </c>
+      <c r="F401" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7">
+      <c r="A402" t="s">
+        <v>831</v>
+      </c>
+      <c r="B402" t="s">
+        <v>9</v>
+      </c>
+      <c r="C402">
+        <v>2</v>
+      </c>
+      <c r="D402" t="s">
+        <v>479</v>
+      </c>
+      <c r="F402" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7">
+      <c r="A403" t="s">
+        <v>831</v>
+      </c>
+      <c r="B403" t="s">
+        <v>833</v>
+      </c>
+      <c r="C403">
+        <v>3</v>
+      </c>
+      <c r="D403" t="s">
+        <v>834</v>
+      </c>
+      <c r="E403" t="s">
+        <v>835</v>
+      </c>
+      <c r="G403" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7">
+      <c r="A404" t="s">
+        <v>831</v>
+      </c>
+      <c r="B404" t="s">
+        <v>836</v>
+      </c>
+      <c r="C404">
+        <v>3</v>
+      </c>
+      <c r="D404" t="s">
+        <v>837</v>
+      </c>
+      <c r="F404" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7">
+      <c r="A405" t="s">
+        <v>831</v>
+      </c>
+      <c r="B405" t="s">
+        <v>296</v>
+      </c>
+      <c r="C405">
+        <v>3</v>
+      </c>
+      <c r="D405" t="s">
+        <v>679</v>
+      </c>
+      <c r="F405" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7">
+      <c r="A406" t="s">
+        <v>831</v>
+      </c>
+      <c r="B406" t="s">
+        <v>162</v>
+      </c>
+      <c r="C406">
+        <v>3</v>
+      </c>
+      <c r="D406" t="s">
+        <v>163</v>
+      </c>
+      <c r="F406" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7">
+      <c r="A407" t="s">
+        <v>831</v>
+      </c>
+      <c r="B407" t="s">
+        <v>838</v>
+      </c>
+      <c r="C407">
+        <v>2</v>
+      </c>
+      <c r="D407" t="s">
+        <v>480</v>
+      </c>
+      <c r="E407" t="s">
+        <v>839</v>
+      </c>
+      <c r="G407" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7">
+      <c r="A408" t="s">
+        <v>831</v>
+      </c>
+      <c r="B408" t="s">
+        <v>840</v>
+      </c>
+      <c r="C408">
+        <v>2</v>
+      </c>
+      <c r="D408" t="s">
+        <v>496</v>
+      </c>
+      <c r="E408" t="s">
+        <v>498</v>
+      </c>
+      <c r="G408" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7">
+      <c r="A409" t="s">
+        <v>841</v>
+      </c>
+      <c r="B409" t="s">
+        <v>842</v>
+      </c>
+      <c r="C409">
+        <v>2</v>
+      </c>
+      <c r="D409" t="s">
+        <v>843</v>
+      </c>
+      <c r="F409" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7">
+      <c r="A410" t="s">
+        <v>841</v>
+      </c>
+      <c r="B410" t="s">
+        <v>50</v>
+      </c>
+      <c r="C410">
+        <v>2</v>
+      </c>
+      <c r="D410" t="s">
+        <v>53</v>
+      </c>
+      <c r="F410" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7">
+      <c r="A411" t="s">
+        <v>841</v>
+      </c>
+      <c r="B411" t="s">
+        <v>844</v>
+      </c>
+      <c r="C411">
+        <v>2</v>
+      </c>
+      <c r="D411" t="s">
+        <v>845</v>
+      </c>
+      <c r="F411" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7">
+      <c r="A412" t="s">
+        <v>841</v>
+      </c>
+      <c r="B412" t="s">
+        <v>846</v>
+      </c>
+      <c r="C412">
+        <v>3</v>
+      </c>
+      <c r="D412" t="s">
+        <v>847</v>
+      </c>
+      <c r="F412" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7">
+      <c r="A413" t="s">
+        <v>841</v>
+      </c>
+      <c r="B413" t="s">
+        <v>848</v>
+      </c>
+      <c r="C413">
+        <v>3</v>
+      </c>
+      <c r="D413" t="s">
+        <v>849</v>
+      </c>
+      <c r="F413" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7">
+      <c r="A414" t="s">
+        <v>841</v>
+      </c>
+      <c r="B414" t="s">
+        <v>76</v>
+      </c>
+      <c r="C414">
+        <v>2</v>
+      </c>
+      <c r="D414" t="s">
+        <v>850</v>
+      </c>
+      <c r="F414" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7">
+      <c r="A415" t="s">
+        <v>841</v>
+      </c>
+      <c r="B415" t="s">
+        <v>851</v>
+      </c>
+      <c r="C415">
+        <v>2</v>
+      </c>
+      <c r="D415" t="s">
+        <v>852</v>
+      </c>
+      <c r="F415" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7">
+      <c r="A416" t="s">
+        <v>841</v>
+      </c>
+      <c r="B416" t="s">
+        <v>814</v>
+      </c>
+      <c r="C416">
+        <v>3</v>
+      </c>
+      <c r="D416" t="s">
+        <v>815</v>
+      </c>
+      <c r="F416" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7">
+      <c r="A417" t="s">
+        <v>841</v>
+      </c>
+      <c r="B417" t="s">
+        <v>853</v>
+      </c>
+      <c r="C417">
+        <v>3</v>
+      </c>
+      <c r="D417" t="s">
+        <v>826</v>
+      </c>
+      <c r="F417" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7">
+      <c r="A418" t="s">
+        <v>841</v>
+      </c>
+      <c r="B418" t="s">
+        <v>48</v>
+      </c>
+      <c r="C418">
+        <v>2</v>
+      </c>
+      <c r="D418" t="s">
+        <v>448</v>
+      </c>
+      <c r="E418" t="s">
+        <v>854</v>
+      </c>
+      <c r="G418" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7">
+      <c r="A419" t="s">
+        <v>855</v>
+      </c>
+      <c r="B419" t="s">
+        <v>856</v>
+      </c>
+      <c r="C419">
+        <v>3</v>
+      </c>
+      <c r="D419" t="s">
+        <v>857</v>
+      </c>
+      <c r="F419" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7">
+      <c r="A420" t="s">
+        <v>855</v>
+      </c>
+      <c r="B420" t="s">
+        <v>858</v>
+      </c>
+      <c r="C420">
+        <v>2</v>
+      </c>
+      <c r="D420" t="s">
+        <v>859</v>
+      </c>
+      <c r="F420" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7">
+      <c r="A421" t="s">
+        <v>855</v>
+      </c>
+      <c r="B421" t="s">
+        <v>860</v>
+      </c>
+      <c r="C421">
+        <v>3</v>
+      </c>
+      <c r="D421" t="s">
+        <v>861</v>
+      </c>
+      <c r="F421" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7">
+      <c r="A422" t="s">
+        <v>855</v>
+      </c>
+      <c r="B422" t="s">
+        <v>862</v>
+      </c>
+      <c r="C422">
+        <v>3</v>
+      </c>
+      <c r="D422" t="s">
+        <v>863</v>
+      </c>
+      <c r="F422" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7">
+      <c r="A423" t="s">
+        <v>855</v>
+      </c>
+      <c r="B423" t="s">
+        <v>864</v>
+      </c>
+      <c r="C423">
+        <v>3</v>
+      </c>
+      <c r="D423" t="s">
+        <v>865</v>
+      </c>
+      <c r="F423" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7">
+      <c r="A424" t="s">
+        <v>855</v>
+      </c>
+      <c r="B424" t="s">
+        <v>866</v>
+      </c>
+      <c r="C424">
+        <v>2</v>
+      </c>
+      <c r="D424" t="s">
+        <v>867</v>
+      </c>
+      <c r="F424" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7">
+      <c r="A425" t="s">
+        <v>855</v>
+      </c>
+      <c r="B425" t="s">
+        <v>868</v>
+      </c>
+      <c r="C425">
+        <v>2</v>
+      </c>
+      <c r="D425" t="s">
+        <v>869</v>
+      </c>
+      <c r="F425" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7">
+      <c r="A426" t="s">
+        <v>855</v>
+      </c>
+      <c r="B426" t="s">
+        <v>208</v>
+      </c>
+      <c r="C426">
+        <v>2</v>
+      </c>
+      <c r="D426" t="s">
+        <v>234</v>
+      </c>
+      <c r="F426" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7">
+      <c r="A427" t="s">
+        <v>855</v>
+      </c>
+      <c r="B427" t="s">
+        <v>870</v>
+      </c>
+      <c r="C427">
+        <v>2</v>
+      </c>
+      <c r="D427" t="s">
+        <v>871</v>
+      </c>
+      <c r="F427" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7">
+      <c r="A428" t="s">
+        <v>855</v>
+      </c>
+      <c r="B428" t="s">
+        <v>872</v>
+      </c>
+      <c r="C428">
+        <v>2</v>
+      </c>
+      <c r="D428" t="s">
+        <v>873</v>
+      </c>
+      <c r="F428" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7">
+      <c r="A429" t="s">
+        <v>874</v>
+      </c>
+      <c r="B429" t="s">
+        <v>875</v>
+      </c>
+      <c r="C429">
+        <v>3</v>
+      </c>
+      <c r="D429" t="s">
+        <v>876</v>
+      </c>
+      <c r="E429" t="s">
+        <v>877</v>
+      </c>
+      <c r="G429" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7">
+      <c r="A430" t="s">
+        <v>874</v>
+      </c>
+      <c r="B430" t="s">
+        <v>878</v>
+      </c>
+      <c r="C430">
+        <v>2</v>
+      </c>
+      <c r="D430" t="s">
+        <v>879</v>
+      </c>
+      <c r="E430" t="s">
+        <v>880</v>
+      </c>
+      <c r="G430" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7">
+      <c r="A431" t="s">
+        <v>874</v>
+      </c>
+      <c r="B431" t="s">
+        <v>881</v>
+      </c>
+      <c r="C431">
+        <v>2</v>
+      </c>
+      <c r="D431" t="s">
+        <v>882</v>
+      </c>
+      <c r="F431" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7">
+      <c r="A432" t="s">
+        <v>874</v>
+      </c>
+      <c r="B432" t="s">
+        <v>883</v>
+      </c>
+      <c r="C432">
+        <v>2</v>
+      </c>
+      <c r="D432" t="s">
+        <v>884</v>
+      </c>
+      <c r="F432" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7">
+      <c r="A433" t="s">
+        <v>874</v>
+      </c>
+      <c r="B433" t="s">
+        <v>885</v>
+      </c>
+      <c r="C433">
+        <v>3</v>
+      </c>
+      <c r="D433" t="s">
+        <v>886</v>
+      </c>
+      <c r="E433" t="s">
+        <v>887</v>
+      </c>
+      <c r="G433" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7">
+      <c r="A434" t="s">
+        <v>874</v>
+      </c>
+      <c r="B434" t="s">
+        <v>888</v>
+      </c>
+      <c r="C434">
+        <v>3</v>
+      </c>
+      <c r="D434" t="s">
+        <v>889</v>
+      </c>
+      <c r="F434" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7">
+      <c r="A435" t="s">
+        <v>874</v>
+      </c>
+      <c r="B435" t="s">
+        <v>535</v>
+      </c>
+      <c r="C435">
+        <v>2</v>
+      </c>
+      <c r="D435" t="s">
+        <v>208</v>
+      </c>
+      <c r="F435" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7">
+      <c r="A436" t="s">
+        <v>874</v>
+      </c>
+      <c r="B436" t="s">
+        <v>890</v>
+      </c>
+      <c r="C436">
+        <v>2</v>
+      </c>
+      <c r="D436" t="s">
+        <v>891</v>
+      </c>
+      <c r="F436" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7">
+      <c r="A437" t="s">
+        <v>874</v>
+      </c>
+      <c r="B437" t="s">
+        <v>892</v>
+      </c>
+      <c r="C437">
+        <v>2</v>
+      </c>
+      <c r="D437" t="s">
+        <v>893</v>
+      </c>
+      <c r="F437" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7">
+      <c r="A438" t="s">
+        <v>874</v>
+      </c>
+      <c r="B438" t="s">
+        <v>894</v>
+      </c>
+      <c r="C438">
+        <v>2</v>
+      </c>
+      <c r="D438" t="s">
+        <v>895</v>
+      </c>
+      <c r="F438" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7">
+      <c r="A439" t="s">
+        <v>896</v>
+      </c>
+      <c r="B439" t="s">
+        <v>897</v>
+      </c>
+      <c r="C439">
+        <v>3</v>
+      </c>
+      <c r="D439" t="s">
+        <v>898</v>
+      </c>
+      <c r="E439" t="s">
+        <v>899</v>
+      </c>
+      <c r="G439" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7">
+      <c r="A440" t="s">
+        <v>896</v>
+      </c>
+      <c r="B440" t="s">
+        <v>900</v>
+      </c>
+      <c r="C440">
+        <v>2</v>
+      </c>
+      <c r="D440" t="s">
+        <v>901</v>
+      </c>
+      <c r="F440" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7">
+      <c r="A441" t="s">
+        <v>896</v>
+      </c>
+      <c r="B441" t="s">
+        <v>902</v>
+      </c>
+      <c r="C441">
+        <v>2</v>
+      </c>
+      <c r="D441" t="s">
+        <v>903</v>
+      </c>
+      <c r="F441" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7">
+      <c r="A442" t="s">
+        <v>896</v>
+      </c>
+      <c r="B442" t="s">
+        <v>904</v>
+      </c>
+      <c r="C442">
+        <v>3</v>
+      </c>
+      <c r="D442" t="s">
+        <v>905</v>
+      </c>
+      <c r="F442" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7">
+      <c r="A443" t="s">
+        <v>896</v>
+      </c>
+      <c r="B443" t="s">
+        <v>906</v>
+      </c>
+      <c r="C443">
+        <v>3</v>
+      </c>
+      <c r="D443" t="s">
+        <v>907</v>
+      </c>
+      <c r="F443" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7">
+      <c r="A444" t="s">
+        <v>896</v>
+      </c>
+      <c r="B444" t="s">
+        <v>908</v>
+      </c>
+      <c r="C444">
+        <v>3</v>
+      </c>
+      <c r="D444" t="s">
+        <v>909</v>
+      </c>
+      <c r="E444" t="s">
+        <v>910</v>
+      </c>
+      <c r="G444" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7">
+      <c r="A445" t="s">
+        <v>896</v>
+      </c>
+      <c r="B445" t="s">
+        <v>911</v>
+      </c>
+      <c r="C445">
+        <v>3</v>
+      </c>
+      <c r="D445" t="s">
+        <v>912</v>
+      </c>
+      <c r="F445" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7">
+      <c r="A446" t="s">
+        <v>896</v>
+      </c>
+      <c r="B446" t="s">
+        <v>913</v>
+      </c>
+      <c r="C446">
+        <v>2</v>
+      </c>
+      <c r="D446" t="s">
+        <v>914</v>
+      </c>
+      <c r="F446" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7">
+      <c r="A447" t="s">
+        <v>896</v>
+      </c>
+      <c r="B447" t="s">
+        <v>915</v>
+      </c>
+      <c r="C447">
+        <v>2</v>
+      </c>
+      <c r="D447" t="s">
+        <v>916</v>
+      </c>
+      <c r="F447" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7">
+      <c r="A448" t="s">
+        <v>896</v>
+      </c>
+      <c r="B448" t="s">
+        <v>48</v>
+      </c>
+      <c r="C448">
+        <v>2</v>
+      </c>
+      <c r="D448" t="s">
+        <v>917</v>
+      </c>
+      <c r="E448" t="s">
+        <v>918</v>
+      </c>
+      <c r="G448" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7">
+      <c r="A449" t="s">
+        <v>919</v>
+      </c>
+      <c r="B449" t="s">
+        <v>920</v>
+      </c>
+      <c r="C449">
+        <v>2</v>
+      </c>
+      <c r="D449" t="s">
+        <v>921</v>
+      </c>
+      <c r="E449" t="s">
+        <v>407</v>
+      </c>
+      <c r="G449" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7">
+      <c r="A450" t="s">
+        <v>919</v>
+      </c>
+      <c r="B450" t="s">
+        <v>922</v>
+      </c>
+      <c r="C450">
+        <v>2</v>
+      </c>
+      <c r="D450" t="s">
+        <v>923</v>
+      </c>
+      <c r="F450" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7">
+      <c r="A451" t="s">
+        <v>919</v>
+      </c>
+      <c r="B451" t="s">
+        <v>924</v>
+      </c>
+      <c r="C451">
+        <v>2</v>
+      </c>
+      <c r="D451" t="s">
+        <v>925</v>
+      </c>
+      <c r="F451" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7">
+      <c r="A452" t="s">
+        <v>919</v>
+      </c>
+      <c r="B452" t="s">
+        <v>419</v>
+      </c>
+      <c r="C452">
+        <v>3</v>
+      </c>
+      <c r="D452" t="s">
+        <v>420</v>
+      </c>
+      <c r="F452" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7">
+      <c r="A453" t="s">
+        <v>919</v>
+      </c>
+      <c r="B453" t="s">
+        <v>926</v>
+      </c>
+      <c r="C453">
+        <v>3</v>
+      </c>
+      <c r="D453" t="s">
+        <v>927</v>
+      </c>
+      <c r="F453" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7">
+      <c r="A454" t="s">
+        <v>919</v>
+      </c>
+      <c r="B454" t="s">
+        <v>417</v>
+      </c>
+      <c r="C454">
+        <v>3</v>
+      </c>
+      <c r="D454" t="s">
+        <v>418</v>
+      </c>
+      <c r="F454" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7">
+      <c r="A455" t="s">
+        <v>919</v>
+      </c>
+      <c r="B455" t="s">
+        <v>598</v>
+      </c>
+      <c r="C455">
+        <v>2</v>
+      </c>
+      <c r="D455" t="s">
+        <v>928</v>
+      </c>
+      <c r="F455" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7">
+      <c r="A456" t="s">
+        <v>919</v>
+      </c>
+      <c r="B456" t="s">
+        <v>176</v>
+      </c>
+      <c r="C456">
+        <v>2</v>
+      </c>
+      <c r="D456" t="s">
+        <v>929</v>
+      </c>
+      <c r="F456" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7">
+      <c r="A457" t="s">
+        <v>919</v>
+      </c>
+      <c r="B457" t="s">
+        <v>427</v>
+      </c>
+      <c r="C457">
+        <v>2</v>
+      </c>
+      <c r="D457" t="s">
+        <v>429</v>
+      </c>
+      <c r="F457" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7">
+      <c r="A458" t="s">
+        <v>919</v>
+      </c>
+      <c r="B458" t="s">
+        <v>930</v>
+      </c>
+      <c r="C458">
+        <v>2</v>
+      </c>
+      <c r="D458" t="s">
+        <v>931</v>
+      </c>
+      <c r="F458" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7">
+      <c r="A459" t="s">
+        <v>932</v>
+      </c>
+      <c r="B459" t="s">
+        <v>933</v>
+      </c>
+      <c r="C459">
+        <v>2</v>
+      </c>
+      <c r="D459" t="s">
+        <v>646</v>
+      </c>
+      <c r="E459" t="s">
+        <v>934</v>
+      </c>
+      <c r="G459" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7">
+      <c r="A460" t="s">
+        <v>932</v>
+      </c>
+      <c r="B460" t="s">
+        <v>935</v>
+      </c>
+      <c r="C460">
+        <v>2</v>
+      </c>
+      <c r="D460" t="s">
+        <v>936</v>
+      </c>
+      <c r="F460" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7">
+      <c r="A461" t="s">
+        <v>932</v>
+      </c>
+      <c r="B461" t="s">
+        <v>937</v>
+      </c>
+      <c r="C461">
+        <v>2</v>
+      </c>
+      <c r="D461" t="s">
+        <v>938</v>
+      </c>
+      <c r="F461" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7">
+      <c r="A462" t="s">
+        <v>932</v>
+      </c>
+      <c r="B462" t="s">
+        <v>939</v>
+      </c>
+      <c r="C462">
+        <v>3</v>
+      </c>
+      <c r="D462" t="s">
+        <v>940</v>
+      </c>
+      <c r="F462" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7">
+      <c r="A463" t="s">
+        <v>932</v>
+      </c>
+      <c r="B463" t="s">
+        <v>941</v>
+      </c>
+      <c r="C463">
+        <v>3</v>
+      </c>
+      <c r="D463" t="s">
+        <v>942</v>
+      </c>
+      <c r="F463" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7">
+      <c r="A464" t="s">
+        <v>932</v>
+      </c>
+      <c r="B464" t="s">
+        <v>943</v>
+      </c>
+      <c r="C464">
+        <v>3</v>
+      </c>
+      <c r="D464" t="s">
+        <v>944</v>
+      </c>
+      <c r="F464" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7">
+      <c r="A465" t="s">
+        <v>932</v>
+      </c>
+      <c r="B465" t="s">
+        <v>945</v>
+      </c>
+      <c r="C465">
+        <v>3</v>
+      </c>
+      <c r="D465" t="s">
+        <v>946</v>
+      </c>
+      <c r="F465" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7">
+      <c r="A466" t="s">
+        <v>932</v>
+      </c>
+      <c r="B466" t="s">
+        <v>947</v>
+      </c>
+      <c r="C466">
+        <v>3</v>
+      </c>
+      <c r="D466" t="s">
+        <v>948</v>
+      </c>
+      <c r="F466" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7">
+      <c r="A467" t="s">
+        <v>932</v>
+      </c>
+      <c r="B467" t="s">
+        <v>949</v>
+      </c>
+      <c r="C467">
+        <v>3</v>
+      </c>
+      <c r="D467" t="s">
+        <v>950</v>
+      </c>
+      <c r="F467" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7">
+      <c r="A468" t="s">
+        <v>932</v>
+      </c>
+      <c r="B468" t="s">
+        <v>951</v>
+      </c>
+      <c r="C468">
+        <v>3</v>
+      </c>
+      <c r="D468" t="s">
+        <v>952</v>
+      </c>
+      <c r="F468" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7">
+      <c r="A469" t="s">
+        <v>953</v>
+      </c>
+      <c r="B469" t="s">
+        <v>954</v>
+      </c>
+      <c r="C469">
+        <v>2</v>
+      </c>
+      <c r="D469" t="s">
+        <v>955</v>
+      </c>
+      <c r="F469" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7">
+      <c r="A470" t="s">
+        <v>953</v>
+      </c>
+      <c r="B470" t="s">
+        <v>956</v>
+      </c>
+      <c r="C470">
+        <v>2</v>
+      </c>
+      <c r="D470" t="s">
+        <v>957</v>
+      </c>
+      <c r="F470" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7">
+      <c r="A471" t="s">
+        <v>953</v>
+      </c>
+      <c r="B471" t="s">
+        <v>413</v>
+      </c>
+      <c r="C471">
+        <v>2</v>
+      </c>
+      <c r="D471" t="s">
+        <v>414</v>
+      </c>
+      <c r="E471" t="s">
+        <v>958</v>
+      </c>
+      <c r="G471" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7">
+      <c r="A472" t="s">
+        <v>953</v>
+      </c>
+      <c r="B472" t="s">
+        <v>959</v>
+      </c>
+      <c r="C472">
+        <v>3</v>
+      </c>
+      <c r="D472" t="s">
+        <v>960</v>
+      </c>
+      <c r="F472" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7">
+      <c r="A473" t="s">
+        <v>953</v>
+      </c>
+      <c r="B473" t="s">
+        <v>961</v>
+      </c>
+      <c r="C473">
+        <v>3</v>
+      </c>
+      <c r="D473" t="s">
+        <v>962</v>
+      </c>
+      <c r="F473" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7">
+      <c r="A474" t="s">
+        <v>953</v>
+      </c>
+      <c r="B474" t="s">
+        <v>963</v>
+      </c>
+      <c r="C474">
+        <v>3</v>
+      </c>
+      <c r="D474" t="s">
+        <v>964</v>
+      </c>
+      <c r="E474" t="s">
+        <v>965</v>
+      </c>
+      <c r="G474" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7">
+      <c r="A475" t="s">
+        <v>953</v>
+      </c>
+      <c r="B475" t="s">
+        <v>417</v>
+      </c>
+      <c r="C475">
+        <v>3</v>
+      </c>
+      <c r="D475" t="s">
+        <v>418</v>
+      </c>
+      <c r="F475" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7">
+      <c r="A476" t="s">
+        <v>953</v>
+      </c>
+      <c r="B476" t="s">
+        <v>966</v>
+      </c>
+      <c r="C476">
+        <v>3</v>
+      </c>
+      <c r="D476" t="s">
+        <v>967</v>
+      </c>
+      <c r="F476" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7">
+      <c r="A477" t="s">
+        <v>953</v>
+      </c>
+      <c r="B477" t="s">
+        <v>968</v>
+      </c>
+      <c r="C477">
+        <v>3</v>
+      </c>
+      <c r="D477" t="s">
+        <v>969</v>
+      </c>
+      <c r="F477" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7">
+      <c r="A478" t="s">
+        <v>953</v>
+      </c>
+      <c r="B478" t="s">
+        <v>970</v>
+      </c>
+      <c r="C478">
+        <v>3</v>
+      </c>
+      <c r="D478" t="s">
+        <v>971</v>
+      </c>
+      <c r="F478" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/data/简答题评分.xlsx
+++ b/data/简答题评分.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2153" uniqueCount="972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2103" uniqueCount="971">
   <si>
     <t>疾病</t>
   </si>
@@ -1718,7 +1718,7 @@
     <t>骨保护剂</t>
   </si>
   <si>
-    <t>“脑中风的警报”</t>
+    <t>“半身风云”</t>
   </si>
   <si>
     <t>偏瘫</t>
@@ -1776,9 +1776,6 @@
   </si>
   <si>
     <t>动脉硬化</t>
-  </si>
-  <si>
-    <t>“半身风云”</t>
   </si>
   <si>
     <t>“惊厥之舞”</t>
@@ -3907,7 +3904,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H478"/>
+  <dimension ref="A1:H466"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -8633,16 +8630,16 @@
         <v>583</v>
       </c>
       <c r="B251" t="s">
-        <v>564</v>
+        <v>584</v>
       </c>
       <c r="C251">
         <v>2</v>
       </c>
       <c r="D251" t="s">
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="E251" t="s">
-        <v>566</v>
+        <v>586</v>
       </c>
       <c r="G251" t="s">
         <v>54</v>
@@ -8653,15 +8650,18 @@
         <v>583</v>
       </c>
       <c r="B252" t="s">
-        <v>567</v>
+        <v>244</v>
       </c>
       <c r="C252">
         <v>2</v>
       </c>
       <c r="D252" t="s">
-        <v>34</v>
-      </c>
-      <c r="F252" t="s">
+        <v>587</v>
+      </c>
+      <c r="E252" t="s">
+        <v>245</v>
+      </c>
+      <c r="G252" t="s">
         <v>54</v>
       </c>
     </row>
@@ -8670,19 +8670,16 @@
         <v>583</v>
       </c>
       <c r="B253" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="C253">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D253" t="s">
-        <v>569</v>
-      </c>
-      <c r="E253" t="s">
-        <v>570</v>
-      </c>
-      <c r="G253" t="s">
-        <v>118</v>
+        <v>589</v>
+      </c>
+      <c r="F253" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -8690,16 +8687,19 @@
         <v>583</v>
       </c>
       <c r="B254" t="s">
-        <v>571</v>
+        <v>590</v>
       </c>
       <c r="C254">
         <v>3</v>
       </c>
       <c r="D254" t="s">
-        <v>572</v>
-      </c>
-      <c r="F254" t="s">
-        <v>39</v>
+        <v>591</v>
+      </c>
+      <c r="E254" t="s">
+        <v>592</v>
+      </c>
+      <c r="G254" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -8707,13 +8707,13 @@
         <v>583</v>
       </c>
       <c r="B255" t="s">
-        <v>573</v>
+        <v>593</v>
       </c>
       <c r="C255">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D255" t="s">
-        <v>574</v>
+        <v>594</v>
       </c>
       <c r="F255" t="s">
         <v>118</v>
@@ -8724,16 +8724,16 @@
         <v>583</v>
       </c>
       <c r="B256" t="s">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="C256">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D256" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="F256" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -8741,16 +8741,16 @@
         <v>583</v>
       </c>
       <c r="B257" t="s">
-        <v>44</v>
+        <v>597</v>
       </c>
       <c r="C257">
         <v>2</v>
       </c>
       <c r="D257" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="F257" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -8758,16 +8758,16 @@
         <v>583</v>
       </c>
       <c r="B258" t="s">
-        <v>234</v>
+        <v>598</v>
       </c>
       <c r="C258">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D258" t="s">
-        <v>208</v>
+        <v>599</v>
       </c>
       <c r="F258" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -8775,13 +8775,13 @@
         <v>583</v>
       </c>
       <c r="B259" t="s">
-        <v>9</v>
+        <v>600</v>
       </c>
       <c r="C259">
         <v>2</v>
       </c>
       <c r="D259" t="s">
-        <v>479</v>
+        <v>601</v>
       </c>
       <c r="F259" t="s">
         <v>54</v>
@@ -8792,16 +8792,16 @@
         <v>583</v>
       </c>
       <c r="B260" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="C260">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D260" t="s">
-        <v>578</v>
+        <v>79</v>
       </c>
       <c r="F260" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -8809,16 +8809,16 @@
         <v>583</v>
       </c>
       <c r="B261" t="s">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="C261">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D261" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="F261" t="s">
-        <v>39</v>
+        <v>118</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -8826,33 +8826,33 @@
         <v>583</v>
       </c>
       <c r="B262" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="C262">
         <v>2</v>
       </c>
       <c r="D262" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="F262" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
     </row>
     <row r="263" spans="1:7">
       <c r="A263" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="B263" t="s">
-        <v>585</v>
+        <v>608</v>
       </c>
       <c r="C263">
         <v>2</v>
       </c>
       <c r="D263" t="s">
-        <v>586</v>
+        <v>609</v>
       </c>
       <c r="E263" t="s">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="G263" t="s">
         <v>54</v>
@@ -8860,101 +8860,104 @@
     </row>
     <row r="264" spans="1:7">
       <c r="A264" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="B264" t="s">
-        <v>244</v>
+        <v>611</v>
       </c>
       <c r="C264">
         <v>2</v>
       </c>
       <c r="D264" t="s">
-        <v>588</v>
-      </c>
-      <c r="E264" t="s">
-        <v>245</v>
-      </c>
-      <c r="G264" t="s">
+        <v>612</v>
+      </c>
+      <c r="F264" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="265" spans="1:7">
       <c r="A265" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="B265" t="s">
-        <v>589</v>
+        <v>613</v>
       </c>
       <c r="C265">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D265" t="s">
-        <v>590</v>
-      </c>
-      <c r="F265" t="s">
-        <v>54</v>
+        <v>614</v>
+      </c>
+      <c r="E265" t="s">
+        <v>615</v>
+      </c>
+      <c r="G265" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="266" spans="1:7">
       <c r="A266" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="B266" t="s">
-        <v>591</v>
+        <v>616</v>
       </c>
       <c r="C266">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D266" t="s">
-        <v>592</v>
+        <v>617</v>
       </c>
       <c r="E266" t="s">
-        <v>593</v>
+        <v>618</v>
       </c>
       <c r="G266" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
     </row>
     <row r="267" spans="1:7">
       <c r="A267" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="B267" t="s">
-        <v>594</v>
+        <v>619</v>
       </c>
       <c r="C267">
         <v>3</v>
       </c>
       <c r="D267" t="s">
-        <v>595</v>
-      </c>
-      <c r="F267" t="s">
+        <v>620</v>
+      </c>
+      <c r="E267" t="s">
+        <v>621</v>
+      </c>
+      <c r="G267" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="268" spans="1:7">
       <c r="A268" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="B268" t="s">
-        <v>596</v>
+        <v>621</v>
       </c>
       <c r="C268">
         <v>3</v>
       </c>
       <c r="D268" t="s">
-        <v>597</v>
+        <v>622</v>
       </c>
       <c r="F268" t="s">
-        <v>39</v>
+        <v>118</v>
       </c>
     </row>
     <row r="269" spans="1:7">
       <c r="A269" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="B269" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C269">
         <v>2</v>
@@ -8968,24 +8971,27 @@
     </row>
     <row r="270" spans="1:7">
       <c r="A270" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="B270" t="s">
-        <v>599</v>
+        <v>623</v>
       </c>
       <c r="C270">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D270" t="s">
-        <v>600</v>
-      </c>
-      <c r="F270" t="s">
-        <v>39</v>
+        <v>624</v>
+      </c>
+      <c r="E270" t="s">
+        <v>625</v>
+      </c>
+      <c r="G270" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="271" spans="1:7">
       <c r="A271" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="B271" t="s">
         <v>601</v>
@@ -8994,41 +9000,44 @@
         <v>2</v>
       </c>
       <c r="D271" t="s">
-        <v>602</v>
-      </c>
-      <c r="F271" t="s">
-        <v>54</v>
+        <v>626</v>
+      </c>
+      <c r="E271" t="s">
+        <v>48</v>
+      </c>
+      <c r="G271" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="272" spans="1:7">
       <c r="A272" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="B272" t="s">
-        <v>603</v>
+        <v>110</v>
       </c>
       <c r="C272">
         <v>2</v>
       </c>
       <c r="D272" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="F272" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="273" spans="1:7">
       <c r="A273" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="B273" t="s">
-        <v>604</v>
+        <v>627</v>
       </c>
       <c r="C273">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D273" t="s">
-        <v>605</v>
+        <v>628</v>
       </c>
       <c r="F273" t="s">
         <v>118</v>
@@ -9036,36 +9045,36 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="B274" t="s">
-        <v>606</v>
+        <v>629</v>
       </c>
       <c r="C274">
         <v>2</v>
       </c>
       <c r="D274" t="s">
-        <v>607</v>
+        <v>630</v>
       </c>
       <c r="F274" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="B275" t="s">
-        <v>609</v>
+        <v>306</v>
       </c>
       <c r="C275">
         <v>2</v>
       </c>
       <c r="D275" t="s">
-        <v>610</v>
+        <v>242</v>
       </c>
       <c r="E275" t="s">
-        <v>611</v>
+        <v>243</v>
       </c>
       <c r="G275" t="s">
         <v>54</v>
@@ -9073,110 +9082,107 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="B276" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="C276">
         <v>2</v>
       </c>
       <c r="D276" t="s">
-        <v>613</v>
-      </c>
-      <c r="F276" t="s">
+        <v>633</v>
+      </c>
+      <c r="E276" t="s">
+        <v>634</v>
+      </c>
+      <c r="G276" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="B277" t="s">
-        <v>614</v>
+        <v>635</v>
       </c>
       <c r="C277">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D277" t="s">
-        <v>615</v>
-      </c>
-      <c r="E277" t="s">
-        <v>616</v>
-      </c>
-      <c r="G277" t="s">
-        <v>39</v>
+        <v>636</v>
+      </c>
+      <c r="F277" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="278" spans="1:7">
       <c r="A278" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="B278" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="C278">
         <v>2</v>
       </c>
       <c r="D278" t="s">
-        <v>618</v>
-      </c>
-      <c r="E278" t="s">
-        <v>619</v>
-      </c>
-      <c r="G278" t="s">
+        <v>638</v>
+      </c>
+      <c r="F278" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="279" spans="1:7">
       <c r="A279" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="B279" t="s">
-        <v>620</v>
+        <v>639</v>
       </c>
       <c r="C279">
         <v>3</v>
       </c>
       <c r="D279" t="s">
-        <v>621</v>
-      </c>
-      <c r="E279" t="s">
-        <v>622</v>
-      </c>
-      <c r="G279" t="s">
+        <v>640</v>
+      </c>
+      <c r="F279" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="B280" t="s">
-        <v>622</v>
+        <v>260</v>
       </c>
       <c r="C280">
         <v>3</v>
       </c>
       <c r="D280" t="s">
-        <v>623</v>
-      </c>
-      <c r="F280" t="s">
+        <v>261</v>
+      </c>
+      <c r="E280" t="s">
+        <v>262</v>
+      </c>
+      <c r="G280" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="B281" t="s">
-        <v>598</v>
+        <v>573</v>
       </c>
       <c r="C281">
         <v>2</v>
       </c>
       <c r="D281" t="s">
-        <v>352</v>
+        <v>574</v>
       </c>
       <c r="F281" t="s">
         <v>118</v>
@@ -9184,56 +9190,50 @@
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="B282" t="s">
-        <v>624</v>
+        <v>575</v>
       </c>
       <c r="C282">
         <v>2</v>
       </c>
       <c r="D282" t="s">
-        <v>625</v>
-      </c>
-      <c r="E282" t="s">
-        <v>626</v>
-      </c>
-      <c r="G282" t="s">
+        <v>576</v>
+      </c>
+      <c r="F282" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="B283" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="C283">
         <v>2</v>
       </c>
       <c r="D283" t="s">
-        <v>627</v>
-      </c>
-      <c r="E283" t="s">
-        <v>48</v>
-      </c>
-      <c r="G283" t="s">
-        <v>39</v>
+        <v>642</v>
+      </c>
+      <c r="F283" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="284" spans="1:7">
       <c r="A284" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="B284" t="s">
-        <v>110</v>
+        <v>643</v>
       </c>
       <c r="C284">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D284" t="s">
-        <v>111</v>
+        <v>264</v>
       </c>
       <c r="F284" t="s">
         <v>39</v>
@@ -9241,33 +9241,33 @@
     </row>
     <row r="285" spans="1:7">
       <c r="A285" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="B285" t="s">
-        <v>628</v>
+        <v>44</v>
       </c>
       <c r="C285">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D285" t="s">
-        <v>629</v>
+        <v>372</v>
       </c>
       <c r="F285" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
     </row>
     <row r="286" spans="1:7">
       <c r="A286" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="B286" t="s">
-        <v>630</v>
+        <v>47</v>
       </c>
       <c r="C286">
         <v>2</v>
       </c>
       <c r="D286" t="s">
-        <v>631</v>
+        <v>429</v>
       </c>
       <c r="F286" t="s">
         <v>54</v>
@@ -9275,19 +9275,19 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B287" t="s">
-        <v>306</v>
+        <v>645</v>
       </c>
       <c r="C287">
         <v>2</v>
       </c>
       <c r="D287" t="s">
-        <v>242</v>
+        <v>646</v>
       </c>
       <c r="E287" t="s">
-        <v>243</v>
+        <v>647</v>
       </c>
       <c r="G287" t="s">
         <v>54</v>
@@ -9295,19 +9295,19 @@
     </row>
     <row r="288" spans="1:7">
       <c r="A288" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B288" t="s">
-        <v>633</v>
+        <v>243</v>
       </c>
       <c r="C288">
         <v>2</v>
       </c>
       <c r="D288" t="s">
-        <v>634</v>
+        <v>648</v>
       </c>
       <c r="E288" t="s">
-        <v>635</v>
+        <v>649</v>
       </c>
       <c r="G288" t="s">
         <v>54</v>
@@ -9315,50 +9315,53 @@
     </row>
     <row r="289" spans="1:7">
       <c r="A289" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B289" t="s">
-        <v>636</v>
+        <v>650</v>
       </c>
       <c r="C289">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D289" t="s">
-        <v>637</v>
-      </c>
-      <c r="F289" t="s">
-        <v>54</v>
+        <v>651</v>
+      </c>
+      <c r="E289" t="s">
+        <v>652</v>
+      </c>
+      <c r="G289" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="290" spans="1:7">
       <c r="A290" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B290" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
       <c r="C290">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D290" t="s">
-        <v>639</v>
+        <v>654</v>
       </c>
       <c r="F290" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="291" spans="1:7">
       <c r="A291" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B291" t="s">
-        <v>640</v>
+        <v>655</v>
       </c>
       <c r="C291">
         <v>3</v>
       </c>
       <c r="D291" t="s">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="F291" t="s">
         <v>118</v>
@@ -9366,36 +9369,33 @@
     </row>
     <row r="292" spans="1:7">
       <c r="A292" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B292" t="s">
-        <v>260</v>
+        <v>657</v>
       </c>
       <c r="C292">
         <v>3</v>
       </c>
       <c r="D292" t="s">
-        <v>261</v>
-      </c>
-      <c r="E292" t="s">
-        <v>262</v>
-      </c>
-      <c r="G292" t="s">
+        <v>658</v>
+      </c>
+      <c r="F292" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="293" spans="1:7">
       <c r="A293" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B293" t="s">
-        <v>573</v>
+        <v>659</v>
       </c>
       <c r="C293">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D293" t="s">
-        <v>574</v>
+        <v>660</v>
       </c>
       <c r="F293" t="s">
         <v>118</v>
@@ -9403,33 +9403,33 @@
     </row>
     <row r="294" spans="1:7">
       <c r="A294" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B294" t="s">
-        <v>575</v>
+        <v>661</v>
       </c>
       <c r="C294">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D294" t="s">
-        <v>576</v>
+        <v>662</v>
       </c>
       <c r="F294" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
     </row>
     <row r="295" spans="1:7">
       <c r="A295" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B295" t="s">
-        <v>642</v>
+        <v>663</v>
       </c>
       <c r="C295">
         <v>2</v>
       </c>
       <c r="D295" t="s">
-        <v>643</v>
+        <v>664</v>
       </c>
       <c r="F295" t="s">
         <v>118</v>
@@ -9437,16 +9437,16 @@
     </row>
     <row r="296" spans="1:7">
       <c r="A296" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B296" t="s">
-        <v>644</v>
+        <v>665</v>
       </c>
       <c r="C296">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D296" t="s">
-        <v>264</v>
+        <v>666</v>
       </c>
       <c r="F296" t="s">
         <v>39</v>
@@ -9454,16 +9454,16 @@
     </row>
     <row r="297" spans="1:7">
       <c r="A297" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B297" t="s">
-        <v>44</v>
+        <v>667</v>
       </c>
       <c r="C297">
         <v>2</v>
       </c>
       <c r="D297" t="s">
-        <v>372</v>
+        <v>668</v>
       </c>
       <c r="F297" t="s">
         <v>54</v>
@@ -9471,16 +9471,16 @@
     </row>
     <row r="298" spans="1:7">
       <c r="A298" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B298" t="s">
-        <v>47</v>
+        <v>669</v>
       </c>
       <c r="C298">
         <v>2</v>
       </c>
       <c r="D298" t="s">
-        <v>429</v>
+        <v>120</v>
       </c>
       <c r="F298" t="s">
         <v>54</v>
@@ -9488,19 +9488,19 @@
     </row>
     <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="B299" t="s">
-        <v>646</v>
+        <v>304</v>
       </c>
       <c r="C299">
         <v>2</v>
       </c>
       <c r="D299" t="s">
-        <v>647</v>
+        <v>305</v>
       </c>
       <c r="E299" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="G299" t="s">
         <v>54</v>
@@ -9508,1922 +9508,1919 @@
     </row>
     <row r="300" spans="1:7">
       <c r="A300" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="B300" t="s">
-        <v>243</v>
+        <v>671</v>
       </c>
       <c r="C300">
         <v>2</v>
       </c>
       <c r="D300" t="s">
-        <v>649</v>
-      </c>
-      <c r="E300" t="s">
-        <v>650</v>
-      </c>
-      <c r="G300" t="s">
+        <v>672</v>
+      </c>
+      <c r="F300" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="301" spans="1:7">
       <c r="A301" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="B301" t="s">
-        <v>651</v>
+        <v>673</v>
       </c>
       <c r="C301">
         <v>3</v>
       </c>
       <c r="D301" t="s">
-        <v>652</v>
-      </c>
-      <c r="E301" t="s">
-        <v>653</v>
-      </c>
-      <c r="G301" t="s">
+        <v>674</v>
+      </c>
+      <c r="F301" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="302" spans="1:7">
       <c r="A302" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="B302" t="s">
-        <v>654</v>
+        <v>57</v>
       </c>
       <c r="C302">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D302" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="F302" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="303" spans="1:7">
       <c r="A303" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="B303" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="C303">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D303" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="F303" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
     </row>
     <row r="304" spans="1:7">
       <c r="A304" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="B304" t="s">
-        <v>658</v>
+        <v>296</v>
       </c>
       <c r="C304">
         <v>3</v>
       </c>
       <c r="D304" t="s">
-        <v>659</v>
-      </c>
-      <c r="F304" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7">
+        <v>678</v>
+      </c>
+      <c r="E304" t="s">
+        <v>679</v>
+      </c>
+      <c r="G304" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8">
       <c r="A305" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="B305" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="C305">
         <v>3</v>
       </c>
       <c r="D305" t="s">
-        <v>661</v>
+        <v>297</v>
       </c>
       <c r="F305" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="306" spans="1:7">
+    <row r="306" spans="1:8">
       <c r="A306" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="B306" t="s">
-        <v>662</v>
+        <v>282</v>
       </c>
       <c r="C306">
         <v>3</v>
       </c>
       <c r="D306" t="s">
-        <v>663</v>
+        <v>680</v>
       </c>
       <c r="F306" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="307" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8">
       <c r="A307" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="B307" t="s">
-        <v>664</v>
+        <v>681</v>
       </c>
       <c r="C307">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D307" t="s">
-        <v>665</v>
-      </c>
-      <c r="F307" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7">
+        <v>682</v>
+      </c>
+      <c r="E307" t="s">
+        <v>683</v>
+      </c>
+      <c r="G307" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8">
       <c r="A308" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="B308" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
       <c r="C308">
         <v>2</v>
       </c>
       <c r="D308" t="s">
-        <v>667</v>
+        <v>685</v>
       </c>
       <c r="F308" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="309" spans="1:7">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8">
       <c r="A309" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="B309" t="s">
-        <v>668</v>
+        <v>686</v>
       </c>
       <c r="C309">
         <v>2</v>
       </c>
       <c r="D309" t="s">
-        <v>669</v>
+        <v>687</v>
       </c>
       <c r="F309" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="310" spans="1:7">
+    <row r="310" spans="1:8">
       <c r="A310" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="B310" t="s">
-        <v>670</v>
+        <v>688</v>
       </c>
       <c r="C310">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D310" t="s">
+        <v>689</v>
+      </c>
+      <c r="F310" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8">
+      <c r="A311" t="s">
+        <v>690</v>
+      </c>
+      <c r="B311" t="s">
+        <v>691</v>
+      </c>
+      <c r="C311">
+        <v>2</v>
+      </c>
+      <c r="D311" t="s">
+        <v>304</v>
+      </c>
+      <c r="E311" t="s">
+        <v>305</v>
+      </c>
+      <c r="G311" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8">
+      <c r="A312" t="s">
+        <v>690</v>
+      </c>
+      <c r="B312" t="s">
+        <v>692</v>
+      </c>
+      <c r="C312">
+        <v>3</v>
+      </c>
+      <c r="D312" t="s">
+        <v>693</v>
+      </c>
+      <c r="F312" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8">
+      <c r="A313" t="s">
+        <v>690</v>
+      </c>
+      <c r="B313" t="s">
+        <v>671</v>
+      </c>
+      <c r="C313">
+        <v>2</v>
+      </c>
+      <c r="D313" t="s">
+        <v>672</v>
+      </c>
+      <c r="F313" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8">
+      <c r="A314" t="s">
+        <v>690</v>
+      </c>
+      <c r="B314" t="s">
+        <v>694</v>
+      </c>
+      <c r="C314">
+        <v>3</v>
+      </c>
+      <c r="D314" t="s">
+        <v>695</v>
+      </c>
+      <c r="E314" t="s">
+        <v>696</v>
+      </c>
+      <c r="G314" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8">
+      <c r="A315" t="s">
+        <v>690</v>
+      </c>
+      <c r="B315" t="s">
+        <v>697</v>
+      </c>
+      <c r="C315">
+        <v>3</v>
+      </c>
+      <c r="D315" t="s">
+        <v>698</v>
+      </c>
+      <c r="E315" t="s">
+        <v>699</v>
+      </c>
+      <c r="F315" t="s">
+        <v>700</v>
+      </c>
+      <c r="H315" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8">
+      <c r="A316" t="s">
+        <v>690</v>
+      </c>
+      <c r="B316" t="s">
+        <v>701</v>
+      </c>
+      <c r="C316">
+        <v>3</v>
+      </c>
+      <c r="D316" t="s">
+        <v>702</v>
+      </c>
+      <c r="E316" t="s">
+        <v>703</v>
+      </c>
+      <c r="G316" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8">
+      <c r="A317" t="s">
+        <v>690</v>
+      </c>
+      <c r="B317" t="s">
+        <v>704</v>
+      </c>
+      <c r="C317">
+        <v>2</v>
+      </c>
+      <c r="D317" t="s">
+        <v>705</v>
+      </c>
+      <c r="F317" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8">
+      <c r="A318" t="s">
+        <v>690</v>
+      </c>
+      <c r="B318" t="s">
+        <v>706</v>
+      </c>
+      <c r="C318">
+        <v>2</v>
+      </c>
+      <c r="D318" t="s">
+        <v>707</v>
+      </c>
+      <c r="F318" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8">
+      <c r="A319" t="s">
+        <v>690</v>
+      </c>
+      <c r="B319" t="s">
+        <v>708</v>
+      </c>
+      <c r="C319">
+        <v>2</v>
+      </c>
+      <c r="D319" t="s">
+        <v>709</v>
+      </c>
+      <c r="F319" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8">
+      <c r="A320" t="s">
+        <v>690</v>
+      </c>
+      <c r="B320" t="s">
+        <v>710</v>
+      </c>
+      <c r="C320">
+        <v>2</v>
+      </c>
+      <c r="D320" t="s">
+        <v>711</v>
+      </c>
+      <c r="F320" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7">
+      <c r="A321" t="s">
+        <v>690</v>
+      </c>
+      <c r="B321" t="s">
+        <v>602</v>
+      </c>
+      <c r="C321">
+        <v>2</v>
+      </c>
+      <c r="D321" t="s">
+        <v>712</v>
+      </c>
+      <c r="F321" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7">
+      <c r="A322" t="s">
+        <v>690</v>
+      </c>
+      <c r="B322" t="s">
+        <v>713</v>
+      </c>
+      <c r="C322">
+        <v>3</v>
+      </c>
+      <c r="D322" t="s">
+        <v>714</v>
+      </c>
+      <c r="F322" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7">
+      <c r="A323" t="s">
+        <v>715</v>
+      </c>
+      <c r="B323" t="s">
+        <v>306</v>
+      </c>
+      <c r="C323">
+        <v>2</v>
+      </c>
+      <c r="D323" t="s">
+        <v>716</v>
+      </c>
+      <c r="E323" t="s">
+        <v>717</v>
+      </c>
+      <c r="G323" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7">
+      <c r="A324" t="s">
+        <v>715</v>
+      </c>
+      <c r="B324" t="s">
+        <v>304</v>
+      </c>
+      <c r="C324">
+        <v>2</v>
+      </c>
+      <c r="D324" t="s">
+        <v>305</v>
+      </c>
+      <c r="E324" t="s">
+        <v>718</v>
+      </c>
+      <c r="G324" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7">
+      <c r="A325" t="s">
+        <v>715</v>
+      </c>
+      <c r="B325" t="s">
+        <v>719</v>
+      </c>
+      <c r="C325">
+        <v>3</v>
+      </c>
+      <c r="D325" t="s">
+        <v>720</v>
+      </c>
+      <c r="E325" t="s">
+        <v>721</v>
+      </c>
+      <c r="G325" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7">
+      <c r="A326" t="s">
+        <v>715</v>
+      </c>
+      <c r="B326" t="s">
+        <v>722</v>
+      </c>
+      <c r="C326">
+        <v>3</v>
+      </c>
+      <c r="D326" t="s">
+        <v>723</v>
+      </c>
+      <c r="F326" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7">
+      <c r="A327" t="s">
+        <v>715</v>
+      </c>
+      <c r="B327" t="s">
+        <v>724</v>
+      </c>
+      <c r="C327">
+        <v>3</v>
+      </c>
+      <c r="D327" t="s">
+        <v>725</v>
+      </c>
+      <c r="F327" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7">
+      <c r="A328" t="s">
+        <v>715</v>
+      </c>
+      <c r="B328" t="s">
+        <v>726</v>
+      </c>
+      <c r="C328">
+        <v>2</v>
+      </c>
+      <c r="D328" t="s">
+        <v>727</v>
+      </c>
+      <c r="F328" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7">
+      <c r="A329" t="s">
+        <v>715</v>
+      </c>
+      <c r="B329" t="s">
+        <v>728</v>
+      </c>
+      <c r="C329">
+        <v>3</v>
+      </c>
+      <c r="D329" t="s">
+        <v>729</v>
+      </c>
+      <c r="F329" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7">
+      <c r="A330" t="s">
+        <v>715</v>
+      </c>
+      <c r="B330" t="s">
+        <v>730</v>
+      </c>
+      <c r="C330">
+        <v>2</v>
+      </c>
+      <c r="D330" t="s">
+        <v>731</v>
+      </c>
+      <c r="F330" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7">
+      <c r="A331" t="s">
+        <v>715</v>
+      </c>
+      <c r="B331" t="s">
+        <v>110</v>
+      </c>
+      <c r="C331">
+        <v>2</v>
+      </c>
+      <c r="D331" t="s">
+        <v>111</v>
+      </c>
+      <c r="F331" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7">
+      <c r="A332" t="s">
+        <v>715</v>
+      </c>
+      <c r="B332" t="s">
+        <v>732</v>
+      </c>
+      <c r="C332">
+        <v>2</v>
+      </c>
+      <c r="D332" t="s">
+        <v>733</v>
+      </c>
+      <c r="F332" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7">
+      <c r="A333" t="s">
+        <v>715</v>
+      </c>
+      <c r="B333" t="s">
+        <v>734</v>
+      </c>
+      <c r="C333">
+        <v>2</v>
+      </c>
+      <c r="D333" t="s">
+        <v>735</v>
+      </c>
+      <c r="F333" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7">
+      <c r="A334" t="s">
+        <v>715</v>
+      </c>
+      <c r="B334" t="s">
+        <v>736</v>
+      </c>
+      <c r="C334">
+        <v>2</v>
+      </c>
+      <c r="D334" t="s">
+        <v>737</v>
+      </c>
+      <c r="F334" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7">
+      <c r="A335" t="s">
+        <v>738</v>
+      </c>
+      <c r="B335" t="s">
+        <v>55</v>
+      </c>
+      <c r="C335">
+        <v>2</v>
+      </c>
+      <c r="D335" t="s">
+        <v>739</v>
+      </c>
+      <c r="E335" t="s">
+        <v>740</v>
+      </c>
+      <c r="G335" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7">
+      <c r="A336" t="s">
+        <v>738</v>
+      </c>
+      <c r="B336" t="s">
+        <v>741</v>
+      </c>
+      <c r="C336">
+        <v>2</v>
+      </c>
+      <c r="D336" t="s">
+        <v>742</v>
+      </c>
+      <c r="E336" t="s">
+        <v>743</v>
+      </c>
+      <c r="G336" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8">
+      <c r="A337" t="s">
+        <v>738</v>
+      </c>
+      <c r="B337" t="s">
+        <v>744</v>
+      </c>
+      <c r="C337">
+        <v>2</v>
+      </c>
+      <c r="D337" t="s">
+        <v>745</v>
+      </c>
+      <c r="F337" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8">
+      <c r="A338" t="s">
+        <v>738</v>
+      </c>
+      <c r="B338" t="s">
+        <v>746</v>
+      </c>
+      <c r="C338">
+        <v>3</v>
+      </c>
+      <c r="D338" t="s">
+        <v>747</v>
+      </c>
+      <c r="F338" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8">
+      <c r="A339" t="s">
+        <v>738</v>
+      </c>
+      <c r="B339" t="s">
+        <v>748</v>
+      </c>
+      <c r="C339">
+        <v>3</v>
+      </c>
+      <c r="D339" t="s">
+        <v>749</v>
+      </c>
+      <c r="E339" t="s">
+        <v>750</v>
+      </c>
+      <c r="G339" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8">
+      <c r="A340" t="s">
+        <v>738</v>
+      </c>
+      <c r="B340" t="s">
+        <v>751</v>
+      </c>
+      <c r="C340">
+        <v>2</v>
+      </c>
+      <c r="D340" t="s">
+        <v>752</v>
+      </c>
+      <c r="F340" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8">
+      <c r="A341" t="s">
+        <v>738</v>
+      </c>
+      <c r="B341" t="s">
+        <v>753</v>
+      </c>
+      <c r="C341">
+        <v>3</v>
+      </c>
+      <c r="D341" t="s">
+        <v>754</v>
+      </c>
+      <c r="F341" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8">
+      <c r="A342" t="s">
+        <v>738</v>
+      </c>
+      <c r="B342" t="s">
+        <v>337</v>
+      </c>
+      <c r="C342">
+        <v>3</v>
+      </c>
+      <c r="D342" t="s">
+        <v>338</v>
+      </c>
+      <c r="F342" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8">
+      <c r="A343" t="s">
+        <v>738</v>
+      </c>
+      <c r="B343" t="s">
+        <v>755</v>
+      </c>
+      <c r="C343">
+        <v>2</v>
+      </c>
+      <c r="D343" t="s">
+        <v>756</v>
+      </c>
+      <c r="F343" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8">
+      <c r="A344" t="s">
+        <v>738</v>
+      </c>
+      <c r="B344" t="s">
+        <v>559</v>
+      </c>
+      <c r="C344">
+        <v>2</v>
+      </c>
+      <c r="D344" t="s">
+        <v>560</v>
+      </c>
+      <c r="F344" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8">
+      <c r="A345" t="s">
+        <v>738</v>
+      </c>
+      <c r="B345" t="s">
         <v>120</v>
       </c>
-      <c r="F310" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="311" spans="1:7">
-      <c r="A311" t="s">
-        <v>671</v>
-      </c>
-      <c r="B311" t="s">
-        <v>304</v>
-      </c>
-      <c r="C311">
-        <v>2</v>
-      </c>
-      <c r="D311" t="s">
-        <v>305</v>
-      </c>
-      <c r="E311" t="s">
-        <v>650</v>
-      </c>
-      <c r="G311" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="312" spans="1:7">
-      <c r="A312" t="s">
-        <v>671</v>
-      </c>
-      <c r="B312" t="s">
-        <v>672</v>
-      </c>
-      <c r="C312">
-        <v>2</v>
-      </c>
-      <c r="D312" t="s">
-        <v>673</v>
-      </c>
-      <c r="F312" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="313" spans="1:7">
-      <c r="A313" t="s">
-        <v>671</v>
-      </c>
-      <c r="B313" t="s">
-        <v>674</v>
-      </c>
-      <c r="C313">
-        <v>3</v>
-      </c>
-      <c r="D313" t="s">
-        <v>675</v>
-      </c>
-      <c r="F313" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="314" spans="1:7">
-      <c r="A314" t="s">
-        <v>671</v>
-      </c>
-      <c r="B314" t="s">
-        <v>57</v>
-      </c>
-      <c r="C314">
-        <v>2</v>
-      </c>
-      <c r="D314" t="s">
-        <v>676</v>
-      </c>
-      <c r="F314" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="315" spans="1:7">
-      <c r="A315" t="s">
-        <v>671</v>
-      </c>
-      <c r="B315" t="s">
-        <v>677</v>
-      </c>
-      <c r="C315">
-        <v>2</v>
-      </c>
-      <c r="D315" t="s">
+      <c r="C345">
+        <v>2</v>
+      </c>
+      <c r="D345" t="s">
+        <v>119</v>
+      </c>
+      <c r="F345" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8">
+      <c r="A346" t="s">
+        <v>738</v>
+      </c>
+      <c r="B346" t="s">
+        <v>757</v>
+      </c>
+      <c r="C346">
+        <v>2</v>
+      </c>
+      <c r="D346" t="s">
+        <v>758</v>
+      </c>
+      <c r="F346" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8">
+      <c r="A347" t="s">
+        <v>759</v>
+      </c>
+      <c r="B347" t="s">
+        <v>760</v>
+      </c>
+      <c r="C347">
+        <v>2</v>
+      </c>
+      <c r="D347" t="s">
+        <v>761</v>
+      </c>
+      <c r="F347" t="s">
+        <v>762</v>
+      </c>
+      <c r="H347" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8">
+      <c r="A348" t="s">
+        <v>759</v>
+      </c>
+      <c r="B348" t="s">
+        <v>85</v>
+      </c>
+      <c r="C348">
+        <v>2</v>
+      </c>
+      <c r="D348" t="s">
+        <v>763</v>
+      </c>
+      <c r="E348" t="s">
+        <v>764</v>
+      </c>
+      <c r="G348" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8">
+      <c r="A349" t="s">
+        <v>759</v>
+      </c>
+      <c r="B349" t="s">
+        <v>95</v>
+      </c>
+      <c r="C349">
+        <v>3</v>
+      </c>
+      <c r="D349" t="s">
+        <v>96</v>
+      </c>
+      <c r="E349" t="s">
+        <v>97</v>
+      </c>
+      <c r="G349" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8">
+      <c r="A350" t="s">
+        <v>759</v>
+      </c>
+      <c r="B350" t="s">
+        <v>114</v>
+      </c>
+      <c r="C350">
+        <v>3</v>
+      </c>
+      <c r="D350" t="s">
+        <v>112</v>
+      </c>
+      <c r="E350" t="s">
+        <v>765</v>
+      </c>
+      <c r="G350" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8">
+      <c r="A351" t="s">
+        <v>759</v>
+      </c>
+      <c r="B351" t="s">
+        <v>104</v>
+      </c>
+      <c r="C351">
+        <v>2</v>
+      </c>
+      <c r="D351" t="s">
+        <v>106</v>
+      </c>
+      <c r="E351" t="s">
+        <v>105</v>
+      </c>
+      <c r="F351" t="s">
+        <v>766</v>
+      </c>
+      <c r="G351" t="s">
+        <v>767</v>
+      </c>
+      <c r="H351" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8">
+      <c r="A352" t="s">
+        <v>759</v>
+      </c>
+      <c r="B352" t="s">
+        <v>98</v>
+      </c>
+      <c r="C352">
+        <v>2</v>
+      </c>
+      <c r="D352" t="s">
+        <v>99</v>
+      </c>
+      <c r="E352" t="s">
+        <v>768</v>
+      </c>
+      <c r="G352" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7">
+      <c r="A353" t="s">
+        <v>759</v>
+      </c>
+      <c r="B353" t="s">
+        <v>86</v>
+      </c>
+      <c r="C353">
+        <v>2</v>
+      </c>
+      <c r="D353" t="s">
+        <v>769</v>
+      </c>
+      <c r="F353" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7">
+      <c r="A354" t="s">
+        <v>759</v>
+      </c>
+      <c r="B354" t="s">
+        <v>372</v>
+      </c>
+      <c r="C354">
+        <v>2</v>
+      </c>
+      <c r="D354" t="s">
+        <v>44</v>
+      </c>
+      <c r="E354" t="s">
+        <v>427</v>
+      </c>
+      <c r="G354" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7">
+      <c r="A355" t="s">
+        <v>759</v>
+      </c>
+      <c r="B355" t="s">
+        <v>770</v>
+      </c>
+      <c r="C355">
+        <v>2</v>
+      </c>
+      <c r="D355" t="s">
+        <v>771</v>
+      </c>
+      <c r="F355" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7">
+      <c r="A356" t="s">
+        <v>759</v>
+      </c>
+      <c r="B356" t="s">
+        <v>772</v>
+      </c>
+      <c r="C356">
+        <v>3</v>
+      </c>
+      <c r="D356" t="s">
+        <v>773</v>
+      </c>
+      <c r="E356" t="s">
+        <v>774</v>
+      </c>
+      <c r="G356" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7">
+      <c r="A357" t="s">
+        <v>775</v>
+      </c>
+      <c r="B357" t="s">
+        <v>355</v>
+      </c>
+      <c r="C357">
+        <v>2</v>
+      </c>
+      <c r="D357" t="s">
+        <v>776</v>
+      </c>
+      <c r="E357" t="s">
+        <v>777</v>
+      </c>
+      <c r="G357" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7">
+      <c r="A358" t="s">
+        <v>775</v>
+      </c>
+      <c r="B358" t="s">
+        <v>778</v>
+      </c>
+      <c r="C358">
+        <v>3</v>
+      </c>
+      <c r="D358" t="s">
+        <v>779</v>
+      </c>
+      <c r="E358" t="s">
+        <v>780</v>
+      </c>
+      <c r="G358" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7">
+      <c r="A359" t="s">
+        <v>775</v>
+      </c>
+      <c r="B359" t="s">
+        <v>358</v>
+      </c>
+      <c r="C359">
+        <v>3</v>
+      </c>
+      <c r="D359" t="s">
+        <v>359</v>
+      </c>
+      <c r="F359" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7">
+      <c r="A360" t="s">
+        <v>775</v>
+      </c>
+      <c r="B360" t="s">
+        <v>781</v>
+      </c>
+      <c r="C360">
+        <v>3</v>
+      </c>
+      <c r="D360" t="s">
+        <v>782</v>
+      </c>
+      <c r="F360" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7">
+      <c r="A361" t="s">
+        <v>775</v>
+      </c>
+      <c r="B361" t="s">
+        <v>783</v>
+      </c>
+      <c r="C361">
+        <v>2</v>
+      </c>
+      <c r="D361" t="s">
+        <v>784</v>
+      </c>
+      <c r="E361" t="s">
+        <v>785</v>
+      </c>
+      <c r="G361" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7">
+      <c r="A362" t="s">
+        <v>775</v>
+      </c>
+      <c r="B362" t="s">
+        <v>365</v>
+      </c>
+      <c r="C362">
+        <v>3</v>
+      </c>
+      <c r="D362" t="s">
+        <v>366</v>
+      </c>
+      <c r="F362" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7">
+      <c r="A363" t="s">
+        <v>775</v>
+      </c>
+      <c r="B363" t="s">
+        <v>360</v>
+      </c>
+      <c r="C363">
+        <v>3</v>
+      </c>
+      <c r="D363" t="s">
+        <v>361</v>
+      </c>
+      <c r="F363" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7">
+      <c r="A364" t="s">
+        <v>775</v>
+      </c>
+      <c r="B364" t="s">
+        <v>367</v>
+      </c>
+      <c r="C364">
+        <v>3</v>
+      </c>
+      <c r="D364" t="s">
+        <v>368</v>
+      </c>
+      <c r="E364" t="s">
+        <v>369</v>
+      </c>
+      <c r="G364" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7">
+      <c r="A365" t="s">
+        <v>775</v>
+      </c>
+      <c r="B365" t="s">
+        <v>370</v>
+      </c>
+      <c r="C365">
+        <v>2</v>
+      </c>
+      <c r="D365" t="s">
+        <v>786</v>
+      </c>
+      <c r="F365" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7">
+      <c r="A366" t="s">
+        <v>775</v>
+      </c>
+      <c r="B366" t="s">
+        <v>787</v>
+      </c>
+      <c r="C366">
+        <v>2</v>
+      </c>
+      <c r="D366" t="s">
+        <v>788</v>
+      </c>
+      <c r="E366" t="s">
+        <v>789</v>
+      </c>
+      <c r="G366" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7">
+      <c r="A367" t="s">
+        <v>790</v>
+      </c>
+      <c r="B367" t="s">
+        <v>88</v>
+      </c>
+      <c r="C367">
+        <v>2</v>
+      </c>
+      <c r="D367" t="s">
+        <v>791</v>
+      </c>
+      <c r="E367" t="s">
+        <v>792</v>
+      </c>
+      <c r="G367" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7">
+      <c r="A368" t="s">
+        <v>790</v>
+      </c>
+      <c r="B368" t="s">
+        <v>793</v>
+      </c>
+      <c r="C368">
+        <v>2</v>
+      </c>
+      <c r="D368" t="s">
+        <v>794</v>
+      </c>
+      <c r="F368" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8">
+      <c r="A369" t="s">
+        <v>790</v>
+      </c>
+      <c r="B369" t="s">
+        <v>795</v>
+      </c>
+      <c r="C369">
+        <v>3</v>
+      </c>
+      <c r="D369" t="s">
+        <v>796</v>
+      </c>
+      <c r="E369" t="s">
+        <v>797</v>
+      </c>
+      <c r="G369" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8">
+      <c r="A370" t="s">
+        <v>790</v>
+      </c>
+      <c r="B370" t="s">
+        <v>798</v>
+      </c>
+      <c r="C370">
+        <v>3</v>
+      </c>
+      <c r="D370" t="s">
+        <v>799</v>
+      </c>
+      <c r="F370" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8">
+      <c r="A371" t="s">
+        <v>790</v>
+      </c>
+      <c r="B371" t="s">
+        <v>543</v>
+      </c>
+      <c r="C371">
+        <v>3</v>
+      </c>
+      <c r="D371" t="s">
+        <v>542</v>
+      </c>
+      <c r="F371" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8">
+      <c r="A372" t="s">
+        <v>790</v>
+      </c>
+      <c r="B372" t="s">
+        <v>800</v>
+      </c>
+      <c r="C372">
+        <v>3</v>
+      </c>
+      <c r="D372" t="s">
+        <v>801</v>
+      </c>
+      <c r="E372" t="s">
+        <v>802</v>
+      </c>
+      <c r="G372" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8">
+      <c r="A373" t="s">
+        <v>790</v>
+      </c>
+      <c r="B373" t="s">
+        <v>753</v>
+      </c>
+      <c r="C373">
+        <v>3</v>
+      </c>
+      <c r="D373" t="s">
+        <v>754</v>
+      </c>
+      <c r="E373" t="s">
+        <v>803</v>
+      </c>
+      <c r="G373" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8">
+      <c r="A374" t="s">
+        <v>790</v>
+      </c>
+      <c r="B374" t="s">
+        <v>804</v>
+      </c>
+      <c r="C374">
+        <v>3</v>
+      </c>
+      <c r="D374" t="s">
+        <v>805</v>
+      </c>
+      <c r="E374" t="s">
+        <v>806</v>
+      </c>
+      <c r="F374" t="s">
+        <v>807</v>
+      </c>
+      <c r="G374" t="s">
+        <v>808</v>
+      </c>
+      <c r="H374" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8">
+      <c r="A375" t="s">
+        <v>790</v>
+      </c>
+      <c r="B375" t="s">
+        <v>339</v>
+      </c>
+      <c r="C375">
+        <v>3</v>
+      </c>
+      <c r="D375" t="s">
+        <v>340</v>
+      </c>
+      <c r="F375" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8">
+      <c r="A376" t="s">
+        <v>790</v>
+      </c>
+      <c r="B376" t="s">
+        <v>120</v>
+      </c>
+      <c r="C376">
+        <v>2</v>
+      </c>
+      <c r="D376" t="s">
+        <v>179</v>
+      </c>
+      <c r="F376" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8">
+      <c r="A377" t="s">
+        <v>809</v>
+      </c>
+      <c r="B377" t="s">
+        <v>810</v>
+      </c>
+      <c r="C377">
+        <v>2</v>
+      </c>
+      <c r="D377" t="s">
+        <v>811</v>
+      </c>
+      <c r="E377" t="s">
+        <v>812</v>
+      </c>
+      <c r="G377" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8">
+      <c r="A378" t="s">
+        <v>809</v>
+      </c>
+      <c r="B378" t="s">
+        <v>813</v>
+      </c>
+      <c r="C378">
+        <v>3</v>
+      </c>
+      <c r="D378" t="s">
+        <v>814</v>
+      </c>
+      <c r="E378" t="s">
+        <v>815</v>
+      </c>
+      <c r="G378" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8">
+      <c r="A379" t="s">
+        <v>809</v>
+      </c>
+      <c r="B379" t="s">
+        <v>154</v>
+      </c>
+      <c r="C379">
+        <v>2</v>
+      </c>
+      <c r="D379" t="s">
+        <v>155</v>
+      </c>
+      <c r="E379" t="s">
+        <v>156</v>
+      </c>
+      <c r="G379" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8">
+      <c r="A380" t="s">
+        <v>809</v>
+      </c>
+      <c r="B380" t="s">
+        <v>816</v>
+      </c>
+      <c r="C380">
+        <v>3</v>
+      </c>
+      <c r="D380" t="s">
+        <v>817</v>
+      </c>
+      <c r="F380" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8">
+      <c r="A381" t="s">
+        <v>809</v>
+      </c>
+      <c r="B381" t="s">
+        <v>818</v>
+      </c>
+      <c r="C381">
+        <v>3</v>
+      </c>
+      <c r="D381" t="s">
+        <v>819</v>
+      </c>
+      <c r="F381" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8">
+      <c r="A382" t="s">
+        <v>809</v>
+      </c>
+      <c r="B382" t="s">
+        <v>820</v>
+      </c>
+      <c r="C382">
+        <v>2</v>
+      </c>
+      <c r="D382" t="s">
+        <v>821</v>
+      </c>
+      <c r="F382" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8">
+      <c r="A383" t="s">
+        <v>809</v>
+      </c>
+      <c r="B383" t="s">
+        <v>48</v>
+      </c>
+      <c r="C383">
+        <v>2</v>
+      </c>
+      <c r="D383" t="s">
+        <v>448</v>
+      </c>
+      <c r="E383" t="s">
+        <v>822</v>
+      </c>
+      <c r="G383" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8">
+      <c r="A384" t="s">
+        <v>809</v>
+      </c>
+      <c r="B384" t="s">
+        <v>823</v>
+      </c>
+      <c r="C384">
+        <v>2</v>
+      </c>
+      <c r="D384" t="s">
+        <v>824</v>
+      </c>
+      <c r="F384" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7">
+      <c r="A385" t="s">
+        <v>809</v>
+      </c>
+      <c r="B385" t="s">
+        <v>825</v>
+      </c>
+      <c r="C385">
+        <v>2</v>
+      </c>
+      <c r="D385" t="s">
+        <v>826</v>
+      </c>
+      <c r="F385" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7">
+      <c r="A386" t="s">
+        <v>809</v>
+      </c>
+      <c r="B386" t="s">
+        <v>827</v>
+      </c>
+      <c r="C386">
+        <v>2</v>
+      </c>
+      <c r="D386" t="s">
+        <v>828</v>
+      </c>
+      <c r="E386" t="s">
+        <v>829</v>
+      </c>
+      <c r="G386" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7">
+      <c r="A387" t="s">
+        <v>830</v>
+      </c>
+      <c r="B387" t="s">
+        <v>453</v>
+      </c>
+      <c r="C387">
+        <v>2</v>
+      </c>
+      <c r="D387" t="s">
+        <v>454</v>
+      </c>
+      <c r="E387" t="s">
+        <v>455</v>
+      </c>
+      <c r="G387" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7">
+      <c r="A388" t="s">
+        <v>830</v>
+      </c>
+      <c r="B388" t="s">
+        <v>157</v>
+      </c>
+      <c r="C388">
+        <v>3</v>
+      </c>
+      <c r="D388" t="s">
+        <v>158</v>
+      </c>
+      <c r="E388" t="s">
+        <v>831</v>
+      </c>
+      <c r="G388" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7">
+      <c r="A389" t="s">
+        <v>830</v>
+      </c>
+      <c r="B389" t="s">
+        <v>154</v>
+      </c>
+      <c r="C389">
+        <v>2</v>
+      </c>
+      <c r="D389" t="s">
+        <v>155</v>
+      </c>
+      <c r="F389" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7">
+      <c r="A390" t="s">
+        <v>830</v>
+      </c>
+      <c r="B390" t="s">
+        <v>9</v>
+      </c>
+      <c r="C390">
+        <v>2</v>
+      </c>
+      <c r="D390" t="s">
+        <v>479</v>
+      </c>
+      <c r="F390" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7">
+      <c r="A391" t="s">
+        <v>830</v>
+      </c>
+      <c r="B391" t="s">
+        <v>832</v>
+      </c>
+      <c r="C391">
+        <v>3</v>
+      </c>
+      <c r="D391" t="s">
+        <v>833</v>
+      </c>
+      <c r="E391" t="s">
+        <v>834</v>
+      </c>
+      <c r="G391" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7">
+      <c r="A392" t="s">
+        <v>830</v>
+      </c>
+      <c r="B392" t="s">
+        <v>835</v>
+      </c>
+      <c r="C392">
+        <v>3</v>
+      </c>
+      <c r="D392" t="s">
+        <v>836</v>
+      </c>
+      <c r="F392" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7">
+      <c r="A393" t="s">
+        <v>830</v>
+      </c>
+      <c r="B393" t="s">
+        <v>296</v>
+      </c>
+      <c r="C393">
+        <v>3</v>
+      </c>
+      <c r="D393" t="s">
         <v>678</v>
       </c>
-      <c r="F315" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="316" spans="1:7">
-      <c r="A316" t="s">
-        <v>671</v>
-      </c>
-      <c r="B316" t="s">
-        <v>296</v>
-      </c>
-      <c r="C316">
-        <v>3</v>
-      </c>
-      <c r="D316" t="s">
-        <v>679</v>
-      </c>
-      <c r="E316" t="s">
-        <v>680</v>
-      </c>
-      <c r="G316" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="317" spans="1:7">
-      <c r="A317" t="s">
-        <v>671</v>
-      </c>
-      <c r="B317" t="s">
-        <v>668</v>
-      </c>
-      <c r="C317">
-        <v>3</v>
-      </c>
-      <c r="D317" t="s">
-        <v>297</v>
-      </c>
-      <c r="F317" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="318" spans="1:7">
-      <c r="A318" t="s">
-        <v>671</v>
-      </c>
-      <c r="B318" t="s">
-        <v>282</v>
-      </c>
-      <c r="C318">
-        <v>3</v>
-      </c>
-      <c r="D318" t="s">
-        <v>681</v>
-      </c>
-      <c r="F318" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="319" spans="1:7">
-      <c r="A319" t="s">
-        <v>671</v>
-      </c>
-      <c r="B319" t="s">
-        <v>682</v>
-      </c>
-      <c r="C319">
-        <v>3</v>
-      </c>
-      <c r="D319" t="s">
-        <v>683</v>
-      </c>
-      <c r="E319" t="s">
-        <v>684</v>
-      </c>
-      <c r="G319" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="320" spans="1:7">
-      <c r="A320" t="s">
-        <v>671</v>
-      </c>
-      <c r="B320" t="s">
-        <v>685</v>
-      </c>
-      <c r="C320">
-        <v>2</v>
-      </c>
-      <c r="D320" t="s">
-        <v>686</v>
-      </c>
-      <c r="F320" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="321" spans="1:8">
-      <c r="A321" t="s">
-        <v>671</v>
-      </c>
-      <c r="B321" t="s">
-        <v>687</v>
-      </c>
-      <c r="C321">
-        <v>2</v>
-      </c>
-      <c r="D321" t="s">
-        <v>688</v>
-      </c>
-      <c r="F321" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="322" spans="1:8">
-      <c r="A322" t="s">
-        <v>671</v>
-      </c>
-      <c r="B322" t="s">
-        <v>689</v>
-      </c>
-      <c r="C322">
-        <v>3</v>
-      </c>
-      <c r="D322" t="s">
-        <v>690</v>
-      </c>
-      <c r="F322" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="323" spans="1:8">
-      <c r="A323" t="s">
-        <v>691</v>
-      </c>
-      <c r="B323" t="s">
-        <v>692</v>
-      </c>
-      <c r="C323">
-        <v>2</v>
-      </c>
-      <c r="D323" t="s">
-        <v>304</v>
-      </c>
-      <c r="E323" t="s">
-        <v>305</v>
-      </c>
-      <c r="G323" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="324" spans="1:8">
-      <c r="A324" t="s">
-        <v>691</v>
-      </c>
-      <c r="B324" t="s">
-        <v>693</v>
-      </c>
-      <c r="C324">
-        <v>3</v>
-      </c>
-      <c r="D324" t="s">
-        <v>694</v>
-      </c>
-      <c r="F324" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="325" spans="1:8">
-      <c r="A325" t="s">
-        <v>691</v>
-      </c>
-      <c r="B325" t="s">
-        <v>672</v>
-      </c>
-      <c r="C325">
-        <v>2</v>
-      </c>
-      <c r="D325" t="s">
-        <v>673</v>
-      </c>
-      <c r="F325" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="326" spans="1:8">
-      <c r="A326" t="s">
-        <v>691</v>
-      </c>
-      <c r="B326" t="s">
-        <v>695</v>
-      </c>
-      <c r="C326">
-        <v>3</v>
-      </c>
-      <c r="D326" t="s">
-        <v>696</v>
-      </c>
-      <c r="E326" t="s">
-        <v>697</v>
-      </c>
-      <c r="G326" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="327" spans="1:8">
-      <c r="A327" t="s">
-        <v>691</v>
-      </c>
-      <c r="B327" t="s">
-        <v>698</v>
-      </c>
-      <c r="C327">
-        <v>3</v>
-      </c>
-      <c r="D327" t="s">
-        <v>699</v>
-      </c>
-      <c r="E327" t="s">
-        <v>700</v>
-      </c>
-      <c r="F327" t="s">
-        <v>701</v>
-      </c>
-      <c r="H327" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="328" spans="1:8">
-      <c r="A328" t="s">
-        <v>691</v>
-      </c>
-      <c r="B328" t="s">
-        <v>702</v>
-      </c>
-      <c r="C328">
-        <v>3</v>
-      </c>
-      <c r="D328" t="s">
-        <v>703</v>
-      </c>
-      <c r="E328" t="s">
-        <v>704</v>
-      </c>
-      <c r="G328" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="329" spans="1:8">
-      <c r="A329" t="s">
-        <v>691</v>
-      </c>
-      <c r="B329" t="s">
-        <v>705</v>
-      </c>
-      <c r="C329">
-        <v>2</v>
-      </c>
-      <c r="D329" t="s">
-        <v>706</v>
-      </c>
-      <c r="F329" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="330" spans="1:8">
-      <c r="A330" t="s">
-        <v>691</v>
-      </c>
-      <c r="B330" t="s">
-        <v>707</v>
-      </c>
-      <c r="C330">
-        <v>2</v>
-      </c>
-      <c r="D330" t="s">
-        <v>708</v>
-      </c>
-      <c r="F330" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="331" spans="1:8">
-      <c r="A331" t="s">
-        <v>691</v>
-      </c>
-      <c r="B331" t="s">
-        <v>709</v>
-      </c>
-      <c r="C331">
-        <v>2</v>
-      </c>
-      <c r="D331" t="s">
-        <v>710</v>
-      </c>
-      <c r="F331" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="332" spans="1:8">
-      <c r="A332" t="s">
-        <v>691</v>
-      </c>
-      <c r="B332" t="s">
-        <v>711</v>
-      </c>
-      <c r="C332">
-        <v>2</v>
-      </c>
-      <c r="D332" t="s">
-        <v>712</v>
-      </c>
-      <c r="F332" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="333" spans="1:8">
-      <c r="A333" t="s">
-        <v>691</v>
-      </c>
-      <c r="B333" t="s">
-        <v>603</v>
-      </c>
-      <c r="C333">
-        <v>2</v>
-      </c>
-      <c r="D333" t="s">
-        <v>713</v>
-      </c>
-      <c r="F333" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="334" spans="1:8">
-      <c r="A334" t="s">
-        <v>691</v>
-      </c>
-      <c r="B334" t="s">
-        <v>714</v>
-      </c>
-      <c r="C334">
-        <v>3</v>
-      </c>
-      <c r="D334" t="s">
-        <v>715</v>
-      </c>
-      <c r="F334" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="335" spans="1:8">
-      <c r="A335" t="s">
-        <v>716</v>
-      </c>
-      <c r="B335" t="s">
-        <v>306</v>
-      </c>
-      <c r="C335">
-        <v>2</v>
-      </c>
-      <c r="D335" t="s">
-        <v>717</v>
-      </c>
-      <c r="E335" t="s">
-        <v>718</v>
-      </c>
-      <c r="G335" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="336" spans="1:8">
-      <c r="A336" t="s">
-        <v>716</v>
-      </c>
-      <c r="B336" t="s">
-        <v>304</v>
-      </c>
-      <c r="C336">
-        <v>2</v>
-      </c>
-      <c r="D336" t="s">
-        <v>305</v>
-      </c>
-      <c r="E336" t="s">
-        <v>719</v>
-      </c>
-      <c r="G336" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="337" spans="1:7">
-      <c r="A337" t="s">
-        <v>716</v>
-      </c>
-      <c r="B337" t="s">
-        <v>720</v>
-      </c>
-      <c r="C337">
-        <v>3</v>
-      </c>
-      <c r="D337" t="s">
-        <v>721</v>
-      </c>
-      <c r="E337" t="s">
-        <v>722</v>
-      </c>
-      <c r="G337" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="338" spans="1:7">
-      <c r="A338" t="s">
-        <v>716</v>
-      </c>
-      <c r="B338" t="s">
-        <v>723</v>
-      </c>
-      <c r="C338">
-        <v>3</v>
-      </c>
-      <c r="D338" t="s">
-        <v>724</v>
-      </c>
-      <c r="F338" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="339" spans="1:7">
-      <c r="A339" t="s">
-        <v>716</v>
-      </c>
-      <c r="B339" t="s">
-        <v>725</v>
-      </c>
-      <c r="C339">
-        <v>3</v>
-      </c>
-      <c r="D339" t="s">
-        <v>726</v>
-      </c>
-      <c r="F339" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="340" spans="1:7">
-      <c r="A340" t="s">
-        <v>716</v>
-      </c>
-      <c r="B340" t="s">
-        <v>727</v>
-      </c>
-      <c r="C340">
-        <v>2</v>
-      </c>
-      <c r="D340" t="s">
-        <v>728</v>
-      </c>
-      <c r="F340" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="341" spans="1:7">
-      <c r="A341" t="s">
-        <v>716</v>
-      </c>
-      <c r="B341" t="s">
-        <v>729</v>
-      </c>
-      <c r="C341">
-        <v>3</v>
-      </c>
-      <c r="D341" t="s">
-        <v>730</v>
-      </c>
-      <c r="F341" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="342" spans="1:7">
-      <c r="A342" t="s">
-        <v>716</v>
-      </c>
-      <c r="B342" t="s">
-        <v>731</v>
-      </c>
-      <c r="C342">
-        <v>2</v>
-      </c>
-      <c r="D342" t="s">
-        <v>732</v>
-      </c>
-      <c r="F342" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="343" spans="1:7">
-      <c r="A343" t="s">
-        <v>716</v>
-      </c>
-      <c r="B343" t="s">
-        <v>110</v>
-      </c>
-      <c r="C343">
-        <v>2</v>
-      </c>
-      <c r="D343" t="s">
-        <v>111</v>
-      </c>
-      <c r="F343" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="344" spans="1:7">
-      <c r="A344" t="s">
-        <v>716</v>
-      </c>
-      <c r="B344" t="s">
-        <v>733</v>
-      </c>
-      <c r="C344">
-        <v>2</v>
-      </c>
-      <c r="D344" t="s">
-        <v>734</v>
-      </c>
-      <c r="F344" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="345" spans="1:7">
-      <c r="A345" t="s">
-        <v>716</v>
-      </c>
-      <c r="B345" t="s">
-        <v>735</v>
-      </c>
-      <c r="C345">
-        <v>2</v>
-      </c>
-      <c r="D345" t="s">
-        <v>736</v>
-      </c>
-      <c r="F345" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="346" spans="1:7">
-      <c r="A346" t="s">
-        <v>716</v>
-      </c>
-      <c r="B346" t="s">
-        <v>737</v>
-      </c>
-      <c r="C346">
-        <v>2</v>
-      </c>
-      <c r="D346" t="s">
-        <v>738</v>
-      </c>
-      <c r="F346" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="347" spans="1:7">
-      <c r="A347" t="s">
-        <v>739</v>
-      </c>
-      <c r="B347" t="s">
-        <v>55</v>
-      </c>
-      <c r="C347">
-        <v>2</v>
-      </c>
-      <c r="D347" t="s">
-        <v>740</v>
-      </c>
-      <c r="E347" t="s">
-        <v>741</v>
-      </c>
-      <c r="G347" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="348" spans="1:7">
-      <c r="A348" t="s">
-        <v>739</v>
-      </c>
-      <c r="B348" t="s">
-        <v>742</v>
-      </c>
-      <c r="C348">
-        <v>2</v>
-      </c>
-      <c r="D348" t="s">
-        <v>743</v>
-      </c>
-      <c r="E348" t="s">
-        <v>744</v>
-      </c>
-      <c r="G348" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="349" spans="1:7">
-      <c r="A349" t="s">
-        <v>739</v>
-      </c>
-      <c r="B349" t="s">
-        <v>745</v>
-      </c>
-      <c r="C349">
-        <v>2</v>
-      </c>
-      <c r="D349" t="s">
-        <v>746</v>
-      </c>
-      <c r="F349" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="350" spans="1:7">
-      <c r="A350" t="s">
-        <v>739</v>
-      </c>
-      <c r="B350" t="s">
-        <v>747</v>
-      </c>
-      <c r="C350">
-        <v>3</v>
-      </c>
-      <c r="D350" t="s">
-        <v>748</v>
-      </c>
-      <c r="F350" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="351" spans="1:7">
-      <c r="A351" t="s">
-        <v>739</v>
-      </c>
-      <c r="B351" t="s">
-        <v>749</v>
-      </c>
-      <c r="C351">
-        <v>3</v>
-      </c>
-      <c r="D351" t="s">
-        <v>750</v>
-      </c>
-      <c r="E351" t="s">
-        <v>751</v>
-      </c>
-      <c r="G351" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="352" spans="1:7">
-      <c r="A352" t="s">
-        <v>739</v>
-      </c>
-      <c r="B352" t="s">
-        <v>752</v>
-      </c>
-      <c r="C352">
-        <v>2</v>
-      </c>
-      <c r="D352" t="s">
-        <v>753</v>
-      </c>
-      <c r="F352" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="353" spans="1:8">
-      <c r="A353" t="s">
-        <v>739</v>
-      </c>
-      <c r="B353" t="s">
-        <v>754</v>
-      </c>
-      <c r="C353">
-        <v>3</v>
-      </c>
-      <c r="D353" t="s">
-        <v>755</v>
-      </c>
-      <c r="F353" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="354" spans="1:8">
-      <c r="A354" t="s">
-        <v>739</v>
-      </c>
-      <c r="B354" t="s">
-        <v>337</v>
-      </c>
-      <c r="C354">
-        <v>3</v>
-      </c>
-      <c r="D354" t="s">
-        <v>338</v>
-      </c>
-      <c r="F354" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="355" spans="1:8">
-      <c r="A355" t="s">
-        <v>739</v>
-      </c>
-      <c r="B355" t="s">
-        <v>756</v>
-      </c>
-      <c r="C355">
-        <v>2</v>
-      </c>
-      <c r="D355" t="s">
-        <v>757</v>
-      </c>
-      <c r="F355" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="356" spans="1:8">
-      <c r="A356" t="s">
-        <v>739</v>
-      </c>
-      <c r="B356" t="s">
-        <v>559</v>
-      </c>
-      <c r="C356">
-        <v>2</v>
-      </c>
-      <c r="D356" t="s">
-        <v>560</v>
-      </c>
-      <c r="F356" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="357" spans="1:8">
-      <c r="A357" t="s">
-        <v>739</v>
-      </c>
-      <c r="B357" t="s">
-        <v>120</v>
-      </c>
-      <c r="C357">
-        <v>2</v>
-      </c>
-      <c r="D357" t="s">
-        <v>119</v>
-      </c>
-      <c r="F357" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="358" spans="1:8">
-      <c r="A358" t="s">
-        <v>739</v>
-      </c>
-      <c r="B358" t="s">
-        <v>758</v>
-      </c>
-      <c r="C358">
-        <v>2</v>
-      </c>
-      <c r="D358" t="s">
-        <v>759</v>
-      </c>
-      <c r="F358" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="359" spans="1:8">
-      <c r="A359" t="s">
-        <v>760</v>
-      </c>
-      <c r="B359" t="s">
-        <v>761</v>
-      </c>
-      <c r="C359">
-        <v>2</v>
-      </c>
-      <c r="D359" t="s">
-        <v>762</v>
-      </c>
-      <c r="F359" t="s">
-        <v>763</v>
-      </c>
-      <c r="H359" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="360" spans="1:8">
-      <c r="A360" t="s">
-        <v>760</v>
-      </c>
-      <c r="B360" t="s">
-        <v>85</v>
-      </c>
-      <c r="C360">
-        <v>2</v>
-      </c>
-      <c r="D360" t="s">
-        <v>764</v>
-      </c>
-      <c r="E360" t="s">
-        <v>765</v>
-      </c>
-      <c r="G360" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="361" spans="1:8">
-      <c r="A361" t="s">
-        <v>760</v>
-      </c>
-      <c r="B361" t="s">
-        <v>95</v>
-      </c>
-      <c r="C361">
-        <v>3</v>
-      </c>
-      <c r="D361" t="s">
-        <v>96</v>
-      </c>
-      <c r="E361" t="s">
-        <v>97</v>
-      </c>
-      <c r="G361" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="362" spans="1:8">
-      <c r="A362" t="s">
-        <v>760</v>
-      </c>
-      <c r="B362" t="s">
-        <v>114</v>
-      </c>
-      <c r="C362">
-        <v>3</v>
-      </c>
-      <c r="D362" t="s">
-        <v>112</v>
-      </c>
-      <c r="E362" t="s">
-        <v>766</v>
-      </c>
-      <c r="G362" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="363" spans="1:8">
-      <c r="A363" t="s">
-        <v>760</v>
-      </c>
-      <c r="B363" t="s">
-        <v>104</v>
-      </c>
-      <c r="C363">
-        <v>2</v>
-      </c>
-      <c r="D363" t="s">
-        <v>106</v>
-      </c>
-      <c r="E363" t="s">
-        <v>105</v>
-      </c>
-      <c r="F363" t="s">
-        <v>767</v>
-      </c>
-      <c r="G363" t="s">
-        <v>768</v>
-      </c>
-      <c r="H363" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="364" spans="1:8">
-      <c r="A364" t="s">
-        <v>760</v>
-      </c>
-      <c r="B364" t="s">
-        <v>98</v>
-      </c>
-      <c r="C364">
-        <v>2</v>
-      </c>
-      <c r="D364" t="s">
-        <v>99</v>
-      </c>
-      <c r="E364" t="s">
-        <v>769</v>
-      </c>
-      <c r="G364" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="365" spans="1:8">
-      <c r="A365" t="s">
-        <v>760</v>
-      </c>
-      <c r="B365" t="s">
-        <v>86</v>
-      </c>
-      <c r="C365">
-        <v>2</v>
-      </c>
-      <c r="D365" t="s">
-        <v>770</v>
-      </c>
-      <c r="F365" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="366" spans="1:8">
-      <c r="A366" t="s">
-        <v>760</v>
-      </c>
-      <c r="B366" t="s">
-        <v>372</v>
-      </c>
-      <c r="C366">
-        <v>2</v>
-      </c>
-      <c r="D366" t="s">
-        <v>44</v>
-      </c>
-      <c r="E366" t="s">
-        <v>427</v>
-      </c>
-      <c r="G366" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="367" spans="1:8">
-      <c r="A367" t="s">
-        <v>760</v>
-      </c>
-      <c r="B367" t="s">
-        <v>771</v>
-      </c>
-      <c r="C367">
-        <v>2</v>
-      </c>
-      <c r="D367" t="s">
-        <v>772</v>
-      </c>
-      <c r="F367" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="368" spans="1:8">
-      <c r="A368" t="s">
-        <v>760</v>
-      </c>
-      <c r="B368" t="s">
-        <v>773</v>
-      </c>
-      <c r="C368">
-        <v>3</v>
-      </c>
-      <c r="D368" t="s">
-        <v>774</v>
-      </c>
-      <c r="E368" t="s">
-        <v>775</v>
-      </c>
-      <c r="G368" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="369" spans="1:7">
-      <c r="A369" t="s">
-        <v>776</v>
-      </c>
-      <c r="B369" t="s">
-        <v>355</v>
-      </c>
-      <c r="C369">
-        <v>2</v>
-      </c>
-      <c r="D369" t="s">
-        <v>777</v>
-      </c>
-      <c r="E369" t="s">
-        <v>778</v>
-      </c>
-      <c r="G369" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="370" spans="1:7">
-      <c r="A370" t="s">
-        <v>776</v>
-      </c>
-      <c r="B370" t="s">
-        <v>779</v>
-      </c>
-      <c r="C370">
-        <v>3</v>
-      </c>
-      <c r="D370" t="s">
-        <v>780</v>
-      </c>
-      <c r="E370" t="s">
-        <v>781</v>
-      </c>
-      <c r="G370" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="371" spans="1:7">
-      <c r="A371" t="s">
-        <v>776</v>
-      </c>
-      <c r="B371" t="s">
-        <v>358</v>
-      </c>
-      <c r="C371">
-        <v>3</v>
-      </c>
-      <c r="D371" t="s">
-        <v>359</v>
-      </c>
-      <c r="F371" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="372" spans="1:7">
-      <c r="A372" t="s">
-        <v>776</v>
-      </c>
-      <c r="B372" t="s">
-        <v>782</v>
-      </c>
-      <c r="C372">
-        <v>3</v>
-      </c>
-      <c r="D372" t="s">
-        <v>783</v>
-      </c>
-      <c r="F372" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="373" spans="1:7">
-      <c r="A373" t="s">
-        <v>776</v>
-      </c>
-      <c r="B373" t="s">
-        <v>784</v>
-      </c>
-      <c r="C373">
-        <v>2</v>
-      </c>
-      <c r="D373" t="s">
-        <v>785</v>
-      </c>
-      <c r="E373" t="s">
-        <v>786</v>
-      </c>
-      <c r="G373" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="374" spans="1:7">
-      <c r="A374" t="s">
-        <v>776</v>
-      </c>
-      <c r="B374" t="s">
-        <v>365</v>
-      </c>
-      <c r="C374">
-        <v>3</v>
-      </c>
-      <c r="D374" t="s">
-        <v>366</v>
-      </c>
-      <c r="F374" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="375" spans="1:7">
-      <c r="A375" t="s">
-        <v>776</v>
-      </c>
-      <c r="B375" t="s">
-        <v>360</v>
-      </c>
-      <c r="C375">
-        <v>3</v>
-      </c>
-      <c r="D375" t="s">
-        <v>361</v>
-      </c>
-      <c r="F375" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="376" spans="1:7">
-      <c r="A376" t="s">
-        <v>776</v>
-      </c>
-      <c r="B376" t="s">
-        <v>367</v>
-      </c>
-      <c r="C376">
-        <v>3</v>
-      </c>
-      <c r="D376" t="s">
-        <v>368</v>
-      </c>
-      <c r="E376" t="s">
-        <v>369</v>
-      </c>
-      <c r="G376" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="377" spans="1:7">
-      <c r="A377" t="s">
-        <v>776</v>
-      </c>
-      <c r="B377" t="s">
-        <v>370</v>
-      </c>
-      <c r="C377">
-        <v>2</v>
-      </c>
-      <c r="D377" t="s">
-        <v>787</v>
-      </c>
-      <c r="F377" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="378" spans="1:7">
-      <c r="A378" t="s">
-        <v>776</v>
-      </c>
-      <c r="B378" t="s">
-        <v>788</v>
-      </c>
-      <c r="C378">
-        <v>2</v>
-      </c>
-      <c r="D378" t="s">
-        <v>789</v>
-      </c>
-      <c r="E378" t="s">
-        <v>790</v>
-      </c>
-      <c r="G378" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="379" spans="1:7">
-      <c r="A379" t="s">
-        <v>791</v>
-      </c>
-      <c r="B379" t="s">
-        <v>88</v>
-      </c>
-      <c r="C379">
-        <v>2</v>
-      </c>
-      <c r="D379" t="s">
-        <v>792</v>
-      </c>
-      <c r="E379" t="s">
-        <v>793</v>
-      </c>
-      <c r="G379" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="380" spans="1:7">
-      <c r="A380" t="s">
-        <v>791</v>
-      </c>
-      <c r="B380" t="s">
-        <v>794</v>
-      </c>
-      <c r="C380">
-        <v>2</v>
-      </c>
-      <c r="D380" t="s">
-        <v>795</v>
-      </c>
-      <c r="F380" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="381" spans="1:7">
-      <c r="A381" t="s">
-        <v>791</v>
-      </c>
-      <c r="B381" t="s">
-        <v>796</v>
-      </c>
-      <c r="C381">
-        <v>3</v>
-      </c>
-      <c r="D381" t="s">
-        <v>797</v>
-      </c>
-      <c r="E381" t="s">
-        <v>798</v>
-      </c>
-      <c r="G381" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="382" spans="1:7">
-      <c r="A382" t="s">
-        <v>791</v>
-      </c>
-      <c r="B382" t="s">
-        <v>799</v>
-      </c>
-      <c r="C382">
-        <v>3</v>
-      </c>
-      <c r="D382" t="s">
-        <v>800</v>
-      </c>
-      <c r="F382" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="383" spans="1:7">
-      <c r="A383" t="s">
-        <v>791</v>
-      </c>
-      <c r="B383" t="s">
-        <v>543</v>
-      </c>
-      <c r="C383">
-        <v>3</v>
-      </c>
-      <c r="D383" t="s">
-        <v>542</v>
-      </c>
-      <c r="F383" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="384" spans="1:7">
-      <c r="A384" t="s">
-        <v>791</v>
-      </c>
-      <c r="B384" t="s">
-        <v>801</v>
-      </c>
-      <c r="C384">
-        <v>3</v>
-      </c>
-      <c r="D384" t="s">
-        <v>802</v>
-      </c>
-      <c r="E384" t="s">
-        <v>803</v>
-      </c>
-      <c r="G384" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="385" spans="1:8">
-      <c r="A385" t="s">
-        <v>791</v>
-      </c>
-      <c r="B385" t="s">
-        <v>754</v>
-      </c>
-      <c r="C385">
-        <v>3</v>
-      </c>
-      <c r="D385" t="s">
-        <v>755</v>
-      </c>
-      <c r="E385" t="s">
-        <v>804</v>
-      </c>
-      <c r="G385" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="386" spans="1:8">
-      <c r="A386" t="s">
-        <v>791</v>
-      </c>
-      <c r="B386" t="s">
-        <v>805</v>
-      </c>
-      <c r="C386">
-        <v>3</v>
-      </c>
-      <c r="D386" t="s">
-        <v>806</v>
-      </c>
-      <c r="E386" t="s">
-        <v>807</v>
-      </c>
-      <c r="F386" t="s">
-        <v>808</v>
-      </c>
-      <c r="G386" t="s">
-        <v>809</v>
-      </c>
-      <c r="H386" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="387" spans="1:8">
-      <c r="A387" t="s">
-        <v>791</v>
-      </c>
-      <c r="B387" t="s">
-        <v>339</v>
-      </c>
-      <c r="C387">
-        <v>3</v>
-      </c>
-      <c r="D387" t="s">
-        <v>340</v>
-      </c>
-      <c r="F387" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="388" spans="1:8">
-      <c r="A388" t="s">
-        <v>791</v>
-      </c>
-      <c r="B388" t="s">
-        <v>120</v>
-      </c>
-      <c r="C388">
-        <v>2</v>
-      </c>
-      <c r="D388" t="s">
-        <v>179</v>
-      </c>
-      <c r="F388" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="389" spans="1:8">
-      <c r="A389" t="s">
-        <v>810</v>
-      </c>
-      <c r="B389" t="s">
-        <v>811</v>
-      </c>
-      <c r="C389">
-        <v>2</v>
-      </c>
-      <c r="D389" t="s">
-        <v>812</v>
-      </c>
-      <c r="E389" t="s">
-        <v>813</v>
-      </c>
-      <c r="G389" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="390" spans="1:8">
-      <c r="A390" t="s">
-        <v>810</v>
-      </c>
-      <c r="B390" t="s">
-        <v>814</v>
-      </c>
-      <c r="C390">
-        <v>3</v>
-      </c>
-      <c r="D390" t="s">
-        <v>815</v>
-      </c>
-      <c r="E390" t="s">
-        <v>816</v>
-      </c>
-      <c r="G390" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="391" spans="1:8">
-      <c r="A391" t="s">
-        <v>810</v>
-      </c>
-      <c r="B391" t="s">
-        <v>154</v>
-      </c>
-      <c r="C391">
-        <v>2</v>
-      </c>
-      <c r="D391" t="s">
-        <v>155</v>
-      </c>
-      <c r="E391" t="s">
-        <v>156</v>
-      </c>
-      <c r="G391" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="392" spans="1:8">
-      <c r="A392" t="s">
-        <v>810</v>
-      </c>
-      <c r="B392" t="s">
-        <v>817</v>
-      </c>
-      <c r="C392">
-        <v>3</v>
-      </c>
-      <c r="D392" t="s">
-        <v>818</v>
-      </c>
-      <c r="F392" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="393" spans="1:8">
-      <c r="A393" t="s">
-        <v>810</v>
-      </c>
-      <c r="B393" t="s">
-        <v>819</v>
-      </c>
-      <c r="C393">
-        <v>3</v>
-      </c>
-      <c r="D393" t="s">
-        <v>820</v>
-      </c>
       <c r="F393" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="394" spans="1:8">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7">
       <c r="A394" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="B394" t="s">
-        <v>821</v>
+        <v>162</v>
       </c>
       <c r="C394">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D394" t="s">
-        <v>822</v>
+        <v>163</v>
       </c>
       <c r="F394" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="395" spans="1:8">
+    <row r="395" spans="1:7">
       <c r="A395" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="B395" t="s">
-        <v>48</v>
+        <v>837</v>
       </c>
       <c r="C395">
         <v>2</v>
       </c>
       <c r="D395" t="s">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="E395" t="s">
-        <v>823</v>
+        <v>838</v>
       </c>
       <c r="G395" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="396" spans="1:8">
+    <row r="396" spans="1:7">
       <c r="A396" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="B396" t="s">
-        <v>824</v>
+        <v>839</v>
       </c>
       <c r="C396">
         <v>2</v>
       </c>
       <c r="D396" t="s">
-        <v>825</v>
-      </c>
-      <c r="F396" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="397" spans="1:8">
+        <v>496</v>
+      </c>
+      <c r="E396" t="s">
+        <v>498</v>
+      </c>
+      <c r="G396" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7">
       <c r="A397" t="s">
-        <v>810</v>
+        <v>840</v>
       </c>
       <c r="B397" t="s">
-        <v>826</v>
+        <v>841</v>
       </c>
       <c r="C397">
         <v>2</v>
       </c>
       <c r="D397" t="s">
-        <v>827</v>
+        <v>842</v>
       </c>
       <c r="F397" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="398" spans="1:8">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7">
       <c r="A398" t="s">
-        <v>810</v>
+        <v>840</v>
       </c>
       <c r="B398" t="s">
-        <v>828</v>
+        <v>50</v>
       </c>
       <c r="C398">
         <v>2</v>
       </c>
       <c r="D398" t="s">
-        <v>829</v>
-      </c>
-      <c r="E398" t="s">
-        <v>830</v>
-      </c>
-      <c r="G398" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="399" spans="1:8">
+        <v>53</v>
+      </c>
+      <c r="F398" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7">
       <c r="A399" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="B399" t="s">
-        <v>453</v>
+        <v>843</v>
       </c>
       <c r="C399">
         <v>2</v>
       </c>
       <c r="D399" t="s">
-        <v>454</v>
-      </c>
-      <c r="E399" t="s">
-        <v>455</v>
-      </c>
-      <c r="G399" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="400" spans="1:8">
+        <v>844</v>
+      </c>
+      <c r="F399" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7">
       <c r="A400" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="B400" t="s">
-        <v>157</v>
+        <v>845</v>
       </c>
       <c r="C400">
         <v>3</v>
       </c>
       <c r="D400" t="s">
-        <v>158</v>
-      </c>
-      <c r="E400" t="s">
-        <v>832</v>
-      </c>
-      <c r="G400" t="s">
+        <v>846</v>
+      </c>
+      <c r="F400" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="401" spans="1:7">
       <c r="A401" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="B401" t="s">
-        <v>154</v>
+        <v>847</v>
       </c>
       <c r="C401">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D401" t="s">
-        <v>155</v>
+        <v>848</v>
       </c>
       <c r="F401" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="402" spans="1:7">
       <c r="A402" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="B402" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="C402">
         <v>2</v>
       </c>
       <c r="D402" t="s">
-        <v>479</v>
+        <v>849</v>
       </c>
       <c r="F402" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="403" spans="1:7">
       <c r="A403" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="B403" t="s">
-        <v>833</v>
+        <v>850</v>
       </c>
       <c r="C403">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D403" t="s">
-        <v>834</v>
-      </c>
-      <c r="E403" t="s">
-        <v>835</v>
-      </c>
-      <c r="G403" t="s">
+        <v>851</v>
+      </c>
+      <c r="F403" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="404" spans="1:7">
       <c r="A404" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="B404" t="s">
-        <v>836</v>
+        <v>813</v>
       </c>
       <c r="C404">
         <v>3</v>
       </c>
       <c r="D404" t="s">
-        <v>837</v>
+        <v>814</v>
       </c>
       <c r="F404" t="s">
         <v>39</v>
@@ -11431,141 +11428,138 @@
     </row>
     <row r="405" spans="1:7">
       <c r="A405" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="B405" t="s">
-        <v>296</v>
+        <v>852</v>
       </c>
       <c r="C405">
         <v>3</v>
       </c>
       <c r="D405" t="s">
-        <v>679</v>
+        <v>825</v>
       </c>
       <c r="F405" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
     </row>
     <row r="406" spans="1:7">
       <c r="A406" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="B406" t="s">
-        <v>162</v>
+        <v>48</v>
       </c>
       <c r="C406">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D406" t="s">
-        <v>163</v>
-      </c>
-      <c r="F406" t="s">
+        <v>448</v>
+      </c>
+      <c r="E406" t="s">
+        <v>853</v>
+      </c>
+      <c r="G406" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="407" spans="1:7">
       <c r="A407" t="s">
-        <v>831</v>
+        <v>854</v>
       </c>
       <c r="B407" t="s">
-        <v>838</v>
+        <v>855</v>
       </c>
       <c r="C407">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D407" t="s">
-        <v>480</v>
-      </c>
-      <c r="E407" t="s">
-        <v>839</v>
-      </c>
-      <c r="G407" t="s">
-        <v>39</v>
+        <v>856</v>
+      </c>
+      <c r="F407" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="408" spans="1:7">
       <c r="A408" t="s">
-        <v>831</v>
+        <v>854</v>
       </c>
       <c r="B408" t="s">
-        <v>840</v>
+        <v>857</v>
       </c>
       <c r="C408">
         <v>2</v>
       </c>
       <c r="D408" t="s">
-        <v>496</v>
-      </c>
-      <c r="E408" t="s">
-        <v>498</v>
-      </c>
-      <c r="G408" t="s">
-        <v>39</v>
+        <v>858</v>
+      </c>
+      <c r="F408" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="409" spans="1:7">
       <c r="A409" t="s">
-        <v>841</v>
+        <v>854</v>
       </c>
       <c r="B409" t="s">
-        <v>842</v>
+        <v>859</v>
       </c>
       <c r="C409">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D409" t="s">
-        <v>843</v>
+        <v>860</v>
       </c>
       <c r="F409" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="410" spans="1:7">
       <c r="A410" t="s">
-        <v>841</v>
+        <v>854</v>
       </c>
       <c r="B410" t="s">
-        <v>50</v>
+        <v>861</v>
       </c>
       <c r="C410">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D410" t="s">
-        <v>53</v>
+        <v>862</v>
       </c>
       <c r="F410" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="411" spans="1:7">
       <c r="A411" t="s">
-        <v>841</v>
+        <v>854</v>
       </c>
       <c r="B411" t="s">
-        <v>844</v>
+        <v>863</v>
       </c>
       <c r="C411">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D411" t="s">
-        <v>845</v>
+        <v>864</v>
       </c>
       <c r="F411" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="412" spans="1:7">
       <c r="A412" t="s">
-        <v>841</v>
+        <v>854</v>
       </c>
       <c r="B412" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="C412">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D412" t="s">
-        <v>847</v>
+        <v>866</v>
       </c>
       <c r="F412" t="s">
         <v>118</v>
@@ -11573,16 +11567,16 @@
     </row>
     <row r="413" spans="1:7">
       <c r="A413" t="s">
-        <v>841</v>
+        <v>854</v>
       </c>
       <c r="B413" t="s">
-        <v>848</v>
+        <v>867</v>
       </c>
       <c r="C413">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D413" t="s">
-        <v>849</v>
+        <v>868</v>
       </c>
       <c r="F413" t="s">
         <v>118</v>
@@ -11590,33 +11584,33 @@
     </row>
     <row r="414" spans="1:7">
       <c r="A414" t="s">
-        <v>841</v>
+        <v>854</v>
       </c>
       <c r="B414" t="s">
-        <v>76</v>
+        <v>208</v>
       </c>
       <c r="C414">
         <v>2</v>
       </c>
       <c r="D414" t="s">
-        <v>850</v>
+        <v>234</v>
       </c>
       <c r="F414" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
     </row>
     <row r="415" spans="1:7">
       <c r="A415" t="s">
-        <v>841</v>
+        <v>854</v>
       </c>
       <c r="B415" t="s">
-        <v>851</v>
+        <v>869</v>
       </c>
       <c r="C415">
         <v>2</v>
       </c>
       <c r="D415" t="s">
-        <v>852</v>
+        <v>870</v>
       </c>
       <c r="F415" t="s">
         <v>118</v>
@@ -11624,70 +11618,73 @@
     </row>
     <row r="416" spans="1:7">
       <c r="A416" t="s">
-        <v>841</v>
+        <v>854</v>
       </c>
       <c r="B416" t="s">
-        <v>814</v>
+        <v>871</v>
       </c>
       <c r="C416">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D416" t="s">
-        <v>815</v>
+        <v>872</v>
       </c>
       <c r="F416" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="417" spans="1:7">
       <c r="A417" t="s">
-        <v>841</v>
+        <v>873</v>
       </c>
       <c r="B417" t="s">
-        <v>853</v>
+        <v>874</v>
       </c>
       <c r="C417">
         <v>3</v>
       </c>
       <c r="D417" t="s">
-        <v>826</v>
-      </c>
-      <c r="F417" t="s">
-        <v>39</v>
+        <v>875</v>
+      </c>
+      <c r="E417" t="s">
+        <v>876</v>
+      </c>
+      <c r="G417" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="418" spans="1:7">
       <c r="A418" t="s">
-        <v>841</v>
+        <v>873</v>
       </c>
       <c r="B418" t="s">
-        <v>48</v>
+        <v>877</v>
       </c>
       <c r="C418">
         <v>2</v>
       </c>
       <c r="D418" t="s">
-        <v>448</v>
+        <v>878</v>
       </c>
       <c r="E418" t="s">
-        <v>854</v>
+        <v>879</v>
       </c>
       <c r="G418" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="419" spans="1:7">
       <c r="A419" t="s">
-        <v>855</v>
+        <v>873</v>
       </c>
       <c r="B419" t="s">
-        <v>856</v>
+        <v>880</v>
       </c>
       <c r="C419">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D419" t="s">
-        <v>857</v>
+        <v>881</v>
       </c>
       <c r="F419" t="s">
         <v>118</v>
@@ -11695,16 +11692,16 @@
     </row>
     <row r="420" spans="1:7">
       <c r="A420" t="s">
-        <v>855</v>
+        <v>873</v>
       </c>
       <c r="B420" t="s">
-        <v>858</v>
+        <v>882</v>
       </c>
       <c r="C420">
         <v>2</v>
       </c>
       <c r="D420" t="s">
-        <v>859</v>
+        <v>883</v>
       </c>
       <c r="F420" t="s">
         <v>54</v>
@@ -11712,33 +11709,36 @@
     </row>
     <row r="421" spans="1:7">
       <c r="A421" t="s">
-        <v>855</v>
+        <v>873</v>
       </c>
       <c r="B421" t="s">
-        <v>860</v>
+        <v>884</v>
       </c>
       <c r="C421">
         <v>3</v>
       </c>
       <c r="D421" t="s">
-        <v>861</v>
-      </c>
-      <c r="F421" t="s">
+        <v>885</v>
+      </c>
+      <c r="E421" t="s">
+        <v>886</v>
+      </c>
+      <c r="G421" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="422" spans="1:7">
       <c r="A422" t="s">
-        <v>855</v>
+        <v>873</v>
       </c>
       <c r="B422" t="s">
-        <v>862</v>
+        <v>887</v>
       </c>
       <c r="C422">
         <v>3</v>
       </c>
       <c r="D422" t="s">
-        <v>863</v>
+        <v>888</v>
       </c>
       <c r="F422" t="s">
         <v>39</v>
@@ -11746,33 +11746,33 @@
     </row>
     <row r="423" spans="1:7">
       <c r="A423" t="s">
-        <v>855</v>
+        <v>873</v>
       </c>
       <c r="B423" t="s">
-        <v>864</v>
+        <v>535</v>
       </c>
       <c r="C423">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D423" t="s">
-        <v>865</v>
+        <v>208</v>
       </c>
       <c r="F423" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="424" spans="1:7">
       <c r="A424" t="s">
-        <v>855</v>
+        <v>873</v>
       </c>
       <c r="B424" t="s">
-        <v>866</v>
+        <v>889</v>
       </c>
       <c r="C424">
         <v>2</v>
       </c>
       <c r="D424" t="s">
-        <v>867</v>
+        <v>890</v>
       </c>
       <c r="F424" t="s">
         <v>118</v>
@@ -11780,16 +11780,16 @@
     </row>
     <row r="425" spans="1:7">
       <c r="A425" t="s">
-        <v>855</v>
+        <v>873</v>
       </c>
       <c r="B425" t="s">
-        <v>868</v>
+        <v>891</v>
       </c>
       <c r="C425">
         <v>2</v>
       </c>
       <c r="D425" t="s">
-        <v>869</v>
+        <v>892</v>
       </c>
       <c r="F425" t="s">
         <v>118</v>
@@ -11797,50 +11797,53 @@
     </row>
     <row r="426" spans="1:7">
       <c r="A426" t="s">
-        <v>855</v>
+        <v>873</v>
       </c>
       <c r="B426" t="s">
-        <v>208</v>
+        <v>893</v>
       </c>
       <c r="C426">
         <v>2</v>
       </c>
       <c r="D426" t="s">
-        <v>234</v>
+        <v>894</v>
       </c>
       <c r="F426" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="427" spans="1:7">
       <c r="A427" t="s">
-        <v>855</v>
+        <v>895</v>
       </c>
       <c r="B427" t="s">
-        <v>870</v>
+        <v>896</v>
       </c>
       <c r="C427">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D427" t="s">
-        <v>871</v>
-      </c>
-      <c r="F427" t="s">
+        <v>897</v>
+      </c>
+      <c r="E427" t="s">
+        <v>898</v>
+      </c>
+      <c r="G427" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="428" spans="1:7">
       <c r="A428" t="s">
-        <v>855</v>
+        <v>895</v>
       </c>
       <c r="B428" t="s">
-        <v>872</v>
+        <v>899</v>
       </c>
       <c r="C428">
         <v>2</v>
       </c>
       <c r="D428" t="s">
-        <v>873</v>
+        <v>900</v>
       </c>
       <c r="F428" t="s">
         <v>54</v>
@@ -11848,127 +11851,121 @@
     </row>
     <row r="429" spans="1:7">
       <c r="A429" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="B429" t="s">
-        <v>875</v>
+        <v>901</v>
       </c>
       <c r="C429">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D429" t="s">
-        <v>876</v>
-      </c>
-      <c r="E429" t="s">
-        <v>877</v>
-      </c>
-      <c r="G429" t="s">
+        <v>902</v>
+      </c>
+      <c r="F429" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="430" spans="1:7">
       <c r="A430" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="B430" t="s">
-        <v>878</v>
+        <v>903</v>
       </c>
       <c r="C430">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D430" t="s">
-        <v>879</v>
-      </c>
-      <c r="E430" t="s">
-        <v>880</v>
-      </c>
-      <c r="G430" t="s">
-        <v>54</v>
+        <v>904</v>
+      </c>
+      <c r="F430" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="431" spans="1:7">
       <c r="A431" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="B431" t="s">
-        <v>881</v>
+        <v>905</v>
       </c>
       <c r="C431">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D431" t="s">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="F431" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
     </row>
     <row r="432" spans="1:7">
       <c r="A432" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="B432" t="s">
-        <v>883</v>
+        <v>907</v>
       </c>
       <c r="C432">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D432" t="s">
-        <v>884</v>
-      </c>
-      <c r="F432" t="s">
-        <v>54</v>
+        <v>908</v>
+      </c>
+      <c r="E432" t="s">
+        <v>909</v>
+      </c>
+      <c r="G432" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="433" spans="1:7">
       <c r="A433" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="B433" t="s">
-        <v>885</v>
+        <v>910</v>
       </c>
       <c r="C433">
         <v>3</v>
       </c>
       <c r="D433" t="s">
-        <v>886</v>
-      </c>
-      <c r="E433" t="s">
-        <v>887</v>
-      </c>
-      <c r="G433" t="s">
+        <v>911</v>
+      </c>
+      <c r="F433" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="434" spans="1:7">
       <c r="A434" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="B434" t="s">
-        <v>888</v>
+        <v>912</v>
       </c>
       <c r="C434">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D434" t="s">
-        <v>889</v>
+        <v>913</v>
       </c>
       <c r="F434" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="435" spans="1:7">
       <c r="A435" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="B435" t="s">
-        <v>535</v>
+        <v>914</v>
       </c>
       <c r="C435">
         <v>2</v>
       </c>
       <c r="D435" t="s">
-        <v>208</v>
+        <v>915</v>
       </c>
       <c r="F435" t="s">
         <v>54</v>
@@ -11976,104 +11973,107 @@
     </row>
     <row r="436" spans="1:7">
       <c r="A436" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="B436" t="s">
-        <v>890</v>
+        <v>48</v>
       </c>
       <c r="C436">
         <v>2</v>
       </c>
       <c r="D436" t="s">
-        <v>891</v>
-      </c>
-      <c r="F436" t="s">
-        <v>118</v>
+        <v>916</v>
+      </c>
+      <c r="E436" t="s">
+        <v>917</v>
+      </c>
+      <c r="G436" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="437" spans="1:7">
       <c r="A437" t="s">
-        <v>874</v>
+        <v>918</v>
       </c>
       <c r="B437" t="s">
-        <v>892</v>
+        <v>919</v>
       </c>
       <c r="C437">
         <v>2</v>
       </c>
       <c r="D437" t="s">
-        <v>893</v>
-      </c>
-      <c r="F437" t="s">
-        <v>118</v>
+        <v>920</v>
+      </c>
+      <c r="E437" t="s">
+        <v>407</v>
+      </c>
+      <c r="G437" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="438" spans="1:7">
       <c r="A438" t="s">
-        <v>874</v>
+        <v>918</v>
       </c>
       <c r="B438" t="s">
-        <v>894</v>
+        <v>921</v>
       </c>
       <c r="C438">
         <v>2</v>
       </c>
       <c r="D438" t="s">
-        <v>895</v>
+        <v>922</v>
       </c>
       <c r="F438" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="439" spans="1:7">
       <c r="A439" t="s">
-        <v>896</v>
+        <v>918</v>
       </c>
       <c r="B439" t="s">
-        <v>897</v>
+        <v>923</v>
       </c>
       <c r="C439">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D439" t="s">
-        <v>898</v>
-      </c>
-      <c r="E439" t="s">
-        <v>899</v>
-      </c>
-      <c r="G439" t="s">
+        <v>924</v>
+      </c>
+      <c r="F439" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="440" spans="1:7">
       <c r="A440" t="s">
-        <v>896</v>
+        <v>918</v>
       </c>
       <c r="B440" t="s">
-        <v>900</v>
+        <v>419</v>
       </c>
       <c r="C440">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D440" t="s">
-        <v>901</v>
+        <v>420</v>
       </c>
       <c r="F440" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="441" spans="1:7">
       <c r="A441" t="s">
-        <v>896</v>
+        <v>918</v>
       </c>
       <c r="B441" t="s">
-        <v>902</v>
+        <v>925</v>
       </c>
       <c r="C441">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D441" t="s">
-        <v>903</v>
+        <v>926</v>
       </c>
       <c r="F441" t="s">
         <v>118</v>
@@ -12081,178 +12081,172 @@
     </row>
     <row r="442" spans="1:7">
       <c r="A442" t="s">
-        <v>896</v>
+        <v>918</v>
       </c>
       <c r="B442" t="s">
-        <v>904</v>
+        <v>417</v>
       </c>
       <c r="C442">
         <v>3</v>
       </c>
       <c r="D442" t="s">
-        <v>905</v>
+        <v>418</v>
       </c>
       <c r="F442" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
     </row>
     <row r="443" spans="1:7">
       <c r="A443" t="s">
-        <v>896</v>
+        <v>918</v>
       </c>
       <c r="B443" t="s">
-        <v>906</v>
+        <v>597</v>
       </c>
       <c r="C443">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D443" t="s">
-        <v>907</v>
+        <v>927</v>
       </c>
       <c r="F443" t="s">
-        <v>39</v>
+        <v>118</v>
       </c>
     </row>
     <row r="444" spans="1:7">
       <c r="A444" t="s">
-        <v>896</v>
+        <v>918</v>
       </c>
       <c r="B444" t="s">
-        <v>908</v>
+        <v>176</v>
       </c>
       <c r="C444">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D444" t="s">
-        <v>909</v>
-      </c>
-      <c r="E444" t="s">
-        <v>910</v>
-      </c>
-      <c r="G444" t="s">
-        <v>39</v>
+        <v>928</v>
+      </c>
+      <c r="F444" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="445" spans="1:7">
       <c r="A445" t="s">
-        <v>896</v>
+        <v>918</v>
       </c>
       <c r="B445" t="s">
-        <v>911</v>
+        <v>427</v>
       </c>
       <c r="C445">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D445" t="s">
-        <v>912</v>
+        <v>429</v>
       </c>
       <c r="F445" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="446" spans="1:7">
       <c r="A446" t="s">
-        <v>896</v>
+        <v>918</v>
       </c>
       <c r="B446" t="s">
-        <v>913</v>
+        <v>929</v>
       </c>
       <c r="C446">
         <v>2</v>
       </c>
       <c r="D446" t="s">
-        <v>914</v>
+        <v>930</v>
       </c>
       <c r="F446" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="447" spans="1:7">
       <c r="A447" t="s">
-        <v>896</v>
+        <v>931</v>
       </c>
       <c r="B447" t="s">
-        <v>915</v>
+        <v>932</v>
       </c>
       <c r="C447">
         <v>2</v>
       </c>
       <c r="D447" t="s">
-        <v>916</v>
-      </c>
-      <c r="F447" t="s">
+        <v>645</v>
+      </c>
+      <c r="E447" t="s">
+        <v>933</v>
+      </c>
+      <c r="G447" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="448" spans="1:7">
       <c r="A448" t="s">
-        <v>896</v>
+        <v>931</v>
       </c>
       <c r="B448" t="s">
-        <v>48</v>
+        <v>934</v>
       </c>
       <c r="C448">
         <v>2</v>
       </c>
       <c r="D448" t="s">
-        <v>917</v>
-      </c>
-      <c r="E448" t="s">
-        <v>918</v>
-      </c>
-      <c r="G448" t="s">
-        <v>39</v>
+        <v>935</v>
+      </c>
+      <c r="F448" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="449" spans="1:7">
       <c r="A449" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="B449" t="s">
-        <v>920</v>
+        <v>936</v>
       </c>
       <c r="C449">
         <v>2</v>
       </c>
       <c r="D449" t="s">
-        <v>921</v>
-      </c>
-      <c r="E449" t="s">
-        <v>407</v>
-      </c>
-      <c r="G449" t="s">
+        <v>937</v>
+      </c>
+      <c r="F449" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="450" spans="1:7">
       <c r="A450" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="B450" t="s">
-        <v>922</v>
+        <v>938</v>
       </c>
       <c r="C450">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D450" t="s">
-        <v>923</v>
+        <v>939</v>
       </c>
       <c r="F450" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="451" spans="1:7">
       <c r="A451" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="B451" t="s">
-        <v>924</v>
+        <v>940</v>
       </c>
       <c r="C451">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D451" t="s">
-        <v>925</v>
+        <v>941</v>
       </c>
       <c r="F451" t="s">
         <v>118</v>
@@ -12260,16 +12254,16 @@
     </row>
     <row r="452" spans="1:7">
       <c r="A452" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="B452" t="s">
-        <v>419</v>
+        <v>942</v>
       </c>
       <c r="C452">
         <v>3</v>
       </c>
       <c r="D452" t="s">
-        <v>420</v>
+        <v>943</v>
       </c>
       <c r="F452" t="s">
         <v>118</v>
@@ -12277,16 +12271,16 @@
     </row>
     <row r="453" spans="1:7">
       <c r="A453" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="B453" t="s">
-        <v>926</v>
+        <v>944</v>
       </c>
       <c r="C453">
         <v>3</v>
       </c>
       <c r="D453" t="s">
-        <v>927</v>
+        <v>945</v>
       </c>
       <c r="F453" t="s">
         <v>118</v>
@@ -12294,16 +12288,16 @@
     </row>
     <row r="454" spans="1:7">
       <c r="A454" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="B454" t="s">
-        <v>417</v>
+        <v>946</v>
       </c>
       <c r="C454">
         <v>3</v>
       </c>
       <c r="D454" t="s">
-        <v>418</v>
+        <v>947</v>
       </c>
       <c r="F454" t="s">
         <v>39</v>
@@ -12311,50 +12305,50 @@
     </row>
     <row r="455" spans="1:7">
       <c r="A455" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="B455" t="s">
-        <v>598</v>
+        <v>948</v>
       </c>
       <c r="C455">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D455" t="s">
-        <v>928</v>
+        <v>949</v>
       </c>
       <c r="F455" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
     </row>
     <row r="456" spans="1:7">
       <c r="A456" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="B456" t="s">
-        <v>176</v>
+        <v>950</v>
       </c>
       <c r="C456">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D456" t="s">
-        <v>929</v>
+        <v>951</v>
       </c>
       <c r="F456" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
     </row>
     <row r="457" spans="1:7">
       <c r="A457" t="s">
-        <v>919</v>
+        <v>952</v>
       </c>
       <c r="B457" t="s">
-        <v>427</v>
+        <v>953</v>
       </c>
       <c r="C457">
         <v>2</v>
       </c>
       <c r="D457" t="s">
-        <v>429</v>
+        <v>954</v>
       </c>
       <c r="F457" t="s">
         <v>54</v>
@@ -12362,36 +12356,36 @@
     </row>
     <row r="458" spans="1:7">
       <c r="A458" t="s">
-        <v>919</v>
+        <v>952</v>
       </c>
       <c r="B458" t="s">
-        <v>930</v>
+        <v>955</v>
       </c>
       <c r="C458">
         <v>2</v>
       </c>
       <c r="D458" t="s">
-        <v>931</v>
+        <v>956</v>
       </c>
       <c r="F458" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="459" spans="1:7">
       <c r="A459" t="s">
-        <v>932</v>
+        <v>952</v>
       </c>
       <c r="B459" t="s">
-        <v>933</v>
+        <v>413</v>
       </c>
       <c r="C459">
         <v>2</v>
       </c>
       <c r="D459" t="s">
-        <v>646</v>
+        <v>414</v>
       </c>
       <c r="E459" t="s">
-        <v>934</v>
+        <v>957</v>
       </c>
       <c r="G459" t="s">
         <v>54</v>
@@ -12399,330 +12393,123 @@
     </row>
     <row r="460" spans="1:7">
       <c r="A460" t="s">
-        <v>932</v>
+        <v>952</v>
       </c>
       <c r="B460" t="s">
-        <v>935</v>
+        <v>958</v>
       </c>
       <c r="C460">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D460" t="s">
-        <v>936</v>
+        <v>959</v>
       </c>
       <c r="F460" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="461" spans="1:7">
       <c r="A461" t="s">
-        <v>932</v>
+        <v>952</v>
       </c>
       <c r="B461" t="s">
-        <v>937</v>
+        <v>960</v>
       </c>
       <c r="C461">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D461" t="s">
-        <v>938</v>
+        <v>961</v>
       </c>
       <c r="F461" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="462" spans="1:7">
       <c r="A462" t="s">
-        <v>932</v>
+        <v>952</v>
       </c>
       <c r="B462" t="s">
-        <v>939</v>
+        <v>962</v>
       </c>
       <c r="C462">
         <v>3</v>
       </c>
       <c r="D462" t="s">
-        <v>940</v>
-      </c>
-      <c r="F462" t="s">
+        <v>963</v>
+      </c>
+      <c r="E462" t="s">
+        <v>964</v>
+      </c>
+      <c r="G462" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="463" spans="1:7">
       <c r="A463" t="s">
-        <v>932</v>
+        <v>952</v>
       </c>
       <c r="B463" t="s">
-        <v>941</v>
+        <v>417</v>
       </c>
       <c r="C463">
         <v>3</v>
       </c>
       <c r="D463" t="s">
-        <v>942</v>
+        <v>418</v>
       </c>
       <c r="F463" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
     </row>
     <row r="464" spans="1:7">
       <c r="A464" t="s">
-        <v>932</v>
+        <v>952</v>
       </c>
       <c r="B464" t="s">
-        <v>943</v>
+        <v>965</v>
       </c>
       <c r="C464">
         <v>3</v>
       </c>
       <c r="D464" t="s">
-        <v>944</v>
+        <v>966</v>
       </c>
       <c r="F464" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="465" spans="1:7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="465" spans="1:6">
       <c r="A465" t="s">
-        <v>932</v>
+        <v>952</v>
       </c>
       <c r="B465" t="s">
-        <v>945</v>
+        <v>967</v>
       </c>
       <c r="C465">
         <v>3</v>
       </c>
       <c r="D465" t="s">
-        <v>946</v>
+        <v>968</v>
       </c>
       <c r="F465" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="466" spans="1:7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="466" spans="1:6">
       <c r="A466" t="s">
-        <v>932</v>
+        <v>952</v>
       </c>
       <c r="B466" t="s">
-        <v>947</v>
+        <v>969</v>
       </c>
       <c r="C466">
         <v>3</v>
       </c>
       <c r="D466" t="s">
-        <v>948</v>
+        <v>970</v>
       </c>
       <c r="F466" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="467" spans="1:7">
-      <c r="A467" t="s">
-        <v>932</v>
-      </c>
-      <c r="B467" t="s">
-        <v>949</v>
-      </c>
-      <c r="C467">
-        <v>3</v>
-      </c>
-      <c r="D467" t="s">
-        <v>950</v>
-      </c>
-      <c r="F467" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="468" spans="1:7">
-      <c r="A468" t="s">
-        <v>932</v>
-      </c>
-      <c r="B468" t="s">
-        <v>951</v>
-      </c>
-      <c r="C468">
-        <v>3</v>
-      </c>
-      <c r="D468" t="s">
-        <v>952</v>
-      </c>
-      <c r="F468" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="469" spans="1:7">
-      <c r="A469" t="s">
-        <v>953</v>
-      </c>
-      <c r="B469" t="s">
-        <v>954</v>
-      </c>
-      <c r="C469">
-        <v>2</v>
-      </c>
-      <c r="D469" t="s">
-        <v>955</v>
-      </c>
-      <c r="F469" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="470" spans="1:7">
-      <c r="A470" t="s">
-        <v>953</v>
-      </c>
-      <c r="B470" t="s">
-        <v>956</v>
-      </c>
-      <c r="C470">
-        <v>2</v>
-      </c>
-      <c r="D470" t="s">
-        <v>957</v>
-      </c>
-      <c r="F470" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="471" spans="1:7">
-      <c r="A471" t="s">
-        <v>953</v>
-      </c>
-      <c r="B471" t="s">
-        <v>413</v>
-      </c>
-      <c r="C471">
-        <v>2</v>
-      </c>
-      <c r="D471" t="s">
-        <v>414</v>
-      </c>
-      <c r="E471" t="s">
-        <v>958</v>
-      </c>
-      <c r="G471" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="472" spans="1:7">
-      <c r="A472" t="s">
-        <v>953</v>
-      </c>
-      <c r="B472" t="s">
-        <v>959</v>
-      </c>
-      <c r="C472">
-        <v>3</v>
-      </c>
-      <c r="D472" t="s">
-        <v>960</v>
-      </c>
-      <c r="F472" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="473" spans="1:7">
-      <c r="A473" t="s">
-        <v>953</v>
-      </c>
-      <c r="B473" t="s">
-        <v>961</v>
-      </c>
-      <c r="C473">
-        <v>3</v>
-      </c>
-      <c r="D473" t="s">
-        <v>962</v>
-      </c>
-      <c r="F473" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="474" spans="1:7">
-      <c r="A474" t="s">
-        <v>953</v>
-      </c>
-      <c r="B474" t="s">
-        <v>963</v>
-      </c>
-      <c r="C474">
-        <v>3</v>
-      </c>
-      <c r="D474" t="s">
-        <v>964</v>
-      </c>
-      <c r="E474" t="s">
-        <v>965</v>
-      </c>
-      <c r="G474" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="475" spans="1:7">
-      <c r="A475" t="s">
-        <v>953</v>
-      </c>
-      <c r="B475" t="s">
-        <v>417</v>
-      </c>
-      <c r="C475">
-        <v>3</v>
-      </c>
-      <c r="D475" t="s">
-        <v>418</v>
-      </c>
-      <c r="F475" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="476" spans="1:7">
-      <c r="A476" t="s">
-        <v>953</v>
-      </c>
-      <c r="B476" t="s">
-        <v>966</v>
-      </c>
-      <c r="C476">
-        <v>3</v>
-      </c>
-      <c r="D476" t="s">
-        <v>967</v>
-      </c>
-      <c r="F476" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="477" spans="1:7">
-      <c r="A477" t="s">
-        <v>953</v>
-      </c>
-      <c r="B477" t="s">
-        <v>968</v>
-      </c>
-      <c r="C477">
-        <v>3</v>
-      </c>
-      <c r="D477" t="s">
-        <v>969</v>
-      </c>
-      <c r="F477" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="478" spans="1:7">
-      <c r="A478" t="s">
-        <v>953</v>
-      </c>
-      <c r="B478" t="s">
-        <v>970</v>
-      </c>
-      <c r="C478">
-        <v>3</v>
-      </c>
-      <c r="D478" t="s">
-        <v>971</v>
-      </c>
-      <c r="F478" t="s">
         <v>39</v>
       </c>
     </row>
